--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,180 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Ecuadorian Serie A</t>
+  </si>
+  <si>
+    <t>Colombian Primera A</t>
+  </si>
+  <si>
+    <t>Qatari Stars League</t>
+  </si>
+  <si>
+    <t>Bulgarian A League</t>
+  </si>
+  <si>
+    <t>Saudi Professional League</t>
+  </si>
+  <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>French Ligue 1</t>
+  </si>
+  <si>
+    <t>Slovenian Premier League</t>
+  </si>
+  <si>
+    <t>Polish Ekstraklasa</t>
+  </si>
+  <si>
+    <t>Spanish La Liga</t>
+  </si>
+  <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
+    <t>2026-09-04</t>
+  </si>
+  <si>
+    <t>00:00:00</t>
+  </si>
+  <si>
+    <t>01:00:00</t>
+  </si>
+  <si>
+    <t>14:00:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>18:00:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
+    <t>19:00:00</t>
+  </si>
+  <si>
+    <t>19:05:00</t>
+  </si>
+  <si>
+    <t>20:00:00</t>
+  </si>
+  <si>
+    <t>Libertad FC</t>
+  </si>
+  <si>
+    <t>Deportivo Pereira</t>
+  </si>
+  <si>
+    <t>Al Shamal</t>
+  </si>
+  <si>
+    <t>Septemvri</t>
+  </si>
+  <si>
+    <t>Abha</t>
+  </si>
+  <si>
+    <t>Vasas</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>Lyon</t>
+  </si>
+  <si>
+    <t>Al-Shabab (KSA)</t>
+  </si>
+  <si>
+    <t>Al Ahli</t>
+  </si>
+  <si>
+    <t>Arda</t>
+  </si>
+  <si>
+    <t>Nafta Lendava</t>
+  </si>
+  <si>
+    <t>Piast Gliwice</t>
+  </si>
+  <si>
+    <t>Betis</t>
+  </si>
+  <si>
+    <t>Paris St-G</t>
+  </si>
+  <si>
+    <t>Kabylie</t>
+  </si>
+  <si>
+    <t>Emelec</t>
+  </si>
+  <si>
+    <t>Ind Medellin</t>
+  </si>
+  <si>
+    <t>Al Shahaniya</t>
+  </si>
+  <si>
+    <t>Botev Vratsa</t>
+  </si>
+  <si>
+    <t>Al-Ettifaq</t>
+  </si>
+  <si>
+    <t>Nyiregyhaza</t>
+  </si>
+  <si>
+    <t>Lyngby</t>
+  </si>
+  <si>
+    <t>Auxerre</t>
+  </si>
+  <si>
+    <t>Al-Hilal</t>
+  </si>
+  <si>
+    <t>Al Riyadh SC</t>
+  </si>
+  <si>
+    <t>Botev Plovdiv</t>
+  </si>
+  <si>
+    <t>NK Radomlje</t>
+  </si>
+  <si>
+    <t>GKS Katowice</t>
+  </si>
+  <si>
+    <t>Real Madrid</t>
+  </si>
+  <si>
+    <t>Monaco</t>
+  </si>
+  <si>
+    <t>MB Rouissat</t>
+  </si>
+  <si>
+    <t>2026-09-02 01:59:28</t>
   </si>
 </sst>
 </file>
@@ -585,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -828,6 +1002,3878 @@
       </c>
       <c r="CB1" t="s">
         <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2">
+        <v>2.42</v>
+      </c>
+      <c r="G2">
+        <v>2.72</v>
+      </c>
+      <c r="H2">
+        <v>3.15</v>
+      </c>
+      <c r="I2">
+        <v>3.65</v>
+      </c>
+      <c r="J2">
+        <v>2.96</v>
+      </c>
+      <c r="K2">
+        <v>3.45</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.11</v>
+      </c>
+      <c r="N2">
+        <v>2.68</v>
+      </c>
+      <c r="O2">
+        <v>1.47</v>
+      </c>
+      <c r="P2">
+        <v>1.58</v>
+      </c>
+      <c r="Q2">
+        <v>2.36</v>
+      </c>
+      <c r="R2">
+        <v>1.21</v>
+      </c>
+      <c r="S2">
+        <v>4.5</v>
+      </c>
+      <c r="T2">
+        <v>1.97</v>
+      </c>
+      <c r="U2">
+        <v>1.83</v>
+      </c>
+      <c r="V2">
+        <v>1.37</v>
+      </c>
+      <c r="W2">
+        <v>1.58</v>
+      </c>
+      <c r="X2">
+        <v>11.5</v>
+      </c>
+      <c r="Y2">
+        <v>12.5</v>
+      </c>
+      <c r="Z2">
+        <v>27</v>
+      </c>
+      <c r="AA2">
+        <v>85</v>
+      </c>
+      <c r="AB2">
+        <v>10</v>
+      </c>
+      <c r="AC2">
+        <v>8.6</v>
+      </c>
+      <c r="AD2">
+        <v>18.5</v>
+      </c>
+      <c r="AE2">
+        <v>65</v>
+      </c>
+      <c r="AF2">
+        <v>18.5</v>
+      </c>
+      <c r="AG2">
+        <v>15</v>
+      </c>
+      <c r="AH2">
+        <v>26</v>
+      </c>
+      <c r="AI2">
+        <v>85</v>
+      </c>
+      <c r="AJ2">
+        <v>48</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>70</v>
+      </c>
+      <c r="AM2">
+        <v>190</v>
+      </c>
+      <c r="AN2">
+        <v>44</v>
+      </c>
+      <c r="AO2">
+        <v>80</v>
+      </c>
+      <c r="AP2">
+        <v>7.2</v>
+      </c>
+      <c r="AQ2">
+        <v>7.4</v>
+      </c>
+      <c r="AR2">
+        <v>15.5</v>
+      </c>
+      <c r="AS2">
+        <v>1.01</v>
+      </c>
+      <c r="AT2">
+        <v>6.4</v>
+      </c>
+      <c r="AU2">
+        <v>5.4</v>
+      </c>
+      <c r="AV2">
+        <v>10.5</v>
+      </c>
+      <c r="AW2">
+        <v>1.01</v>
+      </c>
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ2">
+        <v>15</v>
+      </c>
+      <c r="BA2">
+        <v>1.01</v>
+      </c>
+      <c r="BB2">
+        <v>1.01</v>
+      </c>
+      <c r="BC2">
+        <v>1.01</v>
+      </c>
+      <c r="BD2">
+        <v>1.01</v>
+      </c>
+      <c r="BE2">
+        <v>1.01</v>
+      </c>
+      <c r="BF2">
+        <v>1.01</v>
+      </c>
+      <c r="BG2">
+        <v>1.01</v>
+      </c>
+      <c r="BH2">
+        <v>3.35</v>
+      </c>
+      <c r="BI2">
+        <v>2.3</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>1000</v>
+      </c>
+      <c r="CA2">
+        <v>1.01</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F3">
+        <v>5.3</v>
+      </c>
+      <c r="G3">
+        <v>6.4</v>
+      </c>
+      <c r="H3">
+        <v>1.68</v>
+      </c>
+      <c r="I3">
+        <v>1.84</v>
+      </c>
+      <c r="J3">
+        <v>3.6</v>
+      </c>
+      <c r="K3">
+        <v>4.7</v>
+      </c>
+      <c r="L3">
+        <v>1.01</v>
+      </c>
+      <c r="M3">
+        <v>1.01</v>
+      </c>
+      <c r="N3">
+        <v>2.78</v>
+      </c>
+      <c r="O3">
+        <v>1.35</v>
+      </c>
+      <c r="P3">
+        <v>1.77</v>
+      </c>
+      <c r="Q3">
+        <v>2.04</v>
+      </c>
+      <c r="R3">
+        <v>1.24</v>
+      </c>
+      <c r="S3">
+        <v>3.35</v>
+      </c>
+      <c r="T3">
+        <v>1.01</v>
+      </c>
+      <c r="U3">
+        <v>1.01</v>
+      </c>
+      <c r="V3">
+        <v>2.18</v>
+      </c>
+      <c r="W3">
+        <v>1.18</v>
+      </c>
+      <c r="X3">
+        <v>18.5</v>
+      </c>
+      <c r="Y3">
+        <v>10.5</v>
+      </c>
+      <c r="Z3">
+        <v>14.5</v>
+      </c>
+      <c r="AA3">
+        <v>28</v>
+      </c>
+      <c r="AB3">
+        <v>25</v>
+      </c>
+      <c r="AC3">
+        <v>12.5</v>
+      </c>
+      <c r="AD3">
+        <v>15</v>
+      </c>
+      <c r="AE3">
+        <v>30</v>
+      </c>
+      <c r="AF3">
+        <v>65</v>
+      </c>
+      <c r="AG3">
+        <v>34</v>
+      </c>
+      <c r="AH3">
+        <v>32</v>
+      </c>
+      <c r="AI3">
+        <v>65</v>
+      </c>
+      <c r="AJ3">
+        <v>1000</v>
+      </c>
+      <c r="AK3">
+        <v>1000</v>
+      </c>
+      <c r="AL3">
+        <v>1000</v>
+      </c>
+      <c r="AM3">
+        <v>1000</v>
+      </c>
+      <c r="AN3">
+        <v>1000</v>
+      </c>
+      <c r="AO3">
+        <v>19</v>
+      </c>
+      <c r="AP3">
+        <v>2.28</v>
+      </c>
+      <c r="AQ3">
+        <v>2.08</v>
+      </c>
+      <c r="AR3">
+        <v>2.2</v>
+      </c>
+      <c r="AS3">
+        <v>2.38</v>
+      </c>
+      <c r="AT3">
+        <v>11.5</v>
+      </c>
+      <c r="AU3">
+        <v>2.16</v>
+      </c>
+      <c r="AV3">
+        <v>2.22</v>
+      </c>
+      <c r="AW3">
+        <v>2.4</v>
+      </c>
+      <c r="AX3">
+        <v>2.5</v>
+      </c>
+      <c r="AY3">
+        <v>2.42</v>
+      </c>
+      <c r="AZ3">
+        <v>2.42</v>
+      </c>
+      <c r="BA3">
+        <v>2.5</v>
+      </c>
+      <c r="BB3">
+        <v>2.6</v>
+      </c>
+      <c r="BC3">
+        <v>2.6</v>
+      </c>
+      <c r="BD3">
+        <v>2.6</v>
+      </c>
+      <c r="BE3">
+        <v>2.6</v>
+      </c>
+      <c r="BF3">
+        <v>2.6</v>
+      </c>
+      <c r="BG3">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH3">
+        <v>1000</v>
+      </c>
+      <c r="BI3">
+        <v>1.01</v>
+      </c>
+      <c r="BJ3">
+        <v>1000</v>
+      </c>
+      <c r="BK3">
+        <v>1.01</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>1000</v>
+      </c>
+      <c r="BO3">
+        <v>1.01</v>
+      </c>
+      <c r="BP3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3">
+        <v>1.01</v>
+      </c>
+      <c r="BR3">
+        <v>1000</v>
+      </c>
+      <c r="BS3">
+        <v>1.01</v>
+      </c>
+      <c r="BT3">
+        <v>1000</v>
+      </c>
+      <c r="BU3">
+        <v>1.01</v>
+      </c>
+      <c r="BV3">
+        <v>1000</v>
+      </c>
+      <c r="BW3">
+        <v>1.01</v>
+      </c>
+      <c r="BX3">
+        <v>1000</v>
+      </c>
+      <c r="BY3">
+        <v>1.01</v>
+      </c>
+      <c r="BZ3">
+        <v>1000</v>
+      </c>
+      <c r="CA3">
+        <v>1.01</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4">
+        <v>1.85</v>
+      </c>
+      <c r="G4">
+        <v>2.06</v>
+      </c>
+      <c r="H4">
+        <v>3.8</v>
+      </c>
+      <c r="I4">
+        <v>5.1</v>
+      </c>
+      <c r="J4">
+        <v>3.7</v>
+      </c>
+      <c r="K4">
+        <v>5.1</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>2.24</v>
+      </c>
+      <c r="Q4">
+        <v>1.63</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0</v>
+      </c>
+      <c r="X4">
+        <v>0</v>
+      </c>
+      <c r="Y4">
+        <v>0</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>0</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
+        <v>0</v>
+      </c>
+      <c r="AN4">
+        <v>0</v>
+      </c>
+      <c r="AO4">
+        <v>0</v>
+      </c>
+      <c r="AP4">
+        <v>0</v>
+      </c>
+      <c r="AQ4">
+        <v>0</v>
+      </c>
+      <c r="AR4">
+        <v>0</v>
+      </c>
+      <c r="AS4">
+        <v>0</v>
+      </c>
+      <c r="AT4">
+        <v>0</v>
+      </c>
+      <c r="AU4">
+        <v>0</v>
+      </c>
+      <c r="AV4">
+        <v>0</v>
+      </c>
+      <c r="AW4">
+        <v>0</v>
+      </c>
+      <c r="AX4">
+        <v>0</v>
+      </c>
+      <c r="AY4">
+        <v>0</v>
+      </c>
+      <c r="AZ4">
+        <v>0</v>
+      </c>
+      <c r="BA4">
+        <v>0</v>
+      </c>
+      <c r="BB4">
+        <v>0</v>
+      </c>
+      <c r="BC4">
+        <v>0</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0</v>
+      </c>
+      <c r="BG4">
+        <v>0</v>
+      </c>
+      <c r="BH4">
+        <v>0</v>
+      </c>
+      <c r="BI4">
+        <v>0</v>
+      </c>
+      <c r="BJ4">
+        <v>0</v>
+      </c>
+      <c r="BK4">
+        <v>0</v>
+      </c>
+      <c r="BL4">
+        <v>0</v>
+      </c>
+      <c r="BM4">
+        <v>0</v>
+      </c>
+      <c r="BN4">
+        <v>0</v>
+      </c>
+      <c r="BO4">
+        <v>0</v>
+      </c>
+      <c r="BP4">
+        <v>0</v>
+      </c>
+      <c r="BQ4">
+        <v>0</v>
+      </c>
+      <c r="BR4">
+        <v>0</v>
+      </c>
+      <c r="BS4">
+        <v>0</v>
+      </c>
+      <c r="BT4">
+        <v>0</v>
+      </c>
+      <c r="BU4">
+        <v>0</v>
+      </c>
+      <c r="BV4">
+        <v>0</v>
+      </c>
+      <c r="BW4">
+        <v>0</v>
+      </c>
+      <c r="BX4">
+        <v>0</v>
+      </c>
+      <c r="BY4">
+        <v>0</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C5" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F5">
+        <v>2.62</v>
+      </c>
+      <c r="G5">
+        <v>2.96</v>
+      </c>
+      <c r="H5">
+        <v>2.84</v>
+      </c>
+      <c r="I5">
+        <v>3.2</v>
+      </c>
+      <c r="J5">
+        <v>2.94</v>
+      </c>
+      <c r="K5">
+        <v>3.8</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1.59</v>
+      </c>
+      <c r="Q5">
+        <v>2.36</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>0</v>
+      </c>
+      <c r="AG5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>0</v>
+      </c>
+      <c r="AI5">
+        <v>0</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AK5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>0</v>
+      </c>
+      <c r="AO5">
+        <v>0</v>
+      </c>
+      <c r="AP5">
+        <v>0</v>
+      </c>
+      <c r="AQ5">
+        <v>0</v>
+      </c>
+      <c r="AR5">
+        <v>0</v>
+      </c>
+      <c r="AS5">
+        <v>0</v>
+      </c>
+      <c r="AT5">
+        <v>0</v>
+      </c>
+      <c r="AU5">
+        <v>0</v>
+      </c>
+      <c r="AV5">
+        <v>0</v>
+      </c>
+      <c r="AW5">
+        <v>0</v>
+      </c>
+      <c r="AX5">
+        <v>0</v>
+      </c>
+      <c r="AY5">
+        <v>0</v>
+      </c>
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+      <c r="BA5">
+        <v>0</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+      <c r="BC5">
+        <v>0</v>
+      </c>
+      <c r="BD5">
+        <v>0</v>
+      </c>
+      <c r="BE5">
+        <v>0</v>
+      </c>
+      <c r="BF5">
+        <v>0</v>
+      </c>
+      <c r="BG5">
+        <v>0</v>
+      </c>
+      <c r="BH5">
+        <v>0</v>
+      </c>
+      <c r="BI5">
+        <v>0</v>
+      </c>
+      <c r="BJ5">
+        <v>0</v>
+      </c>
+      <c r="BK5">
+        <v>0</v>
+      </c>
+      <c r="BL5">
+        <v>0</v>
+      </c>
+      <c r="BM5">
+        <v>0</v>
+      </c>
+      <c r="BN5">
+        <v>0</v>
+      </c>
+      <c r="BO5">
+        <v>0</v>
+      </c>
+      <c r="BP5">
+        <v>0</v>
+      </c>
+      <c r="BQ5">
+        <v>0</v>
+      </c>
+      <c r="BR5">
+        <v>0</v>
+      </c>
+      <c r="BS5">
+        <v>0</v>
+      </c>
+      <c r="BT5">
+        <v>0</v>
+      </c>
+      <c r="BU5">
+        <v>0</v>
+      </c>
+      <c r="BV5">
+        <v>0</v>
+      </c>
+      <c r="BW5">
+        <v>0</v>
+      </c>
+      <c r="BX5">
+        <v>0</v>
+      </c>
+      <c r="BY5">
+        <v>0</v>
+      </c>
+      <c r="BZ5">
+        <v>0</v>
+      </c>
+      <c r="CA5">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E6" t="s">
+        <v>125</v>
+      </c>
+      <c r="F6">
+        <v>2.8</v>
+      </c>
+      <c r="G6">
+        <v>3.2</v>
+      </c>
+      <c r="H6">
+        <v>2.4</v>
+      </c>
+      <c r="I6">
+        <v>2.7</v>
+      </c>
+      <c r="J6">
+        <v>3.4</v>
+      </c>
+      <c r="K6">
+        <v>4.5</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>2.04</v>
+      </c>
+      <c r="Q6">
+        <v>1.77</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>0</v>
+      </c>
+      <c r="Y6">
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>0</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0</v>
+      </c>
+      <c r="AI6">
+        <v>0</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>0</v>
+      </c>
+      <c r="AM6">
+        <v>0</v>
+      </c>
+      <c r="AN6">
+        <v>0</v>
+      </c>
+      <c r="AO6">
+        <v>0</v>
+      </c>
+      <c r="AP6">
+        <v>0</v>
+      </c>
+      <c r="AQ6">
+        <v>0</v>
+      </c>
+      <c r="AR6">
+        <v>0</v>
+      </c>
+      <c r="AS6">
+        <v>0</v>
+      </c>
+      <c r="AT6">
+        <v>0</v>
+      </c>
+      <c r="AU6">
+        <v>0</v>
+      </c>
+      <c r="AV6">
+        <v>0</v>
+      </c>
+      <c r="AW6">
+        <v>0</v>
+      </c>
+      <c r="AX6">
+        <v>0</v>
+      </c>
+      <c r="AY6">
+        <v>0</v>
+      </c>
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+      <c r="BA6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+      <c r="BC6">
+        <v>0</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0</v>
+      </c>
+      <c r="BG6">
+        <v>0</v>
+      </c>
+      <c r="BH6">
+        <v>0</v>
+      </c>
+      <c r="BI6">
+        <v>0</v>
+      </c>
+      <c r="BJ6">
+        <v>0</v>
+      </c>
+      <c r="BK6">
+        <v>0</v>
+      </c>
+      <c r="BL6">
+        <v>0</v>
+      </c>
+      <c r="BM6">
+        <v>0</v>
+      </c>
+      <c r="BN6">
+        <v>0</v>
+      </c>
+      <c r="BO6">
+        <v>0</v>
+      </c>
+      <c r="BP6">
+        <v>0</v>
+      </c>
+      <c r="BQ6">
+        <v>0</v>
+      </c>
+      <c r="BR6">
+        <v>0</v>
+      </c>
+      <c r="BS6">
+        <v>0</v>
+      </c>
+      <c r="BT6">
+        <v>0</v>
+      </c>
+      <c r="BU6">
+        <v>0</v>
+      </c>
+      <c r="BV6">
+        <v>0</v>
+      </c>
+      <c r="BW6">
+        <v>0</v>
+      </c>
+      <c r="BX6">
+        <v>0</v>
+      </c>
+      <c r="BY6">
+        <v>0</v>
+      </c>
+      <c r="BZ6">
+        <v>0</v>
+      </c>
+      <c r="CA6">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" t="s">
+        <v>110</v>
+      </c>
+      <c r="E7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7">
+        <v>2.3</v>
+      </c>
+      <c r="G7">
+        <v>2.62</v>
+      </c>
+      <c r="H7">
+        <v>2.88</v>
+      </c>
+      <c r="I7">
+        <v>3.5</v>
+      </c>
+      <c r="J7">
+        <v>3.45</v>
+      </c>
+      <c r="K7">
+        <v>4.5</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>2.1</v>
+      </c>
+      <c r="Q7">
+        <v>1.65</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7">
+        <v>0</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0</v>
+      </c>
+      <c r="X7">
+        <v>0</v>
+      </c>
+      <c r="Y7">
+        <v>0</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <v>0</v>
+      </c>
+      <c r="AG7">
+        <v>0</v>
+      </c>
+      <c r="AH7">
+        <v>0</v>
+      </c>
+      <c r="AI7">
+        <v>0</v>
+      </c>
+      <c r="AJ7">
+        <v>0</v>
+      </c>
+      <c r="AK7">
+        <v>0</v>
+      </c>
+      <c r="AL7">
+        <v>0</v>
+      </c>
+      <c r="AM7">
+        <v>0</v>
+      </c>
+      <c r="AN7">
+        <v>0</v>
+      </c>
+      <c r="AO7">
+        <v>0</v>
+      </c>
+      <c r="AP7">
+        <v>0</v>
+      </c>
+      <c r="AQ7">
+        <v>0</v>
+      </c>
+      <c r="AR7">
+        <v>0</v>
+      </c>
+      <c r="AS7">
+        <v>0</v>
+      </c>
+      <c r="AT7">
+        <v>0</v>
+      </c>
+      <c r="AU7">
+        <v>0</v>
+      </c>
+      <c r="AV7">
+        <v>0</v>
+      </c>
+      <c r="AW7">
+        <v>0</v>
+      </c>
+      <c r="AX7">
+        <v>0</v>
+      </c>
+      <c r="AY7">
+        <v>0</v>
+      </c>
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+      <c r="BA7">
+        <v>0</v>
+      </c>
+      <c r="BB7">
+        <v>0</v>
+      </c>
+      <c r="BC7">
+        <v>0</v>
+      </c>
+      <c r="BD7">
+        <v>0</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0</v>
+      </c>
+      <c r="BG7">
+        <v>0</v>
+      </c>
+      <c r="BH7">
+        <v>0</v>
+      </c>
+      <c r="BI7">
+        <v>0</v>
+      </c>
+      <c r="BJ7">
+        <v>0</v>
+      </c>
+      <c r="BK7">
+        <v>0</v>
+      </c>
+      <c r="BL7">
+        <v>0</v>
+      </c>
+      <c r="BM7">
+        <v>0</v>
+      </c>
+      <c r="BN7">
+        <v>0</v>
+      </c>
+      <c r="BO7">
+        <v>0</v>
+      </c>
+      <c r="BP7">
+        <v>0</v>
+      </c>
+      <c r="BQ7">
+        <v>0</v>
+      </c>
+      <c r="BR7">
+        <v>0</v>
+      </c>
+      <c r="BS7">
+        <v>0</v>
+      </c>
+      <c r="BT7">
+        <v>0</v>
+      </c>
+      <c r="BU7">
+        <v>0</v>
+      </c>
+      <c r="BV7">
+        <v>0</v>
+      </c>
+      <c r="BW7">
+        <v>0</v>
+      </c>
+      <c r="BX7">
+        <v>0</v>
+      </c>
+      <c r="BY7">
+        <v>0</v>
+      </c>
+      <c r="BZ7">
+        <v>0</v>
+      </c>
+      <c r="CA7">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" t="s">
+        <v>127</v>
+      </c>
+      <c r="F8">
+        <v>1.86</v>
+      </c>
+      <c r="G8">
+        <v>1.98</v>
+      </c>
+      <c r="H8">
+        <v>3.9</v>
+      </c>
+      <c r="I8">
+        <v>4.3</v>
+      </c>
+      <c r="J8">
+        <v>4.1</v>
+      </c>
+      <c r="K8">
+        <v>4.4</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>2.48</v>
+      </c>
+      <c r="Q8">
+        <v>1.55</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8">
+        <v>0</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>0</v>
+      </c>
+      <c r="Y8">
+        <v>0</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
+      </c>
+      <c r="AF8">
+        <v>0</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AJ8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+      <c r="AL8">
+        <v>0</v>
+      </c>
+      <c r="AM8">
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AO8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>0</v>
+      </c>
+      <c r="AQ8">
+        <v>0</v>
+      </c>
+      <c r="AR8">
+        <v>0</v>
+      </c>
+      <c r="AS8">
+        <v>0</v>
+      </c>
+      <c r="AT8">
+        <v>0</v>
+      </c>
+      <c r="AU8">
+        <v>0</v>
+      </c>
+      <c r="AV8">
+        <v>0</v>
+      </c>
+      <c r="AW8">
+        <v>0</v>
+      </c>
+      <c r="AX8">
+        <v>0</v>
+      </c>
+      <c r="AY8">
+        <v>0</v>
+      </c>
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+      <c r="BA8">
+        <v>0</v>
+      </c>
+      <c r="BB8">
+        <v>0</v>
+      </c>
+      <c r="BC8">
+        <v>0</v>
+      </c>
+      <c r="BD8">
+        <v>0</v>
+      </c>
+      <c r="BE8">
+        <v>0</v>
+      </c>
+      <c r="BF8">
+        <v>0</v>
+      </c>
+      <c r="BG8">
+        <v>0</v>
+      </c>
+      <c r="BH8">
+        <v>0</v>
+      </c>
+      <c r="BI8">
+        <v>0</v>
+      </c>
+      <c r="BJ8">
+        <v>0</v>
+      </c>
+      <c r="BK8">
+        <v>0</v>
+      </c>
+      <c r="BL8">
+        <v>0</v>
+      </c>
+      <c r="BM8">
+        <v>0</v>
+      </c>
+      <c r="BN8">
+        <v>0</v>
+      </c>
+      <c r="BO8">
+        <v>0</v>
+      </c>
+      <c r="BP8">
+        <v>0</v>
+      </c>
+      <c r="BQ8">
+        <v>0</v>
+      </c>
+      <c r="BR8">
+        <v>0</v>
+      </c>
+      <c r="BS8">
+        <v>0</v>
+      </c>
+      <c r="BT8">
+        <v>0</v>
+      </c>
+      <c r="BU8">
+        <v>0</v>
+      </c>
+      <c r="BV8">
+        <v>0</v>
+      </c>
+      <c r="BW8">
+        <v>0</v>
+      </c>
+      <c r="BX8">
+        <v>0</v>
+      </c>
+      <c r="BY8">
+        <v>0</v>
+      </c>
+      <c r="BZ8">
+        <v>0</v>
+      </c>
+      <c r="CA8">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9">
+        <v>1.56</v>
+      </c>
+      <c r="G9">
+        <v>1.58</v>
+      </c>
+      <c r="H9">
+        <v>6.4</v>
+      </c>
+      <c r="I9">
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <v>4.6</v>
+      </c>
+      <c r="K9">
+        <v>4.9</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>1.05</v>
+      </c>
+      <c r="N9">
+        <v>4.7</v>
+      </c>
+      <c r="O9">
+        <v>1.24</v>
+      </c>
+      <c r="P9">
+        <v>2.28</v>
+      </c>
+      <c r="Q9">
+        <v>1.68</v>
+      </c>
+      <c r="R9">
+        <v>1.5</v>
+      </c>
+      <c r="S9">
+        <v>2.78</v>
+      </c>
+      <c r="T9">
+        <v>1.86</v>
+      </c>
+      <c r="U9">
+        <v>2.08</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <v>21</v>
+      </c>
+      <c r="Y9">
+        <v>28</v>
+      </c>
+      <c r="Z9">
+        <v>65</v>
+      </c>
+      <c r="AA9">
+        <v>210</v>
+      </c>
+      <c r="AB9">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC9">
+        <v>11</v>
+      </c>
+      <c r="AD9">
+        <v>25</v>
+      </c>
+      <c r="AE9">
+        <v>100</v>
+      </c>
+      <c r="AF9">
+        <v>10</v>
+      </c>
+      <c r="AG9">
+        <v>10.5</v>
+      </c>
+      <c r="AH9">
+        <v>24</v>
+      </c>
+      <c r="AI9">
+        <v>90</v>
+      </c>
+      <c r="AJ9">
+        <v>14.5</v>
+      </c>
+      <c r="AK9">
+        <v>16</v>
+      </c>
+      <c r="AL9">
+        <v>38</v>
+      </c>
+      <c r="AM9">
+        <v>120</v>
+      </c>
+      <c r="AN9">
+        <v>7.2</v>
+      </c>
+      <c r="AO9">
+        <v>110</v>
+      </c>
+      <c r="AP9">
+        <v>17</v>
+      </c>
+      <c r="AQ9">
+        <v>20</v>
+      </c>
+      <c r="AR9">
+        <v>9.6</v>
+      </c>
+      <c r="AS9">
+        <v>10.5</v>
+      </c>
+      <c r="AT9">
+        <v>8.6</v>
+      </c>
+      <c r="AU9">
+        <v>9.4</v>
+      </c>
+      <c r="AV9">
+        <v>20</v>
+      </c>
+      <c r="AW9">
+        <v>10</v>
+      </c>
+      <c r="AX9">
+        <v>9</v>
+      </c>
+      <c r="AY9">
+        <v>9</v>
+      </c>
+      <c r="AZ9">
+        <v>18.5</v>
+      </c>
+      <c r="BA9">
+        <v>10</v>
+      </c>
+      <c r="BB9">
+        <v>12.5</v>
+      </c>
+      <c r="BC9">
+        <v>13.5</v>
+      </c>
+      <c r="BD9">
+        <v>8.6</v>
+      </c>
+      <c r="BE9">
+        <v>10</v>
+      </c>
+      <c r="BF9">
+        <v>6.6</v>
+      </c>
+      <c r="BG9">
+        <v>10</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>0</v>
+      </c>
+      <c r="CA9">
+        <v>0</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10">
+        <v>7.2</v>
+      </c>
+      <c r="G10">
+        <v>1000</v>
+      </c>
+      <c r="H10">
+        <v>1.27</v>
+      </c>
+      <c r="I10">
+        <v>1.44</v>
+      </c>
+      <c r="J10">
+        <v>4.7</v>
+      </c>
+      <c r="K10">
+        <v>14</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>2.62</v>
+      </c>
+      <c r="Q10">
+        <v>1.32</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <v>0</v>
+      </c>
+      <c r="Y10">
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>0</v>
+      </c>
+      <c r="AB10">
+        <v>0</v>
+      </c>
+      <c r="AC10">
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>0</v>
+      </c>
+      <c r="AK10">
+        <v>0</v>
+      </c>
+      <c r="AL10">
+        <v>0</v>
+      </c>
+      <c r="AM10">
+        <v>0</v>
+      </c>
+      <c r="AN10">
+        <v>0</v>
+      </c>
+      <c r="AO10">
+        <v>0</v>
+      </c>
+      <c r="AP10">
+        <v>0</v>
+      </c>
+      <c r="AQ10">
+        <v>0</v>
+      </c>
+      <c r="AR10">
+        <v>0</v>
+      </c>
+      <c r="AS10">
+        <v>0</v>
+      </c>
+      <c r="AT10">
+        <v>0</v>
+      </c>
+      <c r="AU10">
+        <v>0</v>
+      </c>
+      <c r="AV10">
+        <v>0</v>
+      </c>
+      <c r="AW10">
+        <v>0</v>
+      </c>
+      <c r="AX10">
+        <v>0</v>
+      </c>
+      <c r="AY10">
+        <v>0</v>
+      </c>
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+      <c r="BA10">
+        <v>0</v>
+      </c>
+      <c r="BB10">
+        <v>0</v>
+      </c>
+      <c r="BC10">
+        <v>0</v>
+      </c>
+      <c r="BD10">
+        <v>0</v>
+      </c>
+      <c r="BE10">
+        <v>0</v>
+      </c>
+      <c r="BF10">
+        <v>0</v>
+      </c>
+      <c r="BG10">
+        <v>0</v>
+      </c>
+      <c r="BH10">
+        <v>0</v>
+      </c>
+      <c r="BI10">
+        <v>0</v>
+      </c>
+      <c r="BJ10">
+        <v>0</v>
+      </c>
+      <c r="BK10">
+        <v>0</v>
+      </c>
+      <c r="BL10">
+        <v>0</v>
+      </c>
+      <c r="BM10">
+        <v>0</v>
+      </c>
+      <c r="BN10">
+        <v>0</v>
+      </c>
+      <c r="BO10">
+        <v>0</v>
+      </c>
+      <c r="BP10">
+        <v>0</v>
+      </c>
+      <c r="BQ10">
+        <v>0</v>
+      </c>
+      <c r="BR10">
+        <v>0</v>
+      </c>
+      <c r="BS10">
+        <v>0</v>
+      </c>
+      <c r="BT10">
+        <v>0</v>
+      </c>
+      <c r="BU10">
+        <v>0</v>
+      </c>
+      <c r="BV10">
+        <v>0</v>
+      </c>
+      <c r="BW10">
+        <v>0</v>
+      </c>
+      <c r="BX10">
+        <v>0</v>
+      </c>
+      <c r="BY10">
+        <v>0</v>
+      </c>
+      <c r="BZ10">
+        <v>0</v>
+      </c>
+      <c r="CA10">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11">
+        <v>1.26</v>
+      </c>
+      <c r="G11">
+        <v>1.34</v>
+      </c>
+      <c r="H11">
+        <v>10.5</v>
+      </c>
+      <c r="I11">
+        <v>15.5</v>
+      </c>
+      <c r="J11">
+        <v>5.5</v>
+      </c>
+      <c r="K11">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L11">
+        <v>1.19</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>6.6</v>
+      </c>
+      <c r="O11">
+        <v>1.14</v>
+      </c>
+      <c r="P11">
+        <v>2.92</v>
+      </c>
+      <c r="Q11">
+        <v>1.41</v>
+      </c>
+      <c r="R11">
+        <v>1.78</v>
+      </c>
+      <c r="S11">
+        <v>2.02</v>
+      </c>
+      <c r="T11">
+        <v>1.84</v>
+      </c>
+      <c r="U11">
+        <v>1.94</v>
+      </c>
+      <c r="V11">
+        <v>1.06</v>
+      </c>
+      <c r="W11">
+        <v>3.9</v>
+      </c>
+      <c r="X11">
+        <v>44</v>
+      </c>
+      <c r="Y11">
+        <v>60</v>
+      </c>
+      <c r="Z11">
+        <v>140</v>
+      </c>
+      <c r="AA11">
+        <v>470</v>
+      </c>
+      <c r="AB11">
+        <v>15.5</v>
+      </c>
+      <c r="AC11">
+        <v>19.5</v>
+      </c>
+      <c r="AD11">
+        <v>55</v>
+      </c>
+      <c r="AE11">
+        <v>190</v>
+      </c>
+      <c r="AF11">
+        <v>12</v>
+      </c>
+      <c r="AG11">
+        <v>14</v>
+      </c>
+      <c r="AH11">
+        <v>34</v>
+      </c>
+      <c r="AI11">
+        <v>140</v>
+      </c>
+      <c r="AJ11">
+        <v>13</v>
+      </c>
+      <c r="AK11">
+        <v>16.5</v>
+      </c>
+      <c r="AL11">
+        <v>40</v>
+      </c>
+      <c r="AM11">
+        <v>150</v>
+      </c>
+      <c r="AN11">
+        <v>4.4</v>
+      </c>
+      <c r="AO11">
+        <v>200</v>
+      </c>
+      <c r="AP11">
+        <v>4.1</v>
+      </c>
+      <c r="AQ11">
+        <v>4.2</v>
+      </c>
+      <c r="AR11">
+        <v>4.4</v>
+      </c>
+      <c r="AS11">
+        <v>4.5</v>
+      </c>
+      <c r="AT11">
+        <v>10.5</v>
+      </c>
+      <c r="AU11">
+        <v>11.5</v>
+      </c>
+      <c r="AV11">
+        <v>4.2</v>
+      </c>
+      <c r="AW11">
+        <v>4.4</v>
+      </c>
+      <c r="AX11">
+        <v>7.4</v>
+      </c>
+      <c r="AY11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ11">
+        <v>20</v>
+      </c>
+      <c r="BA11">
+        <v>4.4</v>
+      </c>
+      <c r="BB11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC11">
+        <v>10</v>
+      </c>
+      <c r="BD11">
+        <v>4</v>
+      </c>
+      <c r="BE11">
+        <v>4.4</v>
+      </c>
+      <c r="BF11">
+        <v>2.96</v>
+      </c>
+      <c r="BG11">
+        <v>4.4</v>
+      </c>
+      <c r="BH11">
+        <v>6.2</v>
+      </c>
+      <c r="BI11">
+        <v>3.95</v>
+      </c>
+      <c r="BJ11">
+        <v>14</v>
+      </c>
+      <c r="BK11">
+        <v>1.01</v>
+      </c>
+      <c r="BL11">
+        <v>140</v>
+      </c>
+      <c r="BM11">
+        <v>1.01</v>
+      </c>
+      <c r="BN11">
+        <v>4.8</v>
+      </c>
+      <c r="BO11">
+        <v>3.2</v>
+      </c>
+      <c r="BP11">
+        <v>8.4</v>
+      </c>
+      <c r="BQ11">
+        <v>5.3</v>
+      </c>
+      <c r="BR11">
+        <v>24</v>
+      </c>
+      <c r="BS11">
+        <v>1.01</v>
+      </c>
+      <c r="BT11">
+        <v>17.5</v>
+      </c>
+      <c r="BU11">
+        <v>1.01</v>
+      </c>
+      <c r="BV11">
+        <v>100</v>
+      </c>
+      <c r="BW11">
+        <v>1.01</v>
+      </c>
+      <c r="BX11">
+        <v>80</v>
+      </c>
+      <c r="BY11">
+        <v>1.01</v>
+      </c>
+      <c r="BZ11">
+        <v>10.5</v>
+      </c>
+      <c r="CA11">
+        <v>1.01</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12">
+        <v>2.12</v>
+      </c>
+      <c r="G12">
+        <v>2.4</v>
+      </c>
+      <c r="H12">
+        <v>3.5</v>
+      </c>
+      <c r="I12">
+        <v>4.2</v>
+      </c>
+      <c r="J12">
+        <v>3.15</v>
+      </c>
+      <c r="K12">
+        <v>4.2</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.71</v>
+      </c>
+      <c r="Q12">
+        <v>2.1</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.24</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14">
+        <v>2.44</v>
+      </c>
+      <c r="G14">
+        <v>2.72</v>
+      </c>
+      <c r="H14">
+        <v>2.7</v>
+      </c>
+      <c r="I14">
+        <v>3.2</v>
+      </c>
+      <c r="J14">
+        <v>3.65</v>
+      </c>
+      <c r="K14">
+        <v>4.6</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>2.24</v>
+      </c>
+      <c r="Q14">
+        <v>1.56</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+      <c r="S14">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0</v>
+      </c>
+      <c r="U14">
+        <v>0</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <v>0</v>
+      </c>
+      <c r="Y14">
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <v>0</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0</v>
+      </c>
+      <c r="AI14">
+        <v>0</v>
+      </c>
+      <c r="AJ14">
+        <v>0</v>
+      </c>
+      <c r="AK14">
+        <v>0</v>
+      </c>
+      <c r="AL14">
+        <v>0</v>
+      </c>
+      <c r="AM14">
+        <v>0</v>
+      </c>
+      <c r="AN14">
+        <v>0</v>
+      </c>
+      <c r="AO14">
+        <v>0</v>
+      </c>
+      <c r="AP14">
+        <v>0</v>
+      </c>
+      <c r="AQ14">
+        <v>0</v>
+      </c>
+      <c r="AR14">
+        <v>0</v>
+      </c>
+      <c r="AS14">
+        <v>0</v>
+      </c>
+      <c r="AT14">
+        <v>0</v>
+      </c>
+      <c r="AU14">
+        <v>0</v>
+      </c>
+      <c r="AV14">
+        <v>0</v>
+      </c>
+      <c r="AW14">
+        <v>0</v>
+      </c>
+      <c r="AX14">
+        <v>0</v>
+      </c>
+      <c r="AY14">
+        <v>0</v>
+      </c>
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+      <c r="BA14">
+        <v>0</v>
+      </c>
+      <c r="BB14">
+        <v>0</v>
+      </c>
+      <c r="BC14">
+        <v>0</v>
+      </c>
+      <c r="BD14">
+        <v>0</v>
+      </c>
+      <c r="BE14">
+        <v>0</v>
+      </c>
+      <c r="BF14">
+        <v>0</v>
+      </c>
+      <c r="BG14">
+        <v>0</v>
+      </c>
+      <c r="BH14">
+        <v>0</v>
+      </c>
+      <c r="BI14">
+        <v>0</v>
+      </c>
+      <c r="BJ14">
+        <v>0</v>
+      </c>
+      <c r="BK14">
+        <v>0</v>
+      </c>
+      <c r="BL14">
+        <v>0</v>
+      </c>
+      <c r="BM14">
+        <v>0</v>
+      </c>
+      <c r="BN14">
+        <v>0</v>
+      </c>
+      <c r="BO14">
+        <v>0</v>
+      </c>
+      <c r="BP14">
+        <v>0</v>
+      </c>
+      <c r="BQ14">
+        <v>0</v>
+      </c>
+      <c r="BR14">
+        <v>0</v>
+      </c>
+      <c r="BS14">
+        <v>0</v>
+      </c>
+      <c r="BT14">
+        <v>0</v>
+      </c>
+      <c r="BU14">
+        <v>0</v>
+      </c>
+      <c r="BV14">
+        <v>0</v>
+      </c>
+      <c r="BW14">
+        <v>0</v>
+      </c>
+      <c r="BX14">
+        <v>0</v>
+      </c>
+      <c r="BY14">
+        <v>0</v>
+      </c>
+      <c r="BZ14">
+        <v>0</v>
+      </c>
+      <c r="CA14">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" t="s">
+        <v>134</v>
+      </c>
+      <c r="F15">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="G15">
+        <v>8.4</v>
+      </c>
+      <c r="H15">
+        <v>1.43</v>
+      </c>
+      <c r="I15">
+        <v>1.44</v>
+      </c>
+      <c r="J15">
+        <v>5.5</v>
+      </c>
+      <c r="K15">
+        <v>5.6</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>1.03</v>
+      </c>
+      <c r="N15">
+        <v>7.6</v>
+      </c>
+      <c r="O15">
+        <v>1.14</v>
+      </c>
+      <c r="P15">
+        <v>3.2</v>
+      </c>
+      <c r="Q15">
+        <v>1.43</v>
+      </c>
+      <c r="R15">
+        <v>1.86</v>
+      </c>
+      <c r="S15">
+        <v>2.06</v>
+      </c>
+      <c r="T15">
+        <v>1.62</v>
+      </c>
+      <c r="U15">
+        <v>2.5</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>38</v>
+      </c>
+      <c r="Y15">
+        <v>14.5</v>
+      </c>
+      <c r="Z15">
+        <v>12.5</v>
+      </c>
+      <c r="AA15">
+        <v>14.5</v>
+      </c>
+      <c r="AB15">
+        <v>42</v>
+      </c>
+      <c r="AC15">
+        <v>13.5</v>
+      </c>
+      <c r="AD15">
+        <v>10.5</v>
+      </c>
+      <c r="AE15">
+        <v>13.5</v>
+      </c>
+      <c r="AF15">
+        <v>110</v>
+      </c>
+      <c r="AG15">
+        <v>32</v>
+      </c>
+      <c r="AH15">
+        <v>19.5</v>
+      </c>
+      <c r="AI15">
+        <v>24</v>
+      </c>
+      <c r="AJ15">
+        <v>1000</v>
+      </c>
+      <c r="AK15">
+        <v>120</v>
+      </c>
+      <c r="AL15">
+        <v>80</v>
+      </c>
+      <c r="AM15">
+        <v>85</v>
+      </c>
+      <c r="AN15">
+        <v>85</v>
+      </c>
+      <c r="AO15">
+        <v>4.4</v>
+      </c>
+      <c r="AP15">
+        <v>30</v>
+      </c>
+      <c r="AQ15">
+        <v>13</v>
+      </c>
+      <c r="AR15">
+        <v>10.5</v>
+      </c>
+      <c r="AS15">
+        <v>12.5</v>
+      </c>
+      <c r="AT15">
+        <v>34</v>
+      </c>
+      <c r="AU15">
+        <v>12</v>
+      </c>
+      <c r="AV15">
+        <v>9.4</v>
+      </c>
+      <c r="AW15">
+        <v>11.5</v>
+      </c>
+      <c r="AX15">
+        <v>50</v>
+      </c>
+      <c r="AY15">
+        <v>26</v>
+      </c>
+      <c r="AZ15">
+        <v>17</v>
+      </c>
+      <c r="BA15">
+        <v>20</v>
+      </c>
+      <c r="BB15">
+        <v>14.5</v>
+      </c>
+      <c r="BC15">
+        <v>50</v>
+      </c>
+      <c r="BD15">
+        <v>50</v>
+      </c>
+      <c r="BE15">
+        <v>48</v>
+      </c>
+      <c r="BF15">
+        <v>46</v>
+      </c>
+      <c r="BG15">
+        <v>4.1</v>
+      </c>
+      <c r="BH15">
+        <v>6.4</v>
+      </c>
+      <c r="BI15">
+        <v>4.1</v>
+      </c>
+      <c r="BJ15">
+        <v>12</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>95</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>13.5</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>60</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>55</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>5.4</v>
+      </c>
+      <c r="BU15">
+        <v>3.55</v>
+      </c>
+      <c r="BV15">
+        <v>10</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>21</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>11.5</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" t="s">
+        <v>135</v>
+      </c>
+      <c r="F16">
+        <v>1.42</v>
+      </c>
+      <c r="G16">
+        <v>1.43</v>
+      </c>
+      <c r="H16">
+        <v>7.8</v>
+      </c>
+      <c r="I16">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J16">
+        <v>5.6</v>
+      </c>
+      <c r="K16">
+        <v>5.8</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>1.02</v>
+      </c>
+      <c r="N16">
+        <v>6.6</v>
+      </c>
+      <c r="O16">
+        <v>1.15</v>
+      </c>
+      <c r="P16">
+        <v>3</v>
+      </c>
+      <c r="Q16">
+        <v>1.47</v>
+      </c>
+      <c r="R16">
+        <v>1.83</v>
+      </c>
+      <c r="S16">
+        <v>2.14</v>
+      </c>
+      <c r="T16">
+        <v>1.7</v>
+      </c>
+      <c r="U16">
+        <v>2.34</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>34</v>
+      </c>
+      <c r="Y16">
+        <v>38</v>
+      </c>
+      <c r="Z16">
+        <v>90</v>
+      </c>
+      <c r="AA16">
+        <v>250</v>
+      </c>
+      <c r="AB16">
+        <v>13</v>
+      </c>
+      <c r="AC16">
+        <v>13</v>
+      </c>
+      <c r="AD16">
+        <v>32</v>
+      </c>
+      <c r="AE16">
+        <v>110</v>
+      </c>
+      <c r="AF16">
+        <v>11.5</v>
+      </c>
+      <c r="AG16">
+        <v>11</v>
+      </c>
+      <c r="AH16">
+        <v>22</v>
+      </c>
+      <c r="AI16">
+        <v>90</v>
+      </c>
+      <c r="AJ16">
+        <v>14</v>
+      </c>
+      <c r="AK16">
+        <v>14</v>
+      </c>
+      <c r="AL16">
+        <v>26</v>
+      </c>
+      <c r="AM16">
+        <v>100</v>
+      </c>
+      <c r="AN16">
+        <v>4.5</v>
+      </c>
+      <c r="AO16">
+        <v>90</v>
+      </c>
+      <c r="AP16">
+        <v>9.4</v>
+      </c>
+      <c r="AQ16">
+        <v>28</v>
+      </c>
+      <c r="AR16">
+        <v>11</v>
+      </c>
+      <c r="AS16">
+        <v>12.5</v>
+      </c>
+      <c r="AT16">
+        <v>11</v>
+      </c>
+      <c r="AU16">
+        <v>11.5</v>
+      </c>
+      <c r="AV16">
+        <v>24</v>
+      </c>
+      <c r="AW16">
+        <v>11.5</v>
+      </c>
+      <c r="AX16">
+        <v>10</v>
+      </c>
+      <c r="AY16">
+        <v>9.6</v>
+      </c>
+      <c r="AZ16">
+        <v>19.5</v>
+      </c>
+      <c r="BA16">
+        <v>11</v>
+      </c>
+      <c r="BB16">
+        <v>12.5</v>
+      </c>
+      <c r="BC16">
+        <v>12.5</v>
+      </c>
+      <c r="BD16">
+        <v>19</v>
+      </c>
+      <c r="BE16">
+        <v>11.5</v>
+      </c>
+      <c r="BF16">
+        <v>4.1</v>
+      </c>
+      <c r="BG16">
+        <v>11</v>
+      </c>
+      <c r="BH16">
+        <v>1000</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>1000</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>1000</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>1000</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>1000</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>1000</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>1000</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>1000</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>0</v>
+      </c>
+      <c r="CA16">
+        <v>0</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17">
+        <v>1.08</v>
+      </c>
+      <c r="G17">
+        <v>1000</v>
+      </c>
+      <c r="H17">
+        <v>1.08</v>
+      </c>
+      <c r="I17">
+        <v>1000</v>
+      </c>
+      <c r="J17">
+        <v>1.08</v>
+      </c>
+      <c r="K17">
+        <v>1000</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>1.07</v>
+      </c>
+      <c r="Q17">
+        <v>1.01</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -427,7 +427,7 @@
     <t>MB Rouissat</t>
   </si>
   <si>
-    <t>2026-09-02 01:59:28</t>
+    <t>2026-09-02 03:17:29</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1021,7 @@
         <v>121</v>
       </c>
       <c r="F2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G2">
         <v>2.72</v>
@@ -1030,7 +1030,7 @@
         <v>3.15</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J2">
         <v>2.96</v>
@@ -1039,13 +1039,13 @@
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M2">
         <v>1.11</v>
       </c>
       <c r="N2">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O2">
         <v>1.47</v>
@@ -1063,13 +1063,13 @@
         <v>4.5</v>
       </c>
       <c r="T2">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="U2">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2">
         <v>1.58</v>
@@ -1078,13 +1078,13 @@
         <v>11.5</v>
       </c>
       <c r="Y2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB2">
         <v>10</v>
@@ -1093,10 +1093,10 @@
         <v>8.6</v>
       </c>
       <c r="AD2">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE2">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF2">
         <v>18.5</v>
@@ -1126,7 +1126,7 @@
         <v>44</v>
       </c>
       <c r="AO2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AP2">
         <v>7.2</v>
@@ -1183,61 +1183,61 @@
         <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="BI2">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1278,19 +1278,19 @@
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="L3">
         <v>1.01</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N3">
-        <v>2.78</v>
+        <v>3.3</v>
       </c>
       <c r="O3">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P3">
         <v>1.77</v>
@@ -1299,16 +1299,16 @@
         <v>2.04</v>
       </c>
       <c r="R3">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="T3">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V3">
         <v>2.18</v>
@@ -1317,112 +1317,112 @@
         <v>1.18</v>
       </c>
       <c r="X3">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y3">
+        <v>9</v>
+      </c>
+      <c r="Z3">
+        <v>12</v>
+      </c>
+      <c r="AA3">
+        <v>23</v>
+      </c>
+      <c r="AB3">
+        <v>21</v>
+      </c>
+      <c r="AC3">
         <v>10.5</v>
       </c>
-      <c r="Z3">
+      <c r="AD3">
+        <v>12.5</v>
+      </c>
+      <c r="AE3">
+        <v>25</v>
+      </c>
+      <c r="AF3">
+        <v>55</v>
+      </c>
+      <c r="AG3">
+        <v>28</v>
+      </c>
+      <c r="AH3">
+        <v>27</v>
+      </c>
+      <c r="AI3">
+        <v>55</v>
+      </c>
+      <c r="AJ3">
+        <v>200</v>
+      </c>
+      <c r="AK3">
+        <v>110</v>
+      </c>
+      <c r="AL3">
+        <v>120</v>
+      </c>
+      <c r="AM3">
+        <v>180</v>
+      </c>
+      <c r="AN3">
+        <v>160</v>
+      </c>
+      <c r="AO3">
+        <v>16</v>
+      </c>
+      <c r="AP3">
+        <v>9.4</v>
+      </c>
+      <c r="AQ3">
+        <v>5.7</v>
+      </c>
+      <c r="AR3">
+        <v>7.4</v>
+      </c>
+      <c r="AS3">
+        <v>13.5</v>
+      </c>
+      <c r="AT3">
+        <v>12.5</v>
+      </c>
+      <c r="AU3">
+        <v>6.4</v>
+      </c>
+      <c r="AV3">
+        <v>7.6</v>
+      </c>
+      <c r="AW3">
         <v>14.5</v>
       </c>
-      <c r="AA3">
-        <v>28</v>
-      </c>
-      <c r="AB3">
-        <v>25</v>
-      </c>
-      <c r="AC3">
-        <v>12.5</v>
-      </c>
-      <c r="AD3">
-        <v>15</v>
-      </c>
-      <c r="AE3">
-        <v>30</v>
-      </c>
-      <c r="AF3">
-        <v>65</v>
-      </c>
-      <c r="AG3">
-        <v>34</v>
-      </c>
-      <c r="AH3">
-        <v>32</v>
-      </c>
-      <c r="AI3">
-        <v>65</v>
-      </c>
-      <c r="AJ3">
-        <v>1000</v>
-      </c>
-      <c r="AK3">
-        <v>1000</v>
-      </c>
-      <c r="AL3">
-        <v>1000</v>
-      </c>
-      <c r="AM3">
-        <v>1000</v>
-      </c>
-      <c r="AN3">
-        <v>1000</v>
-      </c>
-      <c r="AO3">
-        <v>19</v>
-      </c>
-      <c r="AP3">
-        <v>2.28</v>
-      </c>
-      <c r="AQ3">
-        <v>2.08</v>
-      </c>
-      <c r="AR3">
-        <v>2.2</v>
-      </c>
-      <c r="AS3">
-        <v>2.38</v>
-      </c>
-      <c r="AT3">
-        <v>11.5</v>
-      </c>
-      <c r="AU3">
-        <v>2.16</v>
-      </c>
-      <c r="AV3">
-        <v>2.22</v>
-      </c>
-      <c r="AW3">
-        <v>2.4</v>
-      </c>
       <c r="AX3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="AY3">
-        <v>2.42</v>
+        <v>16.5</v>
       </c>
       <c r="AZ3">
-        <v>2.42</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="BB3">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BC3">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BD3">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE3">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BF3">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1514,10 +1514,10 @@
         <v>3.8</v>
       </c>
       <c r="I4">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J4">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>5.1</v>
@@ -1992,10 +1992,10 @@
         <v>2.8</v>
       </c>
       <c r="G6">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="H6">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="I6">
         <v>2.7</v>
@@ -2004,7 +2004,7 @@
         <v>3.4</v>
       </c>
       <c r="K6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L6">
         <v>0</v>
@@ -2476,10 +2476,10 @@
         <v>1.86</v>
       </c>
       <c r="G8">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H8">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I8">
         <v>4.3</v>
@@ -2506,7 +2506,7 @@
         <v>2.48</v>
       </c>
       <c r="Q8">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>1.68</v>
       </c>
       <c r="R9">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="S9">
         <v>2.78</v>
@@ -2772,7 +2772,7 @@
         <v>21</v>
       </c>
       <c r="Y9">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z9">
         <v>65</v>
@@ -2829,10 +2829,10 @@
         <v>20</v>
       </c>
       <c r="AR9">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT9">
         <v>8.6</v>
@@ -2844,7 +2844,7 @@
         <v>20</v>
       </c>
       <c r="AW9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX9">
         <v>9</v>
@@ -2865,67 +2865,67 @@
         <v>13.5</v>
       </c>
       <c r="BD9">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF9">
         <v>6.6</v>
       </c>
       <c r="BG9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK9">
         <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM9">
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ9">
         <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
         <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU9">
         <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW9">
         <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY9">
         <v>1.01</v>
@@ -2957,23 +2957,23 @@
         <v>129</v>
       </c>
       <c r="F10">
+        <v>8.4</v>
+      </c>
+      <c r="G10">
+        <v>11.5</v>
+      </c>
+      <c r="H10">
+        <v>1.35</v>
+      </c>
+      <c r="I10">
+        <v>1.41</v>
+      </c>
+      <c r="J10">
+        <v>5.7</v>
+      </c>
+      <c r="K10">
         <v>7.2</v>
       </c>
-      <c r="G10">
-        <v>1000</v>
-      </c>
-      <c r="H10">
-        <v>1.27</v>
-      </c>
-      <c r="I10">
-        <v>1.44</v>
-      </c>
-      <c r="J10">
-        <v>4.7</v>
-      </c>
-      <c r="K10">
-        <v>14</v>
-      </c>
       <c r="L10">
         <v>0</v>
       </c>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.62</v>
+        <v>2.98</v>
       </c>
       <c r="Q10">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3199,196 +3199,196 @@
         <v>130</v>
       </c>
       <c r="F11">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="G11">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="H11">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="I11">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="J11">
         <v>5.5</v>
       </c>
       <c r="K11">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="L11">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="O11">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P11">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="Q11">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R11">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="S11">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="T11">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="U11">
-        <v>1.94</v>
+        <v>2.12</v>
       </c>
       <c r="V11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="W11">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="X11">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="Y11">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="Z11">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AA11">
-        <v>470</v>
+        <v>300</v>
       </c>
       <c r="AB11">
+        <v>14.5</v>
+      </c>
+      <c r="AC11">
+        <v>16.5</v>
+      </c>
+      <c r="AD11">
+        <v>40</v>
+      </c>
+      <c r="AE11">
+        <v>130</v>
+      </c>
+      <c r="AF11">
+        <v>13</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>28</v>
+      </c>
+      <c r="AI11">
+        <v>100</v>
+      </c>
+      <c r="AJ11">
         <v>15.5</v>
       </c>
-      <c r="AC11">
-        <v>19.5</v>
-      </c>
-      <c r="AD11">
-        <v>55</v>
-      </c>
-      <c r="AE11">
-        <v>190</v>
-      </c>
-      <c r="AF11">
-        <v>12</v>
-      </c>
-      <c r="AG11">
-        <v>14</v>
-      </c>
-      <c r="AH11">
-        <v>34</v>
-      </c>
-      <c r="AI11">
-        <v>140</v>
-      </c>
-      <c r="AJ11">
-        <v>13</v>
-      </c>
       <c r="AK11">
+        <v>17</v>
+      </c>
+      <c r="AL11">
+        <v>36</v>
+      </c>
+      <c r="AM11">
+        <v>120</v>
+      </c>
+      <c r="AN11">
+        <v>5.5</v>
+      </c>
+      <c r="AO11">
+        <v>130</v>
+      </c>
+      <c r="AP11">
+        <v>22</v>
+      </c>
+      <c r="AQ11">
+        <v>4</v>
+      </c>
+      <c r="AR11">
+        <v>4.2</v>
+      </c>
+      <c r="AS11">
+        <v>4.3</v>
+      </c>
+      <c r="AT11">
+        <v>10</v>
+      </c>
+      <c r="AU11">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV11">
+        <v>3.95</v>
+      </c>
+      <c r="AW11">
+        <v>4.2</v>
+      </c>
+      <c r="AX11">
+        <v>8</v>
+      </c>
+      <c r="AY11">
+        <v>7.8</v>
+      </c>
+      <c r="AZ11">
         <v>16.5</v>
       </c>
-      <c r="AL11">
-        <v>40</v>
-      </c>
-      <c r="AM11">
-        <v>150</v>
-      </c>
-      <c r="AN11">
-        <v>4.4</v>
-      </c>
-      <c r="AO11">
-        <v>200</v>
-      </c>
-      <c r="AP11">
-        <v>4.1</v>
-      </c>
-      <c r="AQ11">
+      <c r="BA11">
         <v>4.2</v>
       </c>
-      <c r="AR11">
-        <v>4.4</v>
-      </c>
-      <c r="AS11">
-        <v>4.5</v>
-      </c>
-      <c r="AT11">
-        <v>10.5</v>
-      </c>
-      <c r="AU11">
-        <v>11.5</v>
-      </c>
-      <c r="AV11">
-        <v>4.2</v>
-      </c>
-      <c r="AW11">
-        <v>4.4</v>
-      </c>
-      <c r="AX11">
-        <v>7.4</v>
-      </c>
-      <c r="AY11">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ11">
-        <v>20</v>
-      </c>
-      <c r="BA11">
-        <v>4.4</v>
-      </c>
       <c r="BB11">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC11">
         <v>10</v>
       </c>
       <c r="BD11">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="BE11">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF11">
-        <v>2.96</v>
+        <v>3.6</v>
       </c>
       <c r="BG11">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BH11">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BI11">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="BJ11">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BK11">
         <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="BM11">
         <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BO11">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="BP11">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="BQ11">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>24</v>
@@ -3397,25 +3397,25 @@
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BU11">
         <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BW11">
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
@@ -3958,7 +3958,7 @@
         <v>2.24</v>
       </c>
       <c r="Q14">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4167,7 +4167,7 @@
         <v>134</v>
       </c>
       <c r="F15">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G15">
         <v>8.4</v>
@@ -4203,13 +4203,13 @@
         <v>1.43</v>
       </c>
       <c r="R15">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="S15">
         <v>2.06</v>
       </c>
       <c r="T15">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U15">
         <v>2.5</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="Y15">
         <v>14.5</v>
@@ -4281,7 +4281,7 @@
         <v>13</v>
       </c>
       <c r="AR15">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AS15">
         <v>12.5</v>
@@ -4311,7 +4311,7 @@
         <v>20</v>
       </c>
       <c r="BB15">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC15">
         <v>50</v>
@@ -4383,7 +4383,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="CA15">
         <v>1.01</v>
@@ -4409,22 +4409,22 @@
         <v>135</v>
       </c>
       <c r="F16">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="G16">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H16">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I16">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J16">
         <v>5.6</v>
       </c>
       <c r="K16">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4451,10 +4451,10 @@
         <v>2.14</v>
       </c>
       <c r="T16">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="U16">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4466,13 +4466,13 @@
         <v>34</v>
       </c>
       <c r="Y16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z16">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AA16">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AB16">
         <v>13</v>
@@ -4481,10 +4481,10 @@
         <v>13</v>
       </c>
       <c r="AD16">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AE16">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF16">
         <v>11.5</v>
@@ -4493,13 +4493,13 @@
         <v>11</v>
       </c>
       <c r="AH16">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI16">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="AJ16">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AK16">
         <v>14</v>
@@ -4508,37 +4508,37 @@
         <v>26</v>
       </c>
       <c r="AM16">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN16">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AO16">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP16">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ16">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="AR16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS16">
         <v>12.5</v>
       </c>
       <c r="AT16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AU16">
         <v>11.5</v>
       </c>
       <c r="AV16">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AW16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX16">
         <v>10</v>
@@ -4547,10 +4547,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ16">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB16">
         <v>12.5</v>
@@ -4562,13 +4562,13 @@
         <v>19</v>
       </c>
       <c r="BE16">
+        <v>12</v>
+      </c>
+      <c r="BF16">
+        <v>4.3</v>
+      </c>
+      <c r="BG16">
         <v>11.5</v>
-      </c>
-      <c r="BF16">
-        <v>4.1</v>
-      </c>
-      <c r="BG16">
-        <v>11</v>
       </c>
       <c r="BH16">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -427,7 +427,7 @@
     <t>MB Rouissat</t>
   </si>
   <si>
-    <t>2026-09-02 03:17:29</t>
+    <t>2026-09-02 05:30:21</t>
   </si>
 </sst>
 </file>
@@ -1039,7 +1039,7 @@
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M2">
         <v>1.11</v>
@@ -1183,10 +1183,10 @@
         <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BI2">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
         <v>13</v>
@@ -1281,7 +1281,7 @@
         <v>4.1</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1371,25 +1371,25 @@
         <v>16</v>
       </c>
       <c r="AP3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AR3">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS3">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
       </c>
       <c r="AU3">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3">
         <v>14.5</v>
@@ -1398,16 +1398,16 @@
         <v>4</v>
       </c>
       <c r="AY3">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AZ3">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BA3">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="BB3">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC3">
         <v>4.2</v>
@@ -1422,64 +1422,64 @@
         <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH3">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ3">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK3">
         <v>1.01</v>
       </c>
       <c r="BL3">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM3">
         <v>1.01</v>
       </c>
       <c r="BN3">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO3">
         <v>1.01</v>
       </c>
       <c r="BP3">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BQ3">
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
       </c>
       <c r="BT3">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU3">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV3">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW3">
         <v>1.01</v>
       </c>
       <c r="BX3">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY3">
         <v>1.01</v>
       </c>
       <c r="BZ3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA3">
         <v>1.01</v>
@@ -1762,7 +1762,7 @@
         <v>2.94</v>
       </c>
       <c r="K5">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L5">
         <v>0</v>
@@ -1780,7 +1780,7 @@
         <v>1.59</v>
       </c>
       <c r="Q5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>2.8</v>
       </c>
       <c r="G6">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="H6">
         <v>2.36</v>
       </c>
       <c r="I6">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="J6">
         <v>3.4</v>
@@ -2019,7 +2019,7 @@
         <v>0</v>
       </c>
       <c r="P6">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q6">
         <v>1.77</v>
@@ -2264,7 +2264,7 @@
         <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2503,10 +2503,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q8">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2748,13 +2748,13 @@
         <v>2.28</v>
       </c>
       <c r="Q9">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R9">
         <v>1.49</v>
       </c>
       <c r="S9">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T9">
         <v>1.86</v>
@@ -2811,7 +2811,7 @@
         <v>16</v>
       </c>
       <c r="AL9">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AM9">
         <v>120</v>
@@ -2829,10 +2829,10 @@
         <v>20</v>
       </c>
       <c r="AR9">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AS9">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT9">
         <v>8.6</v>
@@ -2856,7 +2856,7 @@
         <v>18.5</v>
       </c>
       <c r="BA9">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BB9">
         <v>12.5</v>
@@ -2868,10 +2868,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE9">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF9">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG9">
         <v>10.5</v>
@@ -2895,7 +2895,7 @@
         <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BO9">
         <v>3.4</v>
@@ -2963,16 +2963,16 @@
         <v>11.5</v>
       </c>
       <c r="H10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="I10">
         <v>1.41</v>
       </c>
       <c r="J10">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K10">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2987,10 +2987,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="Q10">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3199,22 +3199,22 @@
         <v>130</v>
       </c>
       <c r="F11">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="G11">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H11">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="J11">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K11">
-        <v>7.2</v>
+        <v>5.9</v>
       </c>
       <c r="L11">
         <v>1.21</v>
@@ -3229,16 +3229,16 @@
         <v>1.16</v>
       </c>
       <c r="P11">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q11">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="R11">
         <v>1.69</v>
       </c>
       <c r="S11">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="T11">
         <v>1.75</v>
@@ -3247,127 +3247,127 @@
         <v>2.12</v>
       </c>
       <c r="V11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W11">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="X11">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y11">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AA11">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AB11">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC11">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD11">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AE11">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF11">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AI11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ11">
         <v>15.5</v>
       </c>
       <c r="AK11">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL11">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AM11">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN11">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AO11">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP11">
-        <v>22</v>
+        <v>5.4</v>
       </c>
       <c r="AQ11">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="AR11">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="AS11">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT11">
         <v>10</v>
       </c>
       <c r="AU11">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AV11">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="AW11">
+        <v>6.2</v>
+      </c>
+      <c r="AX11">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY11">
+        <v>9</v>
+      </c>
+      <c r="AZ11">
+        <v>18.5</v>
+      </c>
+      <c r="BA11">
+        <v>6</v>
+      </c>
+      <c r="BB11">
+        <v>11</v>
+      </c>
+      <c r="BC11">
+        <v>12</v>
+      </c>
+      <c r="BD11">
+        <v>5.4</v>
+      </c>
+      <c r="BE11">
+        <v>6.2</v>
+      </c>
+      <c r="BF11">
         <v>4.2</v>
       </c>
-      <c r="AX11">
-        <v>8</v>
-      </c>
-      <c r="AY11">
-        <v>7.8</v>
-      </c>
-      <c r="AZ11">
-        <v>16.5</v>
-      </c>
-      <c r="BA11">
-        <v>4.2</v>
-      </c>
-      <c r="BB11">
-        <v>9.4</v>
-      </c>
-      <c r="BC11">
-        <v>10</v>
-      </c>
-      <c r="BD11">
-        <v>20</v>
-      </c>
-      <c r="BE11">
-        <v>4.2</v>
-      </c>
-      <c r="BF11">
-        <v>3.6</v>
-      </c>
       <c r="BG11">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH11">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BI11">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BJ11">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK11">
         <v>1.01</v>
@@ -3385,10 +3385,10 @@
         <v>3.3</v>
       </c>
       <c r="BP11">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BQ11">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BR11">
         <v>24</v>
@@ -3397,7 +3397,7 @@
         <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BU11">
         <v>1.01</v>
@@ -3409,13 +3409,13 @@
         <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="BY11">
         <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="CA11">
         <v>1.01</v>
@@ -3925,7 +3925,7 @@
         <v>133</v>
       </c>
       <c r="F14">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G14">
         <v>2.72</v>
@@ -4167,22 +4167,22 @@
         <v>134</v>
       </c>
       <c r="F15">
+        <v>7.8</v>
+      </c>
+      <c r="G15">
         <v>8</v>
       </c>
-      <c r="G15">
-        <v>8.4</v>
-      </c>
       <c r="H15">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="I15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J15">
         <v>5.5</v>
       </c>
       <c r="K15">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L15">
         <v>0</v>
@@ -4191,7 +4191,7 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="O15">
         <v>1.14</v>
@@ -4203,7 +4203,7 @@
         <v>1.43</v>
       </c>
       <c r="R15">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="S15">
         <v>2.06</v>
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="X15">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="Y15">
         <v>14.5</v>
@@ -4281,7 +4281,7 @@
         <v>13</v>
       </c>
       <c r="AR15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AS15">
         <v>12.5</v>
@@ -4299,7 +4299,7 @@
         <v>11.5</v>
       </c>
       <c r="AX15">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AY15">
         <v>26</v>
@@ -4311,19 +4311,19 @@
         <v>20</v>
       </c>
       <c r="BB15">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC15">
+        <v>55</v>
+      </c>
+      <c r="BD15">
+        <v>55</v>
+      </c>
+      <c r="BE15">
         <v>50</v>
       </c>
-      <c r="BD15">
-        <v>50</v>
-      </c>
-      <c r="BE15">
+      <c r="BF15">
         <v>48</v>
-      </c>
-      <c r="BF15">
-        <v>46</v>
       </c>
       <c r="BG15">
         <v>4.1</v>
@@ -4371,7 +4371,7 @@
         <v>3.55</v>
       </c>
       <c r="BV15">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BW15">
         <v>1.01</v>
@@ -4415,16 +4415,16 @@
         <v>1.45</v>
       </c>
       <c r="H16">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I16">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J16">
+        <v>5.5</v>
+      </c>
+      <c r="K16">
         <v>5.6</v>
-      </c>
-      <c r="K16">
-        <v>5.7</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -4484,13 +4484,13 @@
         <v>29</v>
       </c>
       <c r="AE16">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AF16">
         <v>11.5</v>
       </c>
       <c r="AG16">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH16">
         <v>21</v>
@@ -4499,13 +4499,13 @@
         <v>70</v>
       </c>
       <c r="AJ16">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AK16">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AL16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AM16">
         <v>95</v>
@@ -4514,34 +4514,34 @@
         <v>4.6</v>
       </c>
       <c r="AO16">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AP16">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="AQ16">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AR16">
-        <v>11.5</v>
+        <v>55</v>
       </c>
       <c r="AS16">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AU16">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV16">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AW16">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AX16">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY16">
         <v>9.6</v>
@@ -4550,7 +4550,7 @@
         <v>19</v>
       </c>
       <c r="BA16">
-        <v>11.5</v>
+        <v>46</v>
       </c>
       <c r="BB16">
         <v>12.5</v>
@@ -4559,16 +4559,16 @@
         <v>12.5</v>
       </c>
       <c r="BD16">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BE16">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="BF16">
         <v>4.3</v>
       </c>
       <c r="BG16">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4666,7 +4666,7 @@
         <v>1.08</v>
       </c>
       <c r="K17">
-        <v>1000</v>
+        <v>470</v>
       </c>
       <c r="L17">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="151">
   <si>
     <t>League</t>
   </si>
@@ -262,6 +262,12 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Ukrainian Premier League</t>
+  </si>
+  <si>
+    <t>South Korean K2 League</t>
+  </si>
+  <si>
     <t>Qatari Stars League</t>
   </si>
   <si>
@@ -301,9 +307,18 @@
     <t>01:00:00</t>
   </si>
   <si>
+    <t>10:00:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
     <t>16:00:00</t>
   </si>
   <si>
@@ -337,9 +352,21 @@
     <t>Deportivo Pereira</t>
   </si>
   <si>
+    <t>Chernomorets Odesa</t>
+  </si>
+  <si>
+    <t>Cheongju FC</t>
+  </si>
+  <si>
+    <t>Paju Citizen</t>
+  </si>
+  <si>
     <t>Al Shamal</t>
   </si>
   <si>
+    <t>Polissya Zhytomyr</t>
+  </si>
+  <si>
     <t>Septemvri</t>
   </si>
   <si>
@@ -385,9 +412,21 @@
     <t>Ind Medellin</t>
   </si>
   <si>
+    <t>Livyi Bereg Kyiv</t>
+  </si>
+  <si>
+    <t>Seoul E-Land FC</t>
+  </si>
+  <si>
+    <t>Daegu Fc</t>
+  </si>
+  <si>
     <t>Al Shahaniya</t>
   </si>
   <si>
+    <t>FK Kudrivka</t>
+  </si>
+  <si>
     <t>Botev Vratsa</t>
   </si>
   <si>
@@ -427,7 +466,7 @@
     <t>MB Rouissat</t>
   </si>
   <si>
-    <t>2026-09-02 05:30:21</t>
+    <t>2026-09-02 07:42:26</t>
   </si>
 </sst>
 </file>
@@ -759,7 +798,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB17"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1009,22 +1048,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="F2">
         <v>2.44</v>
       </c>
       <c r="G2">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="H2">
         <v>3.15</v>
@@ -1039,28 +1078,28 @@
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="M2">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="O2">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="P2">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
-        <v>2.36</v>
+        <v>1.71</v>
       </c>
       <c r="R2">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S2">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="T2">
         <v>1.96</v>
@@ -1072,7 +1111,7 @@
         <v>1.38</v>
       </c>
       <c r="W2">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X2">
         <v>11.5</v>
@@ -1243,7 +1282,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1251,16 +1290,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E3" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F3">
         <v>5.3</v>
@@ -1269,7 +1308,7 @@
         <v>6.4</v>
       </c>
       <c r="H3">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="I3">
         <v>1.84</v>
@@ -1278,10 +1317,10 @@
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1293,10 +1332,10 @@
         <v>1.36</v>
       </c>
       <c r="P3">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q3">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R3">
         <v>1.29</v>
@@ -1305,10 +1344,10 @@
         <v>3.7</v>
       </c>
       <c r="T3">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="U3">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V3">
         <v>2.18</v>
@@ -1371,7 +1410,7 @@
         <v>16</v>
       </c>
       <c r="AP3">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3">
         <v>6.4</v>
@@ -1392,7 +1431,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AW3">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="AX3">
         <v>4</v>
@@ -1485,7 +1524,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1493,241 +1532,241 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E4" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="F4">
-        <v>1.85</v>
+        <v>1.08</v>
       </c>
       <c r="G4">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="H4">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="J4">
-        <v>3.8</v>
+        <v>1.08</v>
       </c>
       <c r="K4">
-        <v>5.1</v>
+        <v>420</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4">
-        <v>2.24</v>
+        <v>1.24</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.02</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1735,518 +1774,518 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E5" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="F5">
-        <v>2.62</v>
+        <v>4.2</v>
       </c>
       <c r="G5">
-        <v>2.96</v>
+        <v>5.7</v>
       </c>
       <c r="H5">
-        <v>2.84</v>
+        <v>1.78</v>
       </c>
       <c r="I5">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="J5">
-        <v>2.94</v>
+        <v>3.85</v>
       </c>
       <c r="K5">
-        <v>3.45</v>
+        <v>5</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P5">
-        <v>1.59</v>
+        <v>1.96</v>
       </c>
       <c r="Q5">
-        <v>2.34</v>
+        <v>1.61</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:80">
       <c r="A6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E6" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="F6">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="G6">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="H6">
-        <v>2.36</v>
+        <v>1.59</v>
       </c>
       <c r="I6">
-        <v>2.88</v>
+        <v>1.72</v>
       </c>
       <c r="J6">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="K6">
-        <v>4.6</v>
+        <v>5.7</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q6">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:80">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E7" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="F7">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="G7">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="H7">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="I7">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="J7">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="K7">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
         <v>0</v>
@@ -2261,10 +2300,10 @@
         <v>0</v>
       </c>
       <c r="P7">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="Q7">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="R7">
         <v>0</v>
@@ -2453,42 +2492,42 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E8" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="F8">
-        <v>1.86</v>
+        <v>1.1</v>
       </c>
       <c r="G8">
-        <v>1.94</v>
+        <v>7.8</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>1.16</v>
       </c>
       <c r="I8">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J8">
-        <v>4.1</v>
+        <v>1.14</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>350</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2503,10 +2542,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -2695,72 +2734,72 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="F9">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="G9">
-        <v>1.58</v>
+        <v>2.96</v>
       </c>
       <c r="H9">
-        <v>6.4</v>
+        <v>2.82</v>
       </c>
       <c r="I9">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="J9">
-        <v>4.6</v>
+        <v>2.94</v>
       </c>
       <c r="K9">
-        <v>4.9</v>
+        <v>3.45</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N9">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>2.28</v>
+        <v>1.59</v>
       </c>
       <c r="Q9">
-        <v>1.67</v>
+        <v>2.34</v>
       </c>
       <c r="R9">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V9">
         <v>0</v>
@@ -2769,166 +2808,166 @@
         <v>0</v>
       </c>
       <c r="X9">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AA9">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AB9">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD9">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AK9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL9">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN9">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AO9">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AP9">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR9">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AS9">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AT9">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU9">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AV9">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW9">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AX9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY9">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ9">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA9">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BB9">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC9">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BD9">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BE9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BF9">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BG9">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BH9">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI9">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BJ9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL9">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN9">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO9">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BP9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR9">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT9">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV9">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX9">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ9">
         <v>0</v>
@@ -2937,42 +2976,42 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="F10">
-        <v>8.4</v>
+        <v>2.8</v>
       </c>
       <c r="G10">
-        <v>11.5</v>
+        <v>3.55</v>
       </c>
       <c r="H10">
-        <v>1.34</v>
+        <v>2.36</v>
       </c>
       <c r="I10">
-        <v>1.41</v>
+        <v>2.7</v>
       </c>
       <c r="J10">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="K10">
-        <v>7.6</v>
+        <v>4.6</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -2987,10 +3026,10 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>3.05</v>
+        <v>2.02</v>
       </c>
       <c r="Q10">
-        <v>1.34</v>
+        <v>1.78</v>
       </c>
       <c r="R10">
         <v>0</v>
@@ -3179,284 +3218,284 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D11" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E11" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="F11">
-        <v>1.39</v>
+        <v>2.3</v>
       </c>
       <c r="G11">
-        <v>1.48</v>
+        <v>2.62</v>
       </c>
       <c r="H11">
-        <v>7.2</v>
+        <v>2.84</v>
       </c>
       <c r="I11">
-        <v>10.5</v>
+        <v>3.55</v>
       </c>
       <c r="J11">
-        <v>5.1</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>5.9</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P11">
-        <v>2.78</v>
+        <v>2.1</v>
       </c>
       <c r="Q11">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="R11">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="S11">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T11">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U11">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V11">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W11">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="Y11">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z11">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AC11">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AD11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AE11">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AF11">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH11">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AK11">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN11">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AQ11">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AR11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AU11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AV11">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AW11">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AX11">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY11">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ11">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB11">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BC11">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD11">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BE11">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BF11">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BG11">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BH11">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BI11">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="BJ11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL11">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN11">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO11">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BP11">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BQ11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BR11">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT11">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BU11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV11">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BW11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX11">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ11">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CA11">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E12" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="F12">
-        <v>2.12</v>
+        <v>1.87</v>
       </c>
       <c r="G12">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="H12">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
         <v>4.2</v>
       </c>
       <c r="J12">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="K12">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3471,10 +3510,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.71</v>
+        <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>2.1</v>
+        <v>1.51</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3663,240 +3702,240 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13">
+        <v>1.55</v>
+      </c>
+      <c r="G13">
+        <v>1.57</v>
+      </c>
+      <c r="H13">
+        <v>6.6</v>
+      </c>
+      <c r="I13">
+        <v>7.2</v>
+      </c>
+      <c r="J13">
+        <v>4.6</v>
+      </c>
+      <c r="K13">
+        <v>4.9</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1.05</v>
+      </c>
+      <c r="N13">
+        <v>4.7</v>
+      </c>
+      <c r="O13">
+        <v>1.24</v>
+      </c>
+      <c r="P13">
+        <v>2.28</v>
+      </c>
+      <c r="Q13">
+        <v>1.67</v>
+      </c>
+      <c r="R13">
+        <v>1.51</v>
+      </c>
+      <c r="S13">
+        <v>2.74</v>
+      </c>
+      <c r="T13">
+        <v>1.86</v>
+      </c>
+      <c r="U13">
+        <v>2.08</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>21</v>
+      </c>
+      <c r="Y13">
+        <v>26</v>
+      </c>
+      <c r="Z13">
+        <v>65</v>
+      </c>
+      <c r="AA13">
+        <v>210</v>
+      </c>
+      <c r="AB13">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC13">
+        <v>11</v>
+      </c>
+      <c r="AD13">
+        <v>25</v>
+      </c>
+      <c r="AE13">
         <v>100</v>
       </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>2.24</v>
-      </c>
-      <c r="Q13">
-        <v>1.01</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
       <c r="AF13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH13">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL13">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM13">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN13">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AO13">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP13">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AU13">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV13">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AW13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AX13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY13">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ13">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BB13">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC13">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF13">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BG13">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BI13">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BJ13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BK13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="BM13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BO13">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BP13">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BQ13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR13">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BS13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BU13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BW13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX13">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BY13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3905,42 +3944,42 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D14" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E14" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="F14">
-        <v>2.46</v>
+        <v>8.4</v>
       </c>
       <c r="G14">
-        <v>2.72</v>
+        <v>11.5</v>
       </c>
       <c r="H14">
-        <v>2.7</v>
+        <v>1.34</v>
       </c>
       <c r="I14">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>5.8</v>
       </c>
       <c r="K14">
-        <v>4.6</v>
+        <v>7.6</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3955,10 +3994,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
       <c r="Q14">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4147,314 +4186,314 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E15" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F15">
-        <v>7.8</v>
+        <v>1.37</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>1.44</v>
       </c>
       <c r="H15">
-        <v>1.44</v>
+        <v>7.4</v>
       </c>
       <c r="I15">
-        <v>1.45</v>
+        <v>10.5</v>
       </c>
       <c r="J15">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="K15">
+        <v>6.2</v>
+      </c>
+      <c r="L15">
+        <v>1.21</v>
+      </c>
+      <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>6</v>
+      </c>
+      <c r="O15">
+        <v>1.16</v>
+      </c>
+      <c r="P15">
+        <v>2.76</v>
+      </c>
+      <c r="Q15">
+        <v>1.48</v>
+      </c>
+      <c r="R15">
+        <v>1.7</v>
+      </c>
+      <c r="S15">
+        <v>2.2</v>
+      </c>
+      <c r="T15">
+        <v>1.75</v>
+      </c>
+      <c r="U15">
+        <v>2.12</v>
+      </c>
+      <c r="V15">
+        <v>1.11</v>
+      </c>
+      <c r="W15">
+        <v>3.25</v>
+      </c>
+      <c r="X15">
+        <v>32</v>
+      </c>
+      <c r="Y15">
+        <v>40</v>
+      </c>
+      <c r="Z15">
+        <v>85</v>
+      </c>
+      <c r="AA15">
+        <v>260</v>
+      </c>
+      <c r="AB15">
+        <v>12.5</v>
+      </c>
+      <c r="AC15">
+        <v>14</v>
+      </c>
+      <c r="AD15">
+        <v>32</v>
+      </c>
+      <c r="AE15">
+        <v>120</v>
+      </c>
+      <c r="AF15">
+        <v>11</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>23</v>
+      </c>
+      <c r="AI15">
+        <v>95</v>
+      </c>
+      <c r="AJ15">
+        <v>15.5</v>
+      </c>
+      <c r="AK15">
+        <v>14.5</v>
+      </c>
+      <c r="AL15">
+        <v>32</v>
+      </c>
+      <c r="AM15">
+        <v>110</v>
+      </c>
+      <c r="AN15">
+        <v>5.4</v>
+      </c>
+      <c r="AO15">
+        <v>110</v>
+      </c>
+      <c r="AP15">
+        <v>5.8</v>
+      </c>
+      <c r="AQ15">
+        <v>6</v>
+      </c>
+      <c r="AR15">
+        <v>6.4</v>
+      </c>
+      <c r="AS15">
+        <v>6.8</v>
+      </c>
+      <c r="AT15">
+        <v>10</v>
+      </c>
+      <c r="AU15">
+        <v>11</v>
+      </c>
+      <c r="AV15">
+        <v>5.8</v>
+      </c>
+      <c r="AW15">
+        <v>6.6</v>
+      </c>
+      <c r="AX15">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY15">
+        <v>9</v>
+      </c>
+      <c r="AZ15">
+        <v>18.5</v>
+      </c>
+      <c r="BA15">
+        <v>6.6</v>
+      </c>
+      <c r="BB15">
+        <v>11</v>
+      </c>
+      <c r="BC15">
+        <v>12</v>
+      </c>
+      <c r="BD15">
         <v>5.7</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>1.03</v>
-      </c>
-      <c r="N15">
-        <v>7.4</v>
-      </c>
-      <c r="O15">
-        <v>1.14</v>
-      </c>
-      <c r="P15">
-        <v>3.2</v>
-      </c>
-      <c r="Q15">
-        <v>1.43</v>
-      </c>
-      <c r="R15">
-        <v>1.86</v>
-      </c>
-      <c r="S15">
-        <v>2.06</v>
-      </c>
-      <c r="T15">
-        <v>1.61</v>
-      </c>
-      <c r="U15">
-        <v>2.5</v>
-      </c>
-      <c r="V15">
-        <v>0</v>
-      </c>
-      <c r="W15">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>36</v>
-      </c>
-      <c r="Y15">
+      <c r="BE15">
+        <v>6.6</v>
+      </c>
+      <c r="BF15">
+        <v>4</v>
+      </c>
+      <c r="BG15">
+        <v>6.6</v>
+      </c>
+      <c r="BH15">
+        <v>5.7</v>
+      </c>
+      <c r="BI15">
+        <v>3.75</v>
+      </c>
+      <c r="BJ15">
+        <v>12.5</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>120</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>5</v>
+      </c>
+      <c r="BO15">
+        <v>3.3</v>
+      </c>
+      <c r="BP15">
+        <v>9.6</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>24</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
         <v>14.5</v>
       </c>
-      <c r="Z15">
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>75</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>65</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
         <v>12.5</v>
       </c>
-      <c r="AA15">
-        <v>14.5</v>
-      </c>
-      <c r="AB15">
-        <v>42</v>
-      </c>
-      <c r="AC15">
-        <v>13.5</v>
-      </c>
-      <c r="AD15">
-        <v>10.5</v>
-      </c>
-      <c r="AE15">
-        <v>13.5</v>
-      </c>
-      <c r="AF15">
-        <v>110</v>
-      </c>
-      <c r="AG15">
-        <v>32</v>
-      </c>
-      <c r="AH15">
-        <v>19.5</v>
-      </c>
-      <c r="AI15">
-        <v>24</v>
-      </c>
-      <c r="AJ15">
-        <v>1000</v>
-      </c>
-      <c r="AK15">
-        <v>120</v>
-      </c>
-      <c r="AL15">
-        <v>80</v>
-      </c>
-      <c r="AM15">
-        <v>85</v>
-      </c>
-      <c r="AN15">
-        <v>85</v>
-      </c>
-      <c r="AO15">
-        <v>4.4</v>
-      </c>
-      <c r="AP15">
-        <v>30</v>
-      </c>
-      <c r="AQ15">
-        <v>13</v>
-      </c>
-      <c r="AR15">
-        <v>10.5</v>
-      </c>
-      <c r="AS15">
-        <v>12.5</v>
-      </c>
-      <c r="AT15">
-        <v>34</v>
-      </c>
-      <c r="AU15">
-        <v>12</v>
-      </c>
-      <c r="AV15">
-        <v>9.4</v>
-      </c>
-      <c r="AW15">
-        <v>11.5</v>
-      </c>
-      <c r="AX15">
-        <v>60</v>
-      </c>
-      <c r="AY15">
-        <v>26</v>
-      </c>
-      <c r="AZ15">
-        <v>17</v>
-      </c>
-      <c r="BA15">
-        <v>20</v>
-      </c>
-      <c r="BB15">
-        <v>14.5</v>
-      </c>
-      <c r="BC15">
-        <v>55</v>
-      </c>
-      <c r="BD15">
-        <v>55</v>
-      </c>
-      <c r="BE15">
-        <v>50</v>
-      </c>
-      <c r="BF15">
-        <v>48</v>
-      </c>
-      <c r="BG15">
-        <v>4.1</v>
-      </c>
-      <c r="BH15">
-        <v>6.4</v>
-      </c>
-      <c r="BI15">
-        <v>4.1</v>
-      </c>
-      <c r="BJ15">
-        <v>12</v>
-      </c>
-      <c r="BK15">
-        <v>1.01</v>
-      </c>
-      <c r="BL15">
-        <v>95</v>
-      </c>
-      <c r="BM15">
-        <v>1.01</v>
-      </c>
-      <c r="BN15">
-        <v>13.5</v>
-      </c>
-      <c r="BO15">
-        <v>1.01</v>
-      </c>
-      <c r="BP15">
-        <v>60</v>
-      </c>
-      <c r="BQ15">
-        <v>1.01</v>
-      </c>
-      <c r="BR15">
-        <v>55</v>
-      </c>
-      <c r="BS15">
-        <v>1.01</v>
-      </c>
-      <c r="BT15">
-        <v>5.4</v>
-      </c>
-      <c r="BU15">
-        <v>3.55</v>
-      </c>
-      <c r="BV15">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BW15">
-        <v>1.01</v>
-      </c>
-      <c r="BX15">
-        <v>21</v>
-      </c>
-      <c r="BY15">
-        <v>1.01</v>
-      </c>
-      <c r="BZ15">
-        <v>11</v>
-      </c>
       <c r="CA15">
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="F16">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="G16">
-        <v>1.45</v>
+        <v>2.4</v>
       </c>
       <c r="H16">
-        <v>7.6</v>
+        <v>3.5</v>
       </c>
       <c r="I16">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="J16">
-        <v>5.5</v>
+        <v>3.15</v>
       </c>
       <c r="K16">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="Q16">
-        <v>1.47</v>
+        <v>2.08</v>
       </c>
       <c r="R16">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V16">
         <v>0</v>
@@ -4463,166 +4502,166 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BG16">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ16">
         <v>0</v>
@@ -4631,249 +4670,1217 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" t="s">
+        <v>94</v>
+      </c>
+      <c r="C17" t="s">
+        <v>105</v>
+      </c>
+      <c r="D17" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" t="s">
+        <v>145</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>2.24</v>
+      </c>
+      <c r="Q17">
+        <v>1.01</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>0</v>
+      </c>
+      <c r="AE17">
+        <v>0</v>
+      </c>
+      <c r="AF17">
+        <v>0</v>
+      </c>
+      <c r="AG17">
+        <v>0</v>
+      </c>
+      <c r="AH17">
+        <v>0</v>
+      </c>
+      <c r="AI17">
+        <v>0</v>
+      </c>
+      <c r="AJ17">
+        <v>0</v>
+      </c>
+      <c r="AK17">
+        <v>0</v>
+      </c>
+      <c r="AL17">
+        <v>0</v>
+      </c>
+      <c r="AM17">
+        <v>0</v>
+      </c>
+      <c r="AN17">
+        <v>0</v>
+      </c>
+      <c r="AO17">
+        <v>0</v>
+      </c>
+      <c r="AP17">
+        <v>0</v>
+      </c>
+      <c r="AQ17">
+        <v>0</v>
+      </c>
+      <c r="AR17">
+        <v>0</v>
+      </c>
+      <c r="AS17">
+        <v>0</v>
+      </c>
+      <c r="AT17">
+        <v>0</v>
+      </c>
+      <c r="AU17">
+        <v>0</v>
+      </c>
+      <c r="AV17">
+        <v>0</v>
+      </c>
+      <c r="AW17">
+        <v>0</v>
+      </c>
+      <c r="AX17">
+        <v>0</v>
+      </c>
+      <c r="AY17">
+        <v>0</v>
+      </c>
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+      <c r="BA17">
+        <v>0</v>
+      </c>
+      <c r="BB17">
+        <v>0</v>
+      </c>
+      <c r="BC17">
+        <v>0</v>
+      </c>
+      <c r="BD17">
+        <v>0</v>
+      </c>
+      <c r="BE17">
+        <v>0</v>
+      </c>
+      <c r="BF17">
+        <v>0</v>
+      </c>
+      <c r="BG17">
+        <v>0</v>
+      </c>
+      <c r="BH17">
+        <v>0</v>
+      </c>
+      <c r="BI17">
+        <v>0</v>
+      </c>
+      <c r="BJ17">
+        <v>0</v>
+      </c>
+      <c r="BK17">
+        <v>0</v>
+      </c>
+      <c r="BL17">
+        <v>0</v>
+      </c>
+      <c r="BM17">
+        <v>0</v>
+      </c>
+      <c r="BN17">
+        <v>0</v>
+      </c>
+      <c r="BO17">
+        <v>0</v>
+      </c>
+      <c r="BP17">
+        <v>0</v>
+      </c>
+      <c r="BQ17">
+        <v>0</v>
+      </c>
+      <c r="BR17">
+        <v>0</v>
+      </c>
+      <c r="BS17">
+        <v>0</v>
+      </c>
+      <c r="BT17">
+        <v>0</v>
+      </c>
+      <c r="BU17">
+        <v>0</v>
+      </c>
+      <c r="BV17">
+        <v>0</v>
+      </c>
+      <c r="BW17">
+        <v>0</v>
+      </c>
+      <c r="BX17">
+        <v>0</v>
+      </c>
+      <c r="BY17">
+        <v>0</v>
+      </c>
+      <c r="BZ17">
+        <v>0</v>
+      </c>
+      <c r="CA17">
+        <v>0</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
         <v>91</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C18" t="s">
+        <v>106</v>
+      </c>
+      <c r="D18" t="s">
+        <v>126</v>
+      </c>
+      <c r="E18" t="s">
+        <v>146</v>
+      </c>
+      <c r="F18">
+        <v>2.42</v>
+      </c>
+      <c r="G18">
+        <v>2.72</v>
+      </c>
+      <c r="H18">
+        <v>2.7</v>
+      </c>
+      <c r="I18">
+        <v>3.2</v>
+      </c>
+      <c r="J18">
+        <v>3.65</v>
+      </c>
+      <c r="K18">
+        <v>4.6</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>1.25</v>
+      </c>
+      <c r="Q18">
+        <v>1.01</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>0</v>
+      </c>
+      <c r="AE18">
+        <v>0</v>
+      </c>
+      <c r="AF18">
+        <v>0</v>
+      </c>
+      <c r="AG18">
+        <v>0</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
+      </c>
+      <c r="AI18">
+        <v>0</v>
+      </c>
+      <c r="AJ18">
+        <v>0</v>
+      </c>
+      <c r="AK18">
+        <v>0</v>
+      </c>
+      <c r="AL18">
+        <v>0</v>
+      </c>
+      <c r="AM18">
+        <v>0</v>
+      </c>
+      <c r="AN18">
+        <v>0</v>
+      </c>
+      <c r="AO18">
+        <v>0</v>
+      </c>
+      <c r="AP18">
+        <v>0</v>
+      </c>
+      <c r="AQ18">
+        <v>0</v>
+      </c>
+      <c r="AR18">
+        <v>0</v>
+      </c>
+      <c r="AS18">
+        <v>0</v>
+      </c>
+      <c r="AT18">
+        <v>0</v>
+      </c>
+      <c r="AU18">
+        <v>0</v>
+      </c>
+      <c r="AV18">
+        <v>0</v>
+      </c>
+      <c r="AW18">
+        <v>0</v>
+      </c>
+      <c r="AX18">
+        <v>0</v>
+      </c>
+      <c r="AY18">
+        <v>0</v>
+      </c>
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+      <c r="BA18">
+        <v>0</v>
+      </c>
+      <c r="BB18">
+        <v>0</v>
+      </c>
+      <c r="BC18">
+        <v>0</v>
+      </c>
+      <c r="BD18">
+        <v>0</v>
+      </c>
+      <c r="BE18">
+        <v>0</v>
+      </c>
+      <c r="BF18">
+        <v>0</v>
+      </c>
+      <c r="BG18">
+        <v>0</v>
+      </c>
+      <c r="BH18">
+        <v>0</v>
+      </c>
+      <c r="BI18">
+        <v>0</v>
+      </c>
+      <c r="BJ18">
+        <v>0</v>
+      </c>
+      <c r="BK18">
+        <v>0</v>
+      </c>
+      <c r="BL18">
+        <v>0</v>
+      </c>
+      <c r="BM18">
+        <v>0</v>
+      </c>
+      <c r="BN18">
+        <v>0</v>
+      </c>
+      <c r="BO18">
+        <v>0</v>
+      </c>
+      <c r="BP18">
+        <v>0</v>
+      </c>
+      <c r="BQ18">
+        <v>0</v>
+      </c>
+      <c r="BR18">
+        <v>0</v>
+      </c>
+      <c r="BS18">
+        <v>0</v>
+      </c>
+      <c r="BT18">
+        <v>0</v>
+      </c>
+      <c r="BU18">
+        <v>0</v>
+      </c>
+      <c r="BV18">
+        <v>0</v>
+      </c>
+      <c r="BW18">
+        <v>0</v>
+      </c>
+      <c r="BX18">
+        <v>0</v>
+      </c>
+      <c r="BY18">
+        <v>0</v>
+      </c>
+      <c r="BZ18">
+        <v>0</v>
+      </c>
+      <c r="CA18">
+        <v>0</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
         <v>92</v>
       </c>
-      <c r="C17" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>136</v>
-      </c>
-      <c r="F17">
+      <c r="B19" t="s">
+        <v>94</v>
+      </c>
+      <c r="C19" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" t="s">
+        <v>127</v>
+      </c>
+      <c r="E19" t="s">
+        <v>147</v>
+      </c>
+      <c r="F19">
+        <v>7.8</v>
+      </c>
+      <c r="G19">
+        <v>8</v>
+      </c>
+      <c r="H19">
+        <v>1.43</v>
+      </c>
+      <c r="I19">
+        <v>1.44</v>
+      </c>
+      <c r="J19">
+        <v>5.7</v>
+      </c>
+      <c r="K19">
+        <v>5.8</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>1.03</v>
+      </c>
+      <c r="N19">
+        <v>7.4</v>
+      </c>
+      <c r="O19">
+        <v>1.13</v>
+      </c>
+      <c r="P19">
+        <v>3.25</v>
+      </c>
+      <c r="Q19">
+        <v>1.43</v>
+      </c>
+      <c r="R19">
+        <v>1.86</v>
+      </c>
+      <c r="S19">
+        <v>2.04</v>
+      </c>
+      <c r="T19">
+        <v>1.62</v>
+      </c>
+      <c r="U19">
+        <v>2.5</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>38</v>
+      </c>
+      <c r="Y19">
+        <v>14.5</v>
+      </c>
+      <c r="Z19">
+        <v>12</v>
+      </c>
+      <c r="AA19">
+        <v>14</v>
+      </c>
+      <c r="AB19">
+        <v>44</v>
+      </c>
+      <c r="AC19">
+        <v>13.5</v>
+      </c>
+      <c r="AD19">
+        <v>10.5</v>
+      </c>
+      <c r="AE19">
+        <v>13.5</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>32</v>
+      </c>
+      <c r="AH19">
+        <v>19.5</v>
+      </c>
+      <c r="AI19">
+        <v>24</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>110</v>
+      </c>
+      <c r="AL19">
+        <v>85</v>
+      </c>
+      <c r="AM19">
+        <v>85</v>
+      </c>
+      <c r="AN19">
+        <v>75</v>
+      </c>
+      <c r="AO19">
+        <v>4.3</v>
+      </c>
+      <c r="AP19">
+        <v>30</v>
+      </c>
+      <c r="AQ19">
+        <v>13</v>
+      </c>
+      <c r="AR19">
+        <v>11.5</v>
+      </c>
+      <c r="AS19">
+        <v>12.5</v>
+      </c>
+      <c r="AT19">
+        <v>34</v>
+      </c>
+      <c r="AU19">
+        <v>12</v>
+      </c>
+      <c r="AV19">
+        <v>9.6</v>
+      </c>
+      <c r="AW19">
+        <v>11.5</v>
+      </c>
+      <c r="AX19">
+        <v>55</v>
+      </c>
+      <c r="AY19">
+        <v>26</v>
+      </c>
+      <c r="AZ19">
+        <v>17.5</v>
+      </c>
+      <c r="BA19">
+        <v>20</v>
+      </c>
+      <c r="BB19">
+        <v>80</v>
+      </c>
+      <c r="BC19">
+        <v>55</v>
+      </c>
+      <c r="BD19">
+        <v>48</v>
+      </c>
+      <c r="BE19">
+        <v>50</v>
+      </c>
+      <c r="BF19">
+        <v>46</v>
+      </c>
+      <c r="BG19">
+        <v>4</v>
+      </c>
+      <c r="BH19">
+        <v>6.4</v>
+      </c>
+      <c r="BI19">
+        <v>4.1</v>
+      </c>
+      <c r="BJ19">
+        <v>12</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>95</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>13.5</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>60</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>55</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>5.4</v>
+      </c>
+      <c r="BU19">
+        <v>3.55</v>
+      </c>
+      <c r="BV19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>21</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>11</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" t="s">
+        <v>94</v>
+      </c>
+      <c r="C20" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s">
+        <v>128</v>
+      </c>
+      <c r="E20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F20">
+        <v>1.43</v>
+      </c>
+      <c r="G20">
+        <v>1.44</v>
+      </c>
+      <c r="H20">
+        <v>7.6</v>
+      </c>
+      <c r="I20">
+        <v>8</v>
+      </c>
+      <c r="J20">
+        <v>5.6</v>
+      </c>
+      <c r="K20">
+        <v>5.7</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>1.02</v>
+      </c>
+      <c r="N20">
+        <v>6.6</v>
+      </c>
+      <c r="O20">
+        <v>1.15</v>
+      </c>
+      <c r="P20">
+        <v>3</v>
+      </c>
+      <c r="Q20">
+        <v>1.47</v>
+      </c>
+      <c r="R20">
+        <v>1.8</v>
+      </c>
+      <c r="S20">
+        <v>2.14</v>
+      </c>
+      <c r="T20">
+        <v>1.67</v>
+      </c>
+      <c r="U20">
+        <v>2.36</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>34</v>
+      </c>
+      <c r="Y20">
+        <v>44</v>
+      </c>
+      <c r="Z20">
+        <v>90</v>
+      </c>
+      <c r="AA20">
+        <v>240</v>
+      </c>
+      <c r="AB20">
+        <v>13.5</v>
+      </c>
+      <c r="AC20">
+        <v>13.5</v>
+      </c>
+      <c r="AD20">
+        <v>29</v>
+      </c>
+      <c r="AE20">
+        <v>110</v>
+      </c>
+      <c r="AF20">
+        <v>11.5</v>
+      </c>
+      <c r="AG20">
+        <v>10.5</v>
+      </c>
+      <c r="AH20">
+        <v>21</v>
+      </c>
+      <c r="AI20">
+        <v>85</v>
+      </c>
+      <c r="AJ20">
+        <v>14</v>
+      </c>
+      <c r="AK20">
+        <v>13.5</v>
+      </c>
+      <c r="AL20">
+        <v>25</v>
+      </c>
+      <c r="AM20">
+        <v>95</v>
+      </c>
+      <c r="AN20">
+        <v>4.6</v>
+      </c>
+      <c r="AO20">
+        <v>85</v>
+      </c>
+      <c r="AP20">
+        <v>30</v>
+      </c>
+      <c r="AQ20">
+        <v>32</v>
+      </c>
+      <c r="AR20">
+        <v>12.5</v>
+      </c>
+      <c r="AS20">
+        <v>13.5</v>
+      </c>
+      <c r="AT20">
+        <v>12</v>
+      </c>
+      <c r="AU20">
+        <v>12</v>
+      </c>
+      <c r="AV20">
+        <v>26</v>
+      </c>
+      <c r="AW20">
+        <v>29</v>
+      </c>
+      <c r="AX20">
+        <v>10.5</v>
+      </c>
+      <c r="AY20">
+        <v>9.6</v>
+      </c>
+      <c r="AZ20">
+        <v>19</v>
+      </c>
+      <c r="BA20">
+        <v>12</v>
+      </c>
+      <c r="BB20">
+        <v>12.5</v>
+      </c>
+      <c r="BC20">
+        <v>12.5</v>
+      </c>
+      <c r="BD20">
+        <v>19.5</v>
+      </c>
+      <c r="BE20">
+        <v>55</v>
+      </c>
+      <c r="BF20">
+        <v>4.2</v>
+      </c>
+      <c r="BG20">
+        <v>50</v>
+      </c>
+      <c r="BH20">
+        <v>1000</v>
+      </c>
+      <c r="BI20">
+        <v>1.01</v>
+      </c>
+      <c r="BJ20">
+        <v>1000</v>
+      </c>
+      <c r="BK20">
+        <v>1.01</v>
+      </c>
+      <c r="BL20">
+        <v>1000</v>
+      </c>
+      <c r="BM20">
+        <v>1.01</v>
+      </c>
+      <c r="BN20">
+        <v>1000</v>
+      </c>
+      <c r="BO20">
+        <v>1.01</v>
+      </c>
+      <c r="BP20">
+        <v>1000</v>
+      </c>
+      <c r="BQ20">
+        <v>1.01</v>
+      </c>
+      <c r="BR20">
+        <v>1000</v>
+      </c>
+      <c r="BS20">
+        <v>1.01</v>
+      </c>
+      <c r="BT20">
+        <v>1000</v>
+      </c>
+      <c r="BU20">
+        <v>1.01</v>
+      </c>
+      <c r="BV20">
+        <v>1000</v>
+      </c>
+      <c r="BW20">
+        <v>1.01</v>
+      </c>
+      <c r="BX20">
+        <v>1000</v>
+      </c>
+      <c r="BY20">
+        <v>1.01</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" t="s">
+        <v>94</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" t="s">
+        <v>129</v>
+      </c>
+      <c r="E21" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21">
         <v>1.08</v>
       </c>
-      <c r="G17">
-        <v>1000</v>
-      </c>
-      <c r="H17">
+      <c r="G21">
+        <v>1000</v>
+      </c>
+      <c r="H21">
         <v>1.08</v>
       </c>
-      <c r="I17">
-        <v>1000</v>
-      </c>
-      <c r="J17">
+      <c r="I21">
+        <v>1000</v>
+      </c>
+      <c r="J21">
         <v>1.08</v>
       </c>
-      <c r="K17">
+      <c r="K21">
         <v>470</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17">
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
         <v>1.07</v>
       </c>
-      <c r="Q17">
-        <v>1.01</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>0</v>
-      </c>
-      <c r="U17">
-        <v>0</v>
-      </c>
-      <c r="V17">
-        <v>0</v>
-      </c>
-      <c r="W17">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>0</v>
-      </c>
-      <c r="Y17">
-        <v>0</v>
-      </c>
-      <c r="Z17">
-        <v>0</v>
-      </c>
-      <c r="AA17">
-        <v>0</v>
-      </c>
-      <c r="AB17">
-        <v>0</v>
-      </c>
-      <c r="AC17">
-        <v>0</v>
-      </c>
-      <c r="AD17">
-        <v>0</v>
-      </c>
-      <c r="AE17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>0</v>
-      </c>
-      <c r="AG17">
-        <v>0</v>
-      </c>
-      <c r="AH17">
-        <v>0</v>
-      </c>
-      <c r="AI17">
-        <v>0</v>
-      </c>
-      <c r="AJ17">
-        <v>0</v>
-      </c>
-      <c r="AK17">
-        <v>0</v>
-      </c>
-      <c r="AL17">
-        <v>0</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>0</v>
-      </c>
-      <c r="AO17">
-        <v>0</v>
-      </c>
-      <c r="AP17">
-        <v>0</v>
-      </c>
-      <c r="AQ17">
-        <v>0</v>
-      </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
-      <c r="AS17">
-        <v>0</v>
-      </c>
-      <c r="AT17">
-        <v>0</v>
-      </c>
-      <c r="AU17">
-        <v>0</v>
-      </c>
-      <c r="AV17">
-        <v>0</v>
-      </c>
-      <c r="AW17">
-        <v>0</v>
-      </c>
-      <c r="AX17">
-        <v>0</v>
-      </c>
-      <c r="AY17">
-        <v>0</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>0</v>
-      </c>
-      <c r="BC17">
-        <v>0</v>
-      </c>
-      <c r="BD17">
-        <v>0</v>
-      </c>
-      <c r="BE17">
-        <v>0</v>
-      </c>
-      <c r="BF17">
-        <v>0</v>
-      </c>
-      <c r="BG17">
-        <v>0</v>
-      </c>
-      <c r="BH17">
-        <v>0</v>
-      </c>
-      <c r="BI17">
-        <v>0</v>
-      </c>
-      <c r="BJ17">
-        <v>0</v>
-      </c>
-      <c r="BK17">
-        <v>0</v>
-      </c>
-      <c r="BL17">
-        <v>0</v>
-      </c>
-      <c r="BM17">
-        <v>0</v>
-      </c>
-      <c r="BN17">
-        <v>0</v>
-      </c>
-      <c r="BO17">
-        <v>0</v>
-      </c>
-      <c r="BP17">
-        <v>0</v>
-      </c>
-      <c r="BQ17">
-        <v>0</v>
-      </c>
-      <c r="BR17">
-        <v>0</v>
-      </c>
-      <c r="BS17">
-        <v>0</v>
-      </c>
-      <c r="BT17">
-        <v>0</v>
-      </c>
-      <c r="BU17">
-        <v>0</v>
-      </c>
-      <c r="BV17">
-        <v>0</v>
-      </c>
-      <c r="BW17">
-        <v>0</v>
-      </c>
-      <c r="BX17">
-        <v>0</v>
-      </c>
-      <c r="BY17">
-        <v>0</v>
-      </c>
-      <c r="BZ17">
-        <v>0</v>
-      </c>
-      <c r="CA17">
-        <v>0</v>
-      </c>
-      <c r="CB17" t="s">
-        <v>137</v>
+      <c r="Q21">
+        <v>1.01</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -466,7 +466,7 @@
     <t>MB Rouissat</t>
   </si>
   <si>
-    <t>2026-09-02 07:42:26</t>
+    <t>2026-09-02 09:54:29</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1075,7 @@
         <v>2.96</v>
       </c>
       <c r="K2">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L2">
         <v>1.45</v>
@@ -1084,22 +1084,22 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="O2">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P2">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q2">
-        <v>1.71</v>
+        <v>2.3</v>
       </c>
       <c r="R2">
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="T2">
         <v>1.96</v>
@@ -1126,7 +1126,7 @@
         <v>80</v>
       </c>
       <c r="AB2">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC2">
         <v>8.6</v>
@@ -1138,7 +1138,7 @@
         <v>60</v>
       </c>
       <c r="AF2">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AG2">
         <v>15</v>
@@ -1150,10 +1150,10 @@
         <v>85</v>
       </c>
       <c r="AJ2">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL2">
         <v>70</v>
@@ -1162,7 +1162,7 @@
         <v>190</v>
       </c>
       <c r="AN2">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AO2">
         <v>75</v>
@@ -1180,7 +1180,7 @@
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU2">
         <v>5.4</v>
@@ -1222,61 +1222,61 @@
         <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="BI2">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BJ2">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK2">
         <v>1.01</v>
       </c>
       <c r="BL2">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="BM2">
         <v>1.01</v>
       </c>
       <c r="BN2">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="BO2">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BP2">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ2">
         <v>1.01</v>
       </c>
       <c r="BR2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS2">
         <v>1.01</v>
       </c>
       <c r="BT2">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BU2">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV2">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BW2">
         <v>1.01</v>
       </c>
       <c r="BX2">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BY2">
         <v>1.01</v>
       </c>
       <c r="BZ2">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="CA2">
         <v>1.01</v>
@@ -1320,7 +1320,7 @@
         <v>4.5</v>
       </c>
       <c r="L3">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1332,7 +1332,7 @@
         <v>1.36</v>
       </c>
       <c r="P3">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="Q3">
         <v>2.06</v>
@@ -1344,7 +1344,7 @@
         <v>3.7</v>
       </c>
       <c r="T3">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U3">
         <v>1.86</v>
@@ -1386,7 +1386,7 @@
         <v>28</v>
       </c>
       <c r="AH3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI3">
         <v>55</v>
@@ -1428,10 +1428,10 @@
         <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AW3">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX3">
         <v>4</v>
@@ -1440,13 +1440,13 @@
         <v>19</v>
       </c>
       <c r="AZ3">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA3">
         <v>32</v>
       </c>
       <c r="BB3">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BC3">
         <v>4.2</v>
@@ -1467,7 +1467,7 @@
         <v>3.75</v>
       </c>
       <c r="BI3">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="BJ3">
         <v>13</v>
@@ -1494,7 +1494,7 @@
         <v>1.01</v>
       </c>
       <c r="BR3">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BS3">
         <v>1.01</v>
@@ -1571,31 +1571,31 @@
         <v>1.24</v>
       </c>
       <c r="O4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P4">
         <v>1.24</v>
       </c>
       <c r="Q4">
-        <v>1.02</v>
+        <v>1.44</v>
       </c>
       <c r="R4">
         <v>1.18</v>
       </c>
       <c r="S4">
+        <v>1.45</v>
+      </c>
+      <c r="T4">
+        <v>1.01</v>
+      </c>
+      <c r="U4">
+        <v>1.01</v>
+      </c>
+      <c r="V4">
         <v>1.02</v>
       </c>
-      <c r="T4">
-        <v>1.01</v>
-      </c>
-      <c r="U4">
-        <v>1.01</v>
-      </c>
-      <c r="V4">
-        <v>1.01</v>
-      </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -1786,7 +1786,7 @@
         <v>133</v>
       </c>
       <c r="F5">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G5">
         <v>5.7</v>
@@ -1801,16 +1801,16 @@
         <v>3.85</v>
       </c>
       <c r="K5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O5">
         <v>1.19</v>
@@ -1822,10 +1822,10 @@
         <v>1.61</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S5">
-        <v>1.61</v>
+        <v>2.5</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2037,7 +2037,7 @@
         <v>1.59</v>
       </c>
       <c r="I6">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="J6">
         <v>4.4</v>
@@ -2052,10 +2052,10 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="O6">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="P6">
         <v>2.38</v>
@@ -2064,112 +2064,112 @@
         <v>1.58</v>
       </c>
       <c r="R6">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="S6">
-        <v>1.58</v>
+        <v>2.34</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="W6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX6">
         <v>1.01</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BB6">
         <v>1.01</v>
@@ -2187,7 +2187,7 @@
         <v>1.01</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2754,13 +2754,13 @@
         <v>137</v>
       </c>
       <c r="F9">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G9">
         <v>2.96</v>
       </c>
       <c r="H9">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="I9">
         <v>3.2</v>
@@ -3005,7 +3005,7 @@
         <v>2.36</v>
       </c>
       <c r="I10">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="J10">
         <v>3.4</v>
@@ -3238,16 +3238,16 @@
         <v>139</v>
       </c>
       <c r="F11">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G11">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H11">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I11">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J11">
         <v>3.5</v>
@@ -3268,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q11">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3480,7 +3480,7 @@
         <v>140</v>
       </c>
       <c r="F12">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G12">
         <v>1.9</v>
@@ -3489,10 +3489,10 @@
         <v>4.1</v>
       </c>
       <c r="I12">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K12">
         <v>4.4</v>
@@ -3513,7 +3513,7 @@
         <v>2.5</v>
       </c>
       <c r="Q12">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3737,7 +3737,7 @@
         <v>4.6</v>
       </c>
       <c r="K13">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3749,22 +3749,22 @@
         <v>4.7</v>
       </c>
       <c r="O13">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P13">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="Q13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R13">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S13">
         <v>2.74</v>
       </c>
       <c r="T13">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U13">
         <v>2.08</v>
@@ -3824,7 +3824,7 @@
         <v>120</v>
       </c>
       <c r="AN13">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO13">
         <v>110</v>
@@ -3836,10 +3836,10 @@
         <v>20</v>
       </c>
       <c r="AR13">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS13">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT13">
         <v>8.6</v>
@@ -3851,7 +3851,7 @@
         <v>20</v>
       </c>
       <c r="AW13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX13">
         <v>9</v>
@@ -3863,7 +3863,7 @@
         <v>18.5</v>
       </c>
       <c r="BA13">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB13">
         <v>12.5</v>
@@ -3872,16 +3872,16 @@
         <v>13.5</v>
       </c>
       <c r="BD13">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE13">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF13">
         <v>6.4</v>
       </c>
       <c r="BG13">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH13">
         <v>4.5</v>
@@ -3896,13 +3896,13 @@
         <v>1.01</v>
       </c>
       <c r="BL13">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="BM13">
         <v>1.01</v>
       </c>
       <c r="BN13">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BO13">
         <v>3.4</v>
@@ -3926,7 +3926,7 @@
         <v>1.01</v>
       </c>
       <c r="BV13">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BW13">
         <v>1.01</v>
@@ -3979,7 +3979,7 @@
         <v>5.8</v>
       </c>
       <c r="K14">
-        <v>7.6</v>
+        <v>6.8</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3997,7 +3997,7 @@
         <v>3.05</v>
       </c>
       <c r="Q14">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4212,7 +4212,7 @@
         <v>1.44</v>
       </c>
       <c r="H15">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="I15">
         <v>10.5</v>
@@ -4221,7 +4221,7 @@
         <v>5.3</v>
       </c>
       <c r="K15">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="L15">
         <v>1.21</v>
@@ -4236,7 +4236,7 @@
         <v>1.16</v>
       </c>
       <c r="P15">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="Q15">
         <v>1.48</v>
@@ -4245,13 +4245,13 @@
         <v>1.7</v>
       </c>
       <c r="S15">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T15">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V15">
         <v>1.11</v>
@@ -4260,7 +4260,7 @@
         <v>3.25</v>
       </c>
       <c r="X15">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="Y15">
         <v>40</v>
@@ -4269,103 +4269,103 @@
         <v>85</v>
       </c>
       <c r="AA15">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AB15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AC15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AD15">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AE15">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AF15">
         <v>11</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI15">
         <v>95</v>
       </c>
       <c r="AJ15">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK15">
         <v>14.5</v>
       </c>
       <c r="AL15">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM15">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AN15">
         <v>5.4</v>
       </c>
       <c r="AO15">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AP15">
+        <v>5.1</v>
+      </c>
+      <c r="AQ15">
+        <v>30</v>
+      </c>
+      <c r="AR15">
+        <v>5.5</v>
+      </c>
+      <c r="AS15">
         <v>5.8</v>
       </c>
-      <c r="AQ15">
-        <v>6</v>
-      </c>
-      <c r="AR15">
-        <v>6.4</v>
-      </c>
-      <c r="AS15">
-        <v>6.8</v>
-      </c>
       <c r="AT15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU15">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV15">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="AW15">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="AX15">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY15">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AZ15">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA15">
-        <v>6.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB15">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BC15">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BD15">
-        <v>5.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE15">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BF15">
         <v>4</v>
       </c>
       <c r="BG15">
-        <v>6.6</v>
+        <v>5.6</v>
       </c>
       <c r="BH15">
         <v>5.7</v>
@@ -4478,7 +4478,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="Q16">
         <v>2.08</v>
@@ -4932,7 +4932,7 @@
         <v>146</v>
       </c>
       <c r="F18">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G18">
         <v>2.72</v>
@@ -5174,10 +5174,10 @@
         <v>147</v>
       </c>
       <c r="F19">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G19">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H19">
         <v>1.43</v>
@@ -5186,10 +5186,10 @@
         <v>1.44</v>
       </c>
       <c r="J19">
+        <v>5.5</v>
+      </c>
+      <c r="K19">
         <v>5.7</v>
-      </c>
-      <c r="K19">
-        <v>5.8</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5207,16 +5207,16 @@
         <v>3.25</v>
       </c>
       <c r="Q19">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="R19">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="S19">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="T19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U19">
         <v>2.5</v>
@@ -5243,7 +5243,7 @@
         <v>44</v>
       </c>
       <c r="AC19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD19">
         <v>10.5</v>
@@ -5252,7 +5252,7 @@
         <v>13.5</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AG19">
         <v>32</v>
@@ -5270,10 +5270,10 @@
         <v>110</v>
       </c>
       <c r="AL19">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM19">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN19">
         <v>75</v>
@@ -5297,40 +5297,40 @@
         <v>34</v>
       </c>
       <c r="AU19">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AV19">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW19">
         <v>11.5</v>
       </c>
       <c r="AX19">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AY19">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AZ19">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA19">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB19">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="BC19">
         <v>55</v>
       </c>
       <c r="BD19">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="BE19">
         <v>50</v>
       </c>
       <c r="BF19">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BG19">
         <v>4</v>
@@ -5354,7 +5354,7 @@
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BO19">
         <v>1.01</v>
@@ -5372,7 +5372,7 @@
         <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU19">
         <v>3.55</v>
@@ -5419,7 +5419,7 @@
         <v>1.43</v>
       </c>
       <c r="G20">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="H20">
         <v>7.6</v>
@@ -5428,7 +5428,7 @@
         <v>8</v>
       </c>
       <c r="J20">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="K20">
         <v>5.7</v>
@@ -5446,16 +5446,16 @@
         <v>1.15</v>
       </c>
       <c r="P20">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="Q20">
         <v>1.47</v>
       </c>
       <c r="R20">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="S20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T20">
         <v>1.67</v>
@@ -5482,7 +5482,7 @@
         <v>240</v>
       </c>
       <c r="AB20">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC20">
         <v>13.5</v>
@@ -5497,7 +5497,7 @@
         <v>11.5</v>
       </c>
       <c r="AG20">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH20">
         <v>21</v>
@@ -5509,10 +5509,10 @@
         <v>14</v>
       </c>
       <c r="AK20">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL20">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AM20">
         <v>95</v>
@@ -5524,22 +5524,22 @@
         <v>85</v>
       </c>
       <c r="AP20">
+        <v>10</v>
+      </c>
+      <c r="AQ20">
         <v>30</v>
       </c>
-      <c r="AQ20">
-        <v>32</v>
-      </c>
       <c r="AR20">
+        <v>12</v>
+      </c>
+      <c r="AS20">
         <v>12.5</v>
       </c>
-      <c r="AS20">
-        <v>13.5</v>
-      </c>
       <c r="AT20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AU20">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV20">
         <v>26</v>
@@ -5554,10 +5554,10 @@
         <v>9.6</v>
       </c>
       <c r="AZ20">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA20">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="BB20">
         <v>12.5</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="169">
   <si>
     <t>League</t>
   </si>
@@ -268,15 +268,27 @@
     <t>South Korean K2 League</t>
   </si>
   <si>
+    <t>UAE Arabian Gulf League</t>
+  </si>
+  <si>
+    <t>Azerbaijan Premier League</t>
+  </si>
+  <si>
     <t>Qatari Stars League</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
     <t>Saudi Professional League</t>
   </si>
   <si>
+    <t>Algerian Ligue 1</t>
+  </si>
+  <si>
     <t>Hungarian NB I</t>
   </si>
   <si>
@@ -295,9 +307,6 @@
     <t>Spanish La Liga</t>
   </si>
   <si>
-    <t>Algerian Ligue 1</t>
-  </si>
-  <si>
     <t>2026-09-04</t>
   </si>
   <si>
@@ -313,15 +322,24 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>13:45:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
+    <t>14:30:00</t>
+  </si>
+  <si>
     <t>15:00:00</t>
   </si>
   <si>
     <t>16:00:00</t>
   </si>
   <si>
+    <t>16:15:00</t>
+  </si>
+  <si>
     <t>16:30:00</t>
   </si>
   <si>
@@ -361,9 +379,18 @@
     <t>Paju Citizen</t>
   </si>
   <si>
+    <t>Al-Ittihad Kalba</t>
+  </si>
+  <si>
+    <t>FK Qabala</t>
+  </si>
+  <si>
     <t>Al Shamal</t>
   </si>
   <si>
+    <t>CSM Slatina</t>
+  </si>
+  <si>
     <t>Polissya Zhytomyr</t>
   </si>
   <si>
@@ -373,6 +400,15 @@
     <t>Abha</t>
   </si>
   <si>
+    <t>USM Khenchela</t>
+  </si>
+  <si>
+    <t>Kapaz Ganja</t>
+  </si>
+  <si>
+    <t>Al Wasl</t>
+  </si>
+  <si>
     <t>Vasas</t>
   </si>
   <si>
@@ -421,9 +457,18 @@
     <t>Daegu Fc</t>
   </si>
   <si>
+    <t>Al Ain</t>
+  </si>
+  <si>
+    <t>Imisli FK</t>
+  </si>
+  <si>
     <t>Al Shahaniya</t>
   </si>
   <si>
+    <t>Chindia Targoviste</t>
+  </si>
+  <si>
     <t>FK Kudrivka</t>
   </si>
   <si>
@@ -433,6 +478,15 @@
     <t>Al-Ettifaq</t>
   </si>
   <si>
+    <t>USM Alger</t>
+  </si>
+  <si>
+    <t>Shamakhi FK</t>
+  </si>
+  <si>
+    <t>Al-Khaleej Khor Fakkan</t>
+  </si>
+  <si>
     <t>Nyiregyhaza</t>
   </si>
   <si>
@@ -466,7 +520,7 @@
     <t>MB Rouissat</t>
   </si>
   <si>
-    <t>2026-09-02 09:54:29</t>
+    <t>2026-09-02 12:07:40</t>
   </si>
 </sst>
 </file>
@@ -798,7 +852,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1048,16 +1102,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>142</v>
       </c>
       <c r="F2">
         <v>2.44</v>
@@ -1090,7 +1144,7 @@
         <v>1.02</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q2">
         <v>2.3</v>
@@ -1102,13 +1156,13 @@
         <v>4</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="U2">
-        <v>1.84</v>
+        <v>1.71</v>
       </c>
       <c r="V2">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W2">
         <v>1.56</v>
@@ -1282,7 +1336,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1290,37 +1344,37 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="F3">
         <v>5.3</v>
       </c>
       <c r="G3">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="H3">
         <v>1.71</v>
       </c>
       <c r="I3">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J3">
         <v>3.6</v>
       </c>
       <c r="K3">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L3">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1335,22 +1389,22 @@
         <v>1.77</v>
       </c>
       <c r="Q3">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
         <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T3">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U3">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="V3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W3">
         <v>1.18</v>
@@ -1410,16 +1464,16 @@
         <v>16</v>
       </c>
       <c r="AP3">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AQ3">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AR3">
         <v>8.4</v>
       </c>
       <c r="AS3">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="AT3">
         <v>12.5</v>
@@ -1428,31 +1482,31 @@
         <v>7.4</v>
       </c>
       <c r="AV3">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW3">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AX3">
         <v>4</v>
       </c>
       <c r="AY3">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AZ3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA3">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="BB3">
         <v>4.2</v>
       </c>
       <c r="BC3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BE3">
         <v>4.2</v>
@@ -1461,7 +1515,7 @@
         <v>4.2</v>
       </c>
       <c r="BG3">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH3">
         <v>3.75</v>
@@ -1524,7 +1578,7 @@
         <v>1.01</v>
       </c>
       <c r="CB3" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1532,22 +1586,22 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E4" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="F4">
         <v>1.08</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H4">
         <v>1.08</v>
@@ -1568,13 +1622,13 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
         <v>1.02</v>
       </c>
       <c r="P4">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q4">
         <v>1.44</v>
@@ -1766,7 +1820,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1774,16 +1828,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D5" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="F5">
         <v>4.3</v>
@@ -1810,10 +1864,10 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O5">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="P5">
         <v>1.96</v>
@@ -1825,7 +1879,7 @@
         <v>1.37</v>
       </c>
       <c r="S5">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T5">
         <v>1.01</v>
@@ -2008,7 +2062,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2016,16 +2070,16 @@
         <v>83</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="F6">
         <v>5.1</v>
@@ -2040,7 +2094,7 @@
         <v>1.73</v>
       </c>
       <c r="J6">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K6">
         <v>5.7</v>
@@ -2067,19 +2121,19 @@
         <v>1.55</v>
       </c>
       <c r="S6">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="T6">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="U6">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="V6">
         <v>2.36</v>
       </c>
       <c r="W6">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="X6">
         <v>29</v>
@@ -2250,7 +2304,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2258,1002 +2312,1002 @@
         <v>84</v>
       </c>
       <c r="B7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="D7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E7" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="F7">
-        <v>1.85</v>
+        <v>15.5</v>
       </c>
       <c r="G7">
-        <v>2.04</v>
+        <v>24</v>
       </c>
       <c r="H7">
-        <v>3.8</v>
+        <v>1.19</v>
       </c>
       <c r="I7">
-        <v>5.1</v>
+        <v>1.25</v>
       </c>
       <c r="J7">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="K7">
-        <v>5.1</v>
+        <v>10.5</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P7">
-        <v>2.24</v>
+        <v>2.82</v>
       </c>
       <c r="Q7">
+        <v>1.37</v>
+      </c>
+      <c r="R7">
+        <v>1.27</v>
+      </c>
+      <c r="S7">
+        <v>1.43</v>
+      </c>
+      <c r="T7">
+        <v>2.08</v>
+      </c>
+      <c r="U7">
         <v>1.63</v>
       </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-      <c r="U7">
-        <v>0</v>
-      </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="AO7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AP7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU7">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AV7">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AX7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="BH7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB7" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:80">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E8" t="s">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="F8">
-        <v>1.1</v>
+        <v>2.08</v>
       </c>
       <c r="G8">
-        <v>7.8</v>
+        <v>2.68</v>
       </c>
       <c r="H8">
-        <v>1.16</v>
+        <v>2.98</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="J8">
-        <v>1.14</v>
+        <v>2.86</v>
       </c>
       <c r="K8">
-        <v>350</v>
+        <v>5.4</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P8">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E9" t="s">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="F9">
-        <v>2.64</v>
+        <v>1.85</v>
       </c>
       <c r="G9">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="H9">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="I9">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="J9">
-        <v>2.94</v>
+        <v>3.8</v>
       </c>
       <c r="K9">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P9">
-        <v>1.59</v>
+        <v>2.26</v>
       </c>
       <c r="Q9">
-        <v>2.34</v>
+        <v>1.62</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>150</v>
       </c>
       <c r="F10">
-        <v>2.8</v>
+        <v>1.08</v>
       </c>
       <c r="G10">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="H10">
-        <v>2.36</v>
+        <v>1.08</v>
       </c>
       <c r="I10">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="J10">
-        <v>3.4</v>
+        <v>1.08</v>
       </c>
       <c r="K10">
-        <v>4.6</v>
+        <v>230</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P10">
-        <v>2.02</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.78</v>
+        <v>1.02</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="B11" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F11">
-        <v>2.26</v>
+        <v>1.1</v>
       </c>
       <c r="G11">
-        <v>2.64</v>
+        <v>7.8</v>
       </c>
       <c r="H11">
-        <v>2.88</v>
+        <v>1.16</v>
       </c>
       <c r="I11">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>1.14</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>350</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3268,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>2.12</v>
+        <v>1.24</v>
       </c>
       <c r="Q11">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="R11">
         <v>0</v>
@@ -3460,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3468,34 +3522,34 @@
         <v>88</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="F12">
-        <v>1.86</v>
+        <v>2.62</v>
       </c>
       <c r="G12">
-        <v>1.9</v>
+        <v>2.96</v>
       </c>
       <c r="H12">
-        <v>4.1</v>
+        <v>2.84</v>
       </c>
       <c r="I12">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="J12">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3510,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="Q12">
-        <v>1.59</v>
+        <v>2.34</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3702,7 +3756,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3710,64 +3764,64 @@
         <v>89</v>
       </c>
       <c r="B13" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F13">
-        <v>1.55</v>
+        <v>2.8</v>
       </c>
       <c r="G13">
-        <v>1.57</v>
+        <v>3.45</v>
       </c>
       <c r="H13">
-        <v>6.6</v>
+        <v>2.38</v>
       </c>
       <c r="I13">
-        <v>7.2</v>
+        <v>2.74</v>
       </c>
       <c r="J13">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="K13">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N13">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O13">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="P13">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Q13">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="R13">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="S13">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T13">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="U13">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="V13">
         <v>0</v>
@@ -3776,166 +3830,166 @@
         <v>0</v>
       </c>
       <c r="X13">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="Y13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Z13">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AA13">
-        <v>210</v>
+        <v>0</v>
       </c>
       <c r="AB13">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AC13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AD13">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF13">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AG13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH13">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI13">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AJ13">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AK13">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AL13">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AM13">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN13">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO13">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AP13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AQ13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AR13">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AU13">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AV13">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AW13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AX13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ13">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BB13">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC13">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BD13">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BE13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BF13">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BG13">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BH13">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BI13">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="BJ13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL13">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="BM13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN13">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BO13">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="BP13">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BQ13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR13">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BS13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT13">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BU13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV13">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BW13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX13">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY13">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ13">
         <v>0</v>
@@ -3944,42 +3998,42 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="F14">
-        <v>8.4</v>
+        <v>1.08</v>
       </c>
       <c r="G14">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="H14">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="I14">
-        <v>1.41</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>5.8</v>
+        <v>1.08</v>
       </c>
       <c r="K14">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -3994,10 +4048,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>3.05</v>
+        <v>1.07</v>
       </c>
       <c r="Q14">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4186,290 +4240,290 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E15" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="F15">
-        <v>1.37</v>
+        <v>1.08</v>
       </c>
       <c r="G15">
-        <v>1.44</v>
+        <v>1000</v>
       </c>
       <c r="H15">
-        <v>8</v>
+        <v>1.08</v>
       </c>
       <c r="I15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="J15">
-        <v>5.3</v>
+        <v>1.08</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>520</v>
       </c>
       <c r="L15">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q15">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BG15">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BH15">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BI15">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BJ15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL15">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BO15">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BP15">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR15">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT15">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX15">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ15">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C16" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E16" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F16">
-        <v>2.12</v>
+        <v>1.31</v>
       </c>
       <c r="G16">
-        <v>2.4</v>
+        <v>1.41</v>
       </c>
       <c r="H16">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="I16">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="J16">
-        <v>3.15</v>
+        <v>5.9</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="L16">
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4478,23 +4532,23 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>1.6</v>
+        <v>2.72</v>
       </c>
       <c r="Q16">
+        <v>1.39</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>1.74</v>
+      </c>
+      <c r="U16">
         <v>2.08</v>
       </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>0</v>
-      </c>
       <c r="V16">
         <v>0</v>
       </c>
@@ -4502,112 +4556,112 @@
         <v>0</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH16">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AL16">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AM16">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AY16">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ16">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC16">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD16">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BE16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BG16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>0</v>
@@ -4670,42 +4724,42 @@
         <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E17" t="s">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -4720,10 +4774,10 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="Q17">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="R17">
         <v>0</v>
@@ -4912,42 +4966,42 @@
         <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E18" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="F18">
-        <v>2.44</v>
+        <v>1.86</v>
       </c>
       <c r="G18">
-        <v>2.72</v>
+        <v>1.9</v>
       </c>
       <c r="H18">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="I18">
-        <v>3.2</v>
+        <v>4.3</v>
       </c>
       <c r="J18">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="K18">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -4962,10 +5016,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q18">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5154,192 +5208,192 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E19" t="s">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="F19">
-        <v>8</v>
+        <v>1.56</v>
       </c>
       <c r="G19">
-        <v>8.199999999999999</v>
+        <v>1.57</v>
       </c>
       <c r="H19">
-        <v>1.43</v>
+        <v>6.6</v>
       </c>
       <c r="I19">
-        <v>1.44</v>
+        <v>7</v>
       </c>
       <c r="J19">
-        <v>5.5</v>
+        <v>4.6</v>
       </c>
       <c r="K19">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="L19">
         <v>0</v>
       </c>
       <c r="M19">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N19">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="O19">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="P19">
+        <v>2.3</v>
+      </c>
+      <c r="Q19">
+        <v>1.66</v>
+      </c>
+      <c r="R19">
+        <v>1.51</v>
+      </c>
+      <c r="S19">
+        <v>2.72</v>
+      </c>
+      <c r="T19">
+        <v>1.84</v>
+      </c>
+      <c r="U19">
+        <v>2.08</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>21</v>
+      </c>
+      <c r="Y19">
+        <v>29</v>
+      </c>
+      <c r="Z19">
+        <v>65</v>
+      </c>
+      <c r="AA19">
+        <v>210</v>
+      </c>
+      <c r="AB19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC19">
+        <v>11</v>
+      </c>
+      <c r="AD19">
+        <v>26</v>
+      </c>
+      <c r="AE19">
+        <v>100</v>
+      </c>
+      <c r="AF19">
+        <v>10</v>
+      </c>
+      <c r="AG19">
+        <v>10.5</v>
+      </c>
+      <c r="AH19">
+        <v>24</v>
+      </c>
+      <c r="AI19">
+        <v>90</v>
+      </c>
+      <c r="AJ19">
+        <v>14.5</v>
+      </c>
+      <c r="AK19">
+        <v>16</v>
+      </c>
+      <c r="AL19">
+        <v>36</v>
+      </c>
+      <c r="AM19">
+        <v>120</v>
+      </c>
+      <c r="AN19">
+        <v>7</v>
+      </c>
+      <c r="AO19">
+        <v>110</v>
+      </c>
+      <c r="AP19">
+        <v>18</v>
+      </c>
+      <c r="AQ19">
+        <v>21</v>
+      </c>
+      <c r="AR19">
+        <v>9.4</v>
+      </c>
+      <c r="AS19">
+        <v>10.5</v>
+      </c>
+      <c r="AT19">
+        <v>8.6</v>
+      </c>
+      <c r="AU19">
+        <v>9.4</v>
+      </c>
+      <c r="AV19">
+        <v>21</v>
+      </c>
+      <c r="AW19">
+        <v>10</v>
+      </c>
+      <c r="AX19">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY19">
+        <v>9</v>
+      </c>
+      <c r="AZ19">
+        <v>18</v>
+      </c>
+      <c r="BA19">
+        <v>10</v>
+      </c>
+      <c r="BB19">
+        <v>12.5</v>
+      </c>
+      <c r="BC19">
+        <v>13.5</v>
+      </c>
+      <c r="BD19">
+        <v>8.4</v>
+      </c>
+      <c r="BE19">
+        <v>10</v>
+      </c>
+      <c r="BF19">
+        <v>6.4</v>
+      </c>
+      <c r="BG19">
+        <v>10</v>
+      </c>
+      <c r="BH19">
+        <v>4.5</v>
+      </c>
+      <c r="BI19">
         <v>3.25</v>
-      </c>
-      <c r="Q19">
-        <v>1.42</v>
-      </c>
-      <c r="R19">
-        <v>1.88</v>
-      </c>
-      <c r="S19">
-        <v>2.06</v>
-      </c>
-      <c r="T19">
-        <v>1.63</v>
-      </c>
-      <c r="U19">
-        <v>2.5</v>
-      </c>
-      <c r="V19">
-        <v>0</v>
-      </c>
-      <c r="W19">
-        <v>0</v>
-      </c>
-      <c r="X19">
-        <v>38</v>
-      </c>
-      <c r="Y19">
-        <v>14.5</v>
-      </c>
-      <c r="Z19">
-        <v>12</v>
-      </c>
-      <c r="AA19">
-        <v>14</v>
-      </c>
-      <c r="AB19">
-        <v>44</v>
-      </c>
-      <c r="AC19">
-        <v>14</v>
-      </c>
-      <c r="AD19">
-        <v>10.5</v>
-      </c>
-      <c r="AE19">
-        <v>13.5</v>
-      </c>
-      <c r="AF19">
-        <v>95</v>
-      </c>
-      <c r="AG19">
-        <v>32</v>
-      </c>
-      <c r="AH19">
-        <v>19.5</v>
-      </c>
-      <c r="AI19">
-        <v>24</v>
-      </c>
-      <c r="AJ19">
-        <v>1000</v>
-      </c>
-      <c r="AK19">
-        <v>110</v>
-      </c>
-      <c r="AL19">
-        <v>70</v>
-      </c>
-      <c r="AM19">
-        <v>75</v>
-      </c>
-      <c r="AN19">
-        <v>75</v>
-      </c>
-      <c r="AO19">
-        <v>4.3</v>
-      </c>
-      <c r="AP19">
-        <v>30</v>
-      </c>
-      <c r="AQ19">
-        <v>13</v>
-      </c>
-      <c r="AR19">
-        <v>11.5</v>
-      </c>
-      <c r="AS19">
-        <v>12.5</v>
-      </c>
-      <c r="AT19">
-        <v>34</v>
-      </c>
-      <c r="AU19">
-        <v>12.5</v>
-      </c>
-      <c r="AV19">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW19">
-        <v>11.5</v>
-      </c>
-      <c r="AX19">
-        <v>60</v>
-      </c>
-      <c r="AY19">
-        <v>27</v>
-      </c>
-      <c r="AZ19">
-        <v>17</v>
-      </c>
-      <c r="BA19">
-        <v>21</v>
-      </c>
-      <c r="BB19">
-        <v>100</v>
-      </c>
-      <c r="BC19">
-        <v>55</v>
-      </c>
-      <c r="BD19">
-        <v>55</v>
-      </c>
-      <c r="BE19">
-        <v>50</v>
-      </c>
-      <c r="BF19">
-        <v>50</v>
-      </c>
-      <c r="BG19">
-        <v>4</v>
-      </c>
-      <c r="BH19">
-        <v>6.4</v>
-      </c>
-      <c r="BI19">
-        <v>4.1</v>
       </c>
       <c r="BJ19">
         <v>12</v>
@@ -5348,55 +5402,55 @@
         <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="BM19">
         <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>14</v>
+        <v>4.8</v>
       </c>
       <c r="BO19">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP19">
+        <v>11</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>26</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>12</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
         <v>60</v>
       </c>
-      <c r="BQ19">
-        <v>1.01</v>
-      </c>
-      <c r="BR19">
-        <v>55</v>
-      </c>
-      <c r="BS19">
-        <v>1.01</v>
-      </c>
-      <c r="BT19">
-        <v>5.3</v>
-      </c>
-      <c r="BU19">
-        <v>3.55</v>
-      </c>
-      <c r="BV19">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BW19">
         <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="BY19">
         <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="CA19">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:80">
@@ -5404,64 +5458,64 @@
         <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E20" t="s">
-        <v>148</v>
+        <v>160</v>
       </c>
       <c r="F20">
-        <v>1.43</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G20">
-        <v>1.45</v>
+        <v>11.5</v>
       </c>
       <c r="H20">
-        <v>7.6</v>
+        <v>1.34</v>
       </c>
       <c r="I20">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="J20">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="K20">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N20">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P20">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="Q20">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="R20">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="S20">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T20">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U20">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -5470,166 +5524,166 @@
         <v>0</v>
       </c>
       <c r="X20">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Y20">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="Z20">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AA20">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="AB20">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AC20">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AD20">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AE20">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF20">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG20">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AH20">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI20">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AK20">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AL20">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AM20">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AN20">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AO20">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AP20">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ20">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AR20">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AS20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AT20">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU20">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AV20">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AW20">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AX20">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY20">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ20">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BA20">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="BB20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC20">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BD20">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BE20">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="BF20">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="BG20">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ20">
         <v>0</v>
@@ -5638,249 +5692,1701 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C21" t="s">
+        <v>110</v>
+      </c>
+      <c r="D21" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" t="s">
+        <v>161</v>
+      </c>
+      <c r="F21">
+        <v>1.38</v>
+      </c>
+      <c r="G21">
+        <v>1.44</v>
+      </c>
+      <c r="H21">
+        <v>8</v>
+      </c>
+      <c r="I21">
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <v>5.5</v>
+      </c>
+      <c r="K21">
+        <v>7</v>
+      </c>
+      <c r="L21">
+        <v>1.21</v>
+      </c>
+      <c r="M21">
+        <v>1.01</v>
+      </c>
+      <c r="N21">
+        <v>6</v>
+      </c>
+      <c r="O21">
+        <v>1.16</v>
+      </c>
+      <c r="P21">
+        <v>2.74</v>
+      </c>
+      <c r="Q21">
+        <v>1.47</v>
+      </c>
+      <c r="R21">
+        <v>1.69</v>
+      </c>
+      <c r="S21">
+        <v>2.16</v>
+      </c>
+      <c r="T21">
+        <v>1.76</v>
+      </c>
+      <c r="U21">
+        <v>2.06</v>
+      </c>
+      <c r="V21">
+        <v>1.11</v>
+      </c>
+      <c r="W21">
+        <v>3.25</v>
+      </c>
+      <c r="X21">
+        <v>38</v>
+      </c>
+      <c r="Y21">
+        <v>40</v>
+      </c>
+      <c r="Z21">
+        <v>100</v>
+      </c>
+      <c r="AA21">
+        <v>300</v>
+      </c>
+      <c r="AB21">
+        <v>13</v>
+      </c>
+      <c r="AC21">
+        <v>16.5</v>
+      </c>
+      <c r="AD21">
+        <v>40</v>
+      </c>
+      <c r="AE21">
+        <v>130</v>
+      </c>
+      <c r="AF21">
+        <v>11</v>
+      </c>
+      <c r="AG21">
+        <v>13.5</v>
+      </c>
+      <c r="AH21">
+        <v>25</v>
+      </c>
+      <c r="AI21">
+        <v>110</v>
+      </c>
+      <c r="AJ21">
+        <v>15</v>
+      </c>
+      <c r="AK21">
+        <v>14.5</v>
+      </c>
+      <c r="AL21">
+        <v>36</v>
+      </c>
+      <c r="AM21">
+        <v>120</v>
+      </c>
+      <c r="AN21">
+        <v>4.8</v>
+      </c>
+      <c r="AO21">
+        <v>130</v>
+      </c>
+      <c r="AP21">
+        <v>5.3</v>
+      </c>
+      <c r="AQ21">
+        <v>28</v>
+      </c>
+      <c r="AR21">
+        <v>5.8</v>
+      </c>
+      <c r="AS21">
+        <v>6</v>
+      </c>
+      <c r="AT21">
+        <v>10</v>
+      </c>
+      <c r="AU21">
+        <v>10</v>
+      </c>
+      <c r="AV21">
+        <v>24</v>
+      </c>
+      <c r="AW21">
+        <v>5.8</v>
+      </c>
+      <c r="AX21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21">
+        <v>19.5</v>
+      </c>
+      <c r="BA21">
+        <v>5.8</v>
+      </c>
+      <c r="BB21">
+        <v>10.5</v>
+      </c>
+      <c r="BC21">
+        <v>11.5</v>
+      </c>
+      <c r="BD21">
+        <v>21</v>
+      </c>
+      <c r="BE21">
+        <v>5.8</v>
+      </c>
+      <c r="BF21">
+        <v>4</v>
+      </c>
+      <c r="BG21">
+        <v>5.8</v>
+      </c>
+      <c r="BH21">
+        <v>5.7</v>
+      </c>
+      <c r="BI21">
+        <v>3.7</v>
+      </c>
+      <c r="BJ21">
+        <v>12.5</v>
+      </c>
+      <c r="BK21">
+        <v>1.01</v>
+      </c>
+      <c r="BL21">
+        <v>120</v>
+      </c>
+      <c r="BM21">
+        <v>1.01</v>
+      </c>
+      <c r="BN21">
+        <v>5</v>
+      </c>
+      <c r="BO21">
+        <v>3.3</v>
+      </c>
+      <c r="BP21">
+        <v>9.6</v>
+      </c>
+      <c r="BQ21">
+        <v>1.01</v>
+      </c>
+      <c r="BR21">
+        <v>24</v>
+      </c>
+      <c r="BS21">
+        <v>1.01</v>
+      </c>
+      <c r="BT21">
+        <v>14.5</v>
+      </c>
+      <c r="BU21">
+        <v>1.01</v>
+      </c>
+      <c r="BV21">
+        <v>75</v>
+      </c>
+      <c r="BW21">
+        <v>1.01</v>
+      </c>
+      <c r="BX21">
+        <v>65</v>
+      </c>
+      <c r="BY21">
+        <v>1.01</v>
+      </c>
+      <c r="BZ21">
+        <v>12.5</v>
+      </c>
+      <c r="CA21">
+        <v>1.01</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" t="s">
+        <v>111</v>
+      </c>
+      <c r="D22" t="s">
+        <v>136</v>
+      </c>
+      <c r="E22" t="s">
+        <v>162</v>
+      </c>
+      <c r="F22">
+        <v>2.12</v>
+      </c>
+      <c r="G22">
+        <v>2.4</v>
+      </c>
+      <c r="H22">
+        <v>3.5</v>
+      </c>
+      <c r="I22">
+        <v>4.2</v>
+      </c>
+      <c r="J22">
+        <v>3.15</v>
+      </c>
+      <c r="K22">
+        <v>4.2</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>1.6</v>
+      </c>
+      <c r="Q22">
+        <v>2.08</v>
+      </c>
+      <c r="R22">
+        <v>0</v>
+      </c>
+      <c r="S22">
+        <v>0</v>
+      </c>
+      <c r="T22">
+        <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>0</v>
+      </c>
+      <c r="AE22">
+        <v>0</v>
+      </c>
+      <c r="AF22">
+        <v>0</v>
+      </c>
+      <c r="AG22">
+        <v>0</v>
+      </c>
+      <c r="AH22">
+        <v>0</v>
+      </c>
+      <c r="AI22">
+        <v>0</v>
+      </c>
+      <c r="AJ22">
+        <v>0</v>
+      </c>
+      <c r="AK22">
+        <v>0</v>
+      </c>
+      <c r="AL22">
+        <v>0</v>
+      </c>
+      <c r="AM22">
+        <v>0</v>
+      </c>
+      <c r="AN22">
+        <v>0</v>
+      </c>
+      <c r="AO22">
+        <v>0</v>
+      </c>
+      <c r="AP22">
+        <v>0</v>
+      </c>
+      <c r="AQ22">
+        <v>0</v>
+      </c>
+      <c r="AR22">
+        <v>0</v>
+      </c>
+      <c r="AS22">
+        <v>0</v>
+      </c>
+      <c r="AT22">
+        <v>0</v>
+      </c>
+      <c r="AU22">
+        <v>0</v>
+      </c>
+      <c r="AV22">
+        <v>0</v>
+      </c>
+      <c r="AW22">
+        <v>0</v>
+      </c>
+      <c r="AX22">
+        <v>0</v>
+      </c>
+      <c r="AY22">
+        <v>0</v>
+      </c>
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+      <c r="BA22">
+        <v>0</v>
+      </c>
+      <c r="BB22">
+        <v>0</v>
+      </c>
+      <c r="BC22">
+        <v>0</v>
+      </c>
+      <c r="BD22">
+        <v>0</v>
+      </c>
+      <c r="BE22">
+        <v>0</v>
+      </c>
+      <c r="BF22">
+        <v>0</v>
+      </c>
+      <c r="BG22">
+        <v>0</v>
+      </c>
+      <c r="BH22">
+        <v>0</v>
+      </c>
+      <c r="BI22">
+        <v>0</v>
+      </c>
+      <c r="BJ22">
+        <v>0</v>
+      </c>
+      <c r="BK22">
+        <v>0</v>
+      </c>
+      <c r="BL22">
+        <v>0</v>
+      </c>
+      <c r="BM22">
+        <v>0</v>
+      </c>
+      <c r="BN22">
+        <v>0</v>
+      </c>
+      <c r="BO22">
+        <v>0</v>
+      </c>
+      <c r="BP22">
+        <v>0</v>
+      </c>
+      <c r="BQ22">
+        <v>0</v>
+      </c>
+      <c r="BR22">
+        <v>0</v>
+      </c>
+      <c r="BS22">
+        <v>0</v>
+      </c>
+      <c r="BT22">
+        <v>0</v>
+      </c>
+      <c r="BU22">
+        <v>0</v>
+      </c>
+      <c r="BV22">
+        <v>0</v>
+      </c>
+      <c r="BW22">
+        <v>0</v>
+      </c>
+      <c r="BX22">
+        <v>0</v>
+      </c>
+      <c r="BY22">
+        <v>0</v>
+      </c>
+      <c r="BZ22">
+        <v>0</v>
+      </c>
+      <c r="CA22">
+        <v>0</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>94</v>
+      </c>
+      <c r="B23" t="s">
+        <v>97</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" t="s">
+        <v>163</v>
+      </c>
+      <c r="F23">
+        <v>0</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>0</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>2.24</v>
+      </c>
+      <c r="Q23">
+        <v>1.01</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+      <c r="S23">
+        <v>0</v>
+      </c>
+      <c r="T23">
+        <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>0</v>
+      </c>
+      <c r="AE23">
+        <v>0</v>
+      </c>
+      <c r="AF23">
+        <v>0</v>
+      </c>
+      <c r="AG23">
+        <v>0</v>
+      </c>
+      <c r="AH23">
+        <v>0</v>
+      </c>
+      <c r="AI23">
+        <v>0</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>0</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23">
+        <v>0</v>
+      </c>
+      <c r="AQ23">
+        <v>0</v>
+      </c>
+      <c r="AR23">
+        <v>0</v>
+      </c>
+      <c r="AS23">
+        <v>0</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
+      <c r="AV23">
+        <v>0</v>
+      </c>
+      <c r="AW23">
+        <v>0</v>
+      </c>
+      <c r="AX23">
+        <v>0</v>
+      </c>
+      <c r="AY23">
+        <v>0</v>
+      </c>
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+      <c r="BA23">
+        <v>0</v>
+      </c>
+      <c r="BB23">
+        <v>0</v>
+      </c>
+      <c r="BC23">
+        <v>0</v>
+      </c>
+      <c r="BD23">
+        <v>0</v>
+      </c>
+      <c r="BE23">
+        <v>0</v>
+      </c>
+      <c r="BF23">
+        <v>0</v>
+      </c>
+      <c r="BG23">
+        <v>0</v>
+      </c>
+      <c r="BH23">
+        <v>0</v>
+      </c>
+      <c r="BI23">
+        <v>0</v>
+      </c>
+      <c r="BJ23">
+        <v>0</v>
+      </c>
+      <c r="BK23">
+        <v>0</v>
+      </c>
+      <c r="BL23">
+        <v>0</v>
+      </c>
+      <c r="BM23">
+        <v>0</v>
+      </c>
+      <c r="BN23">
+        <v>0</v>
+      </c>
+      <c r="BO23">
+        <v>0</v>
+      </c>
+      <c r="BP23">
+        <v>0</v>
+      </c>
+      <c r="BQ23">
+        <v>0</v>
+      </c>
+      <c r="BR23">
+        <v>0</v>
+      </c>
+      <c r="BS23">
+        <v>0</v>
+      </c>
+      <c r="BT23">
+        <v>0</v>
+      </c>
+      <c r="BU23">
+        <v>0</v>
+      </c>
+      <c r="BV23">
+        <v>0</v>
+      </c>
+      <c r="BW23">
+        <v>0</v>
+      </c>
+      <c r="BX23">
+        <v>0</v>
+      </c>
+      <c r="BY23">
+        <v>0</v>
+      </c>
+      <c r="BZ23">
+        <v>0</v>
+      </c>
+      <c r="CA23">
+        <v>0</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C24" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>164</v>
+      </c>
+      <c r="F24">
+        <v>2.44</v>
+      </c>
+      <c r="G24">
+        <v>2.72</v>
+      </c>
+      <c r="H24">
+        <v>2.7</v>
+      </c>
+      <c r="I24">
+        <v>3.2</v>
+      </c>
+      <c r="J24">
+        <v>3.65</v>
+      </c>
+      <c r="K24">
+        <v>4.6</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>1.25</v>
+      </c>
+      <c r="Q24">
+        <v>1.01</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+      <c r="S24">
+        <v>0</v>
+      </c>
+      <c r="T24">
+        <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>0</v>
+      </c>
+      <c r="AE24">
+        <v>0</v>
+      </c>
+      <c r="AF24">
+        <v>0</v>
+      </c>
+      <c r="AG24">
+        <v>0</v>
+      </c>
+      <c r="AH24">
+        <v>0</v>
+      </c>
+      <c r="AI24">
+        <v>0</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>0</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24">
+        <v>0</v>
+      </c>
+      <c r="AQ24">
+        <v>0</v>
+      </c>
+      <c r="AR24">
+        <v>0</v>
+      </c>
+      <c r="AS24">
+        <v>0</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
+      <c r="AV24">
+        <v>0</v>
+      </c>
+      <c r="AW24">
+        <v>0</v>
+      </c>
+      <c r="AX24">
+        <v>0</v>
+      </c>
+      <c r="AY24">
+        <v>0</v>
+      </c>
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+      <c r="BA24">
+        <v>0</v>
+      </c>
+      <c r="BB24">
+        <v>0</v>
+      </c>
+      <c r="BC24">
+        <v>0</v>
+      </c>
+      <c r="BD24">
+        <v>0</v>
+      </c>
+      <c r="BE24">
+        <v>0</v>
+      </c>
+      <c r="BF24">
+        <v>0</v>
+      </c>
+      <c r="BG24">
+        <v>0</v>
+      </c>
+      <c r="BH24">
+        <v>0</v>
+      </c>
+      <c r="BI24">
+        <v>0</v>
+      </c>
+      <c r="BJ24">
+        <v>0</v>
+      </c>
+      <c r="BK24">
+        <v>0</v>
+      </c>
+      <c r="BL24">
+        <v>0</v>
+      </c>
+      <c r="BM24">
+        <v>0</v>
+      </c>
+      <c r="BN24">
+        <v>0</v>
+      </c>
+      <c r="BO24">
+        <v>0</v>
+      </c>
+      <c r="BP24">
+        <v>0</v>
+      </c>
+      <c r="BQ24">
+        <v>0</v>
+      </c>
+      <c r="BR24">
+        <v>0</v>
+      </c>
+      <c r="BS24">
+        <v>0</v>
+      </c>
+      <c r="BT24">
+        <v>0</v>
+      </c>
+      <c r="BU24">
+        <v>0</v>
+      </c>
+      <c r="BV24">
+        <v>0</v>
+      </c>
+      <c r="BW24">
+        <v>0</v>
+      </c>
+      <c r="BX24">
+        <v>0</v>
+      </c>
+      <c r="BY24">
+        <v>0</v>
+      </c>
+      <c r="BZ24">
+        <v>0</v>
+      </c>
+      <c r="CA24">
+        <v>0</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>96</v>
+      </c>
+      <c r="B25" t="s">
+        <v>97</v>
+      </c>
+      <c r="C25" t="s">
+        <v>113</v>
+      </c>
+      <c r="D25" t="s">
+        <v>139</v>
+      </c>
+      <c r="E25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F25">
+        <v>8</v>
+      </c>
+      <c r="G25">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H25">
+        <v>1.43</v>
+      </c>
+      <c r="I25">
+        <v>1.44</v>
+      </c>
+      <c r="J25">
+        <v>5.6</v>
+      </c>
+      <c r="K25">
+        <v>5.7</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>1.03</v>
+      </c>
+      <c r="N25">
+        <v>7.6</v>
+      </c>
+      <c r="O25">
+        <v>1.13</v>
+      </c>
+      <c r="P25">
+        <v>3.3</v>
+      </c>
+      <c r="Q25">
+        <v>1.42</v>
+      </c>
+      <c r="R25">
+        <v>1.88</v>
+      </c>
+      <c r="S25">
+        <v>2.06</v>
+      </c>
+      <c r="T25">
+        <v>1.62</v>
+      </c>
+      <c r="U25">
+        <v>2.5</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>40</v>
+      </c>
+      <c r="Y25">
+        <v>15</v>
+      </c>
+      <c r="Z25">
+        <v>12.5</v>
+      </c>
+      <c r="AA25">
+        <v>14</v>
+      </c>
+      <c r="AB25">
+        <v>44</v>
+      </c>
+      <c r="AC25">
+        <v>13.5</v>
+      </c>
+      <c r="AD25">
+        <v>10.5</v>
+      </c>
+      <c r="AE25">
+        <v>13.5</v>
+      </c>
+      <c r="AF25">
+        <v>95</v>
+      </c>
+      <c r="AG25">
+        <v>30</v>
+      </c>
+      <c r="AH25">
+        <v>21</v>
+      </c>
+      <c r="AI25">
+        <v>25</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>100</v>
+      </c>
+      <c r="AL25">
+        <v>70</v>
+      </c>
+      <c r="AM25">
+        <v>75</v>
+      </c>
+      <c r="AN25">
+        <v>75</v>
+      </c>
+      <c r="AO25">
+        <v>4.2</v>
+      </c>
+      <c r="AP25">
+        <v>32</v>
+      </c>
+      <c r="AQ25">
+        <v>13</v>
+      </c>
+      <c r="AR25">
+        <v>11.5</v>
+      </c>
+      <c r="AS25">
+        <v>12.5</v>
+      </c>
+      <c r="AT25">
+        <v>34</v>
+      </c>
+      <c r="AU25">
+        <v>12.5</v>
+      </c>
+      <c r="AV25">
+        <v>9.6</v>
+      </c>
+      <c r="AW25">
+        <v>11.5</v>
+      </c>
+      <c r="AX25">
+        <v>50</v>
+      </c>
+      <c r="AY25">
+        <v>26</v>
+      </c>
+      <c r="AZ25">
+        <v>17</v>
+      </c>
+      <c r="BA25">
+        <v>21</v>
+      </c>
+      <c r="BB25">
+        <v>85</v>
+      </c>
+      <c r="BC25">
+        <v>55</v>
+      </c>
+      <c r="BD25">
+        <v>55</v>
+      </c>
+      <c r="BE25">
+        <v>50</v>
+      </c>
+      <c r="BF25">
+        <v>36</v>
+      </c>
+      <c r="BG25">
+        <v>4</v>
+      </c>
+      <c r="BH25">
+        <v>6.4</v>
+      </c>
+      <c r="BI25">
+        <v>4.1</v>
+      </c>
+      <c r="BJ25">
+        <v>12</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>95</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>13.5</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>60</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>55</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>5.4</v>
+      </c>
+      <c r="BU25">
+        <v>3.55</v>
+      </c>
+      <c r="BV25">
+        <v>10</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>21</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>11</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
         <v>93</v>
       </c>
-      <c r="B21" t="s">
-        <v>94</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" t="s">
-        <v>129</v>
-      </c>
-      <c r="E21" t="s">
-        <v>149</v>
-      </c>
-      <c r="F21">
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" t="s">
+        <v>140</v>
+      </c>
+      <c r="E26" t="s">
+        <v>166</v>
+      </c>
+      <c r="F26">
+        <v>1.43</v>
+      </c>
+      <c r="G26">
+        <v>1.45</v>
+      </c>
+      <c r="H26">
+        <v>7.6</v>
+      </c>
+      <c r="I26">
+        <v>8</v>
+      </c>
+      <c r="J26">
+        <v>5.5</v>
+      </c>
+      <c r="K26">
+        <v>5.7</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>1.02</v>
+      </c>
+      <c r="N26">
+        <v>6.8</v>
+      </c>
+      <c r="O26">
+        <v>1.15</v>
+      </c>
+      <c r="P26">
+        <v>2.96</v>
+      </c>
+      <c r="Q26">
+        <v>1.46</v>
+      </c>
+      <c r="R26">
+        <v>1.81</v>
+      </c>
+      <c r="S26">
+        <v>2.14</v>
+      </c>
+      <c r="T26">
+        <v>1.67</v>
+      </c>
+      <c r="U26">
+        <v>2.38</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>34</v>
+      </c>
+      <c r="Y26">
+        <v>38</v>
+      </c>
+      <c r="Z26">
+        <v>90</v>
+      </c>
+      <c r="AA26">
+        <v>240</v>
+      </c>
+      <c r="AB26">
+        <v>13.5</v>
+      </c>
+      <c r="AC26">
+        <v>13.5</v>
+      </c>
+      <c r="AD26">
+        <v>29</v>
+      </c>
+      <c r="AE26">
+        <v>110</v>
+      </c>
+      <c r="AF26">
+        <v>11.5</v>
+      </c>
+      <c r="AG26">
+        <v>11</v>
+      </c>
+      <c r="AH26">
+        <v>21</v>
+      </c>
+      <c r="AI26">
+        <v>85</v>
+      </c>
+      <c r="AJ26">
+        <v>14</v>
+      </c>
+      <c r="AK26">
+        <v>14</v>
+      </c>
+      <c r="AL26">
+        <v>26</v>
+      </c>
+      <c r="AM26">
+        <v>95</v>
+      </c>
+      <c r="AN26">
+        <v>4.5</v>
+      </c>
+      <c r="AO26">
+        <v>85</v>
+      </c>
+      <c r="AP26">
+        <v>28</v>
+      </c>
+      <c r="AQ26">
+        <v>30</v>
+      </c>
+      <c r="AR26">
+        <v>55</v>
+      </c>
+      <c r="AS26">
+        <v>13</v>
+      </c>
+      <c r="AT26">
+        <v>11.5</v>
+      </c>
+      <c r="AU26">
+        <v>11.5</v>
+      </c>
+      <c r="AV26">
+        <v>13</v>
+      </c>
+      <c r="AW26">
+        <v>29</v>
+      </c>
+      <c r="AX26">
+        <v>10.5</v>
+      </c>
+      <c r="AY26">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26">
+        <v>18.5</v>
+      </c>
+      <c r="BA26">
+        <v>46</v>
+      </c>
+      <c r="BB26">
+        <v>12.5</v>
+      </c>
+      <c r="BC26">
+        <v>12.5</v>
+      </c>
+      <c r="BD26">
+        <v>19.5</v>
+      </c>
+      <c r="BE26">
+        <v>55</v>
+      </c>
+      <c r="BF26">
+        <v>4.2</v>
+      </c>
+      <c r="BG26">
+        <v>12</v>
+      </c>
+      <c r="BH26">
+        <v>1000</v>
+      </c>
+      <c r="BI26">
+        <v>1.01</v>
+      </c>
+      <c r="BJ26">
+        <v>1000</v>
+      </c>
+      <c r="BK26">
+        <v>1.01</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>1.01</v>
+      </c>
+      <c r="BN26">
+        <v>1000</v>
+      </c>
+      <c r="BO26">
+        <v>1.01</v>
+      </c>
+      <c r="BP26">
+        <v>1000</v>
+      </c>
+      <c r="BQ26">
+        <v>1.01</v>
+      </c>
+      <c r="BR26">
+        <v>1000</v>
+      </c>
+      <c r="BS26">
+        <v>1.01</v>
+      </c>
+      <c r="BT26">
+        <v>1000</v>
+      </c>
+      <c r="BU26">
+        <v>1.01</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>1.01</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>1.01</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>90</v>
+      </c>
+      <c r="B27" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" t="s">
+        <v>115</v>
+      </c>
+      <c r="D27" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27">
         <v>1.08</v>
       </c>
-      <c r="G21">
-        <v>1000</v>
-      </c>
-      <c r="H21">
+      <c r="G27">
+        <v>1000</v>
+      </c>
+      <c r="H27">
         <v>1.08</v>
       </c>
-      <c r="I21">
-        <v>1000</v>
-      </c>
-      <c r="J21">
+      <c r="I27">
+        <v>1000</v>
+      </c>
+      <c r="J27">
         <v>1.08</v>
       </c>
-      <c r="K21">
+      <c r="K27">
         <v>470</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
         <v>1.07</v>
       </c>
-      <c r="Q21">
-        <v>1.01</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21">
-        <v>0</v>
-      </c>
-      <c r="BE21">
-        <v>0</v>
-      </c>
-      <c r="BF21">
-        <v>0</v>
-      </c>
-      <c r="BG21">
-        <v>0</v>
-      </c>
-      <c r="BH21">
-        <v>0</v>
-      </c>
-      <c r="BI21">
-        <v>0</v>
-      </c>
-      <c r="BJ21">
-        <v>0</v>
-      </c>
-      <c r="BK21">
-        <v>0</v>
-      </c>
-      <c r="BL21">
-        <v>0</v>
-      </c>
-      <c r="BM21">
-        <v>0</v>
-      </c>
-      <c r="BN21">
-        <v>0</v>
-      </c>
-      <c r="BO21">
-        <v>0</v>
-      </c>
-      <c r="BP21">
-        <v>0</v>
-      </c>
-      <c r="BQ21">
-        <v>0</v>
-      </c>
-      <c r="BR21">
-        <v>0</v>
-      </c>
-      <c r="BS21">
-        <v>0</v>
-      </c>
-      <c r="BT21">
-        <v>0</v>
-      </c>
-      <c r="BU21">
-        <v>0</v>
-      </c>
-      <c r="BV21">
-        <v>0</v>
-      </c>
-      <c r="BW21">
-        <v>0</v>
-      </c>
-      <c r="BX21">
-        <v>0</v>
-      </c>
-      <c r="BY21">
-        <v>0</v>
-      </c>
-      <c r="BZ21">
-        <v>0</v>
-      </c>
-      <c r="CA21">
-        <v>0</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>150</v>
+      <c r="Q27">
+        <v>1.01</v>
+      </c>
+      <c r="R27">
+        <v>0</v>
+      </c>
+      <c r="S27">
+        <v>0</v>
+      </c>
+      <c r="T27">
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>0</v>
+      </c>
+      <c r="AE27">
+        <v>0</v>
+      </c>
+      <c r="AF27">
+        <v>0</v>
+      </c>
+      <c r="AG27">
+        <v>0</v>
+      </c>
+      <c r="AH27">
+        <v>0</v>
+      </c>
+      <c r="AI27">
+        <v>0</v>
+      </c>
+      <c r="AJ27">
+        <v>0</v>
+      </c>
+      <c r="AK27">
+        <v>0</v>
+      </c>
+      <c r="AL27">
+        <v>0</v>
+      </c>
+      <c r="AM27">
+        <v>0</v>
+      </c>
+      <c r="AN27">
+        <v>0</v>
+      </c>
+      <c r="AO27">
+        <v>0</v>
+      </c>
+      <c r="AP27">
+        <v>0</v>
+      </c>
+      <c r="AQ27">
+        <v>0</v>
+      </c>
+      <c r="AR27">
+        <v>0</v>
+      </c>
+      <c r="AS27">
+        <v>0</v>
+      </c>
+      <c r="AT27">
+        <v>0</v>
+      </c>
+      <c r="AU27">
+        <v>0</v>
+      </c>
+      <c r="AV27">
+        <v>0</v>
+      </c>
+      <c r="AW27">
+        <v>0</v>
+      </c>
+      <c r="AX27">
+        <v>0</v>
+      </c>
+      <c r="AY27">
+        <v>0</v>
+      </c>
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+      <c r="BA27">
+        <v>0</v>
+      </c>
+      <c r="BB27">
+        <v>0</v>
+      </c>
+      <c r="BC27">
+        <v>0</v>
+      </c>
+      <c r="BD27">
+        <v>0</v>
+      </c>
+      <c r="BE27">
+        <v>0</v>
+      </c>
+      <c r="BF27">
+        <v>0</v>
+      </c>
+      <c r="BG27">
+        <v>0</v>
+      </c>
+      <c r="BH27">
+        <v>0</v>
+      </c>
+      <c r="BI27">
+        <v>0</v>
+      </c>
+      <c r="BJ27">
+        <v>0</v>
+      </c>
+      <c r="BK27">
+        <v>0</v>
+      </c>
+      <c r="BL27">
+        <v>0</v>
+      </c>
+      <c r="BM27">
+        <v>0</v>
+      </c>
+      <c r="BN27">
+        <v>0</v>
+      </c>
+      <c r="BO27">
+        <v>0</v>
+      </c>
+      <c r="BP27">
+        <v>0</v>
+      </c>
+      <c r="BQ27">
+        <v>0</v>
+      </c>
+      <c r="BR27">
+        <v>0</v>
+      </c>
+      <c r="BS27">
+        <v>0</v>
+      </c>
+      <c r="BT27">
+        <v>0</v>
+      </c>
+      <c r="BU27">
+        <v>0</v>
+      </c>
+      <c r="BV27">
+        <v>0</v>
+      </c>
+      <c r="BW27">
+        <v>0</v>
+      </c>
+      <c r="BX27">
+        <v>0</v>
+      </c>
+      <c r="BY27">
+        <v>0</v>
+      </c>
+      <c r="BZ27">
+        <v>0</v>
+      </c>
+      <c r="CA27">
+        <v>0</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-09-04.xlsx
@@ -994,7 +994,7 @@
     <t>UTC Cajamarca</t>
   </si>
   <si>
-    <t>2026-09-02 19:20:28</t>
+    <t>2026-09-02 21:36:11</t>
   </si>
 </sst>
 </file>
@@ -1588,37 +1588,37 @@
         <v>240</v>
       </c>
       <c r="F2">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="G2">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="H2">
         <v>3.2</v>
       </c>
       <c r="I2">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J2">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K2">
         <v>3.45</v>
       </c>
       <c r="L2">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M2">
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O2">
         <v>1.02</v>
       </c>
       <c r="P2">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="Q2">
         <v>2.3</v>
@@ -1627,19 +1627,19 @@
         <v>1.18</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T2">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="U2">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V2">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="W2">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="X2">
         <v>11.5</v>
@@ -1651,13 +1651,13 @@
         <v>26</v>
       </c>
       <c r="AA2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB2">
         <v>10</v>
       </c>
       <c r="AC2">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2">
         <v>18</v>
@@ -1669,43 +1669,43 @@
         <v>18.5</v>
       </c>
       <c r="AG2">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AJ2">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM2">
         <v>180</v>
       </c>
       <c r="AN2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO2">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP2">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ2">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR2">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AS2">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT2">
         <v>6.2</v>
@@ -1714,43 +1714,43 @@
         <v>5.5</v>
       </c>
       <c r="AV2">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AX2">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AY2">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
         <v>15</v>
       </c>
       <c r="BA2">
+        <v>4.5</v>
+      </c>
+      <c r="BB2">
         <v>4.3</v>
       </c>
-      <c r="BB2">
-        <v>4.2</v>
-      </c>
       <c r="BC2">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD2">
+        <v>4.4</v>
+      </c>
+      <c r="BE2">
+        <v>4.6</v>
+      </c>
+      <c r="BF2">
         <v>4.3</v>
       </c>
-      <c r="BE2">
+      <c r="BG2">
         <v>4.4</v>
       </c>
-      <c r="BF2">
-        <v>4.1</v>
-      </c>
-      <c r="BG2">
-        <v>4.3</v>
-      </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI2">
         <v>1.01</v>
@@ -1759,55 +1759,55 @@
         <v>1000</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BN2">
         <v>1000</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BP2">
         <v>1000</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BR2">
         <v>1000</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BT2">
         <v>1000</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BV2">
         <v>1000</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BX2">
         <v>1000</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="CB2" t="s">
         <v>326</v>
@@ -1854,22 +1854,22 @@
         <v>1.01</v>
       </c>
       <c r="N3">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P3">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q3">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="R3">
         <v>1.18</v>
       </c>
       <c r="S3">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="T3">
         <v>1.01</v>
@@ -1878,7 +1878,7 @@
         <v>1.01</v>
       </c>
       <c r="V3">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W3">
         <v>1.02</v>
@@ -2114,10 +2114,10 @@
         <v>3.75</v>
       </c>
       <c r="T4">
-        <v>1.97</v>
+        <v>1.81</v>
       </c>
       <c r="U4">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="V4">
         <v>2.2</v>
@@ -2317,13 +2317,13 @@
         <v>1.08</v>
       </c>
       <c r="G5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H5">
         <v>1.08</v>
       </c>
       <c r="I5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J5">
         <v>1.08</v>
@@ -2350,7 +2350,7 @@
         <v>1.26</v>
       </c>
       <c r="R5">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S5">
         <v>1.27</v>
@@ -2362,7 +2362,7 @@
         <v>1.01</v>
       </c>
       <c r="V5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W5">
         <v>1.02</v>
@@ -2604,10 +2604,10 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W6">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2798,7 +2798,7 @@
         <v>245</v>
       </c>
       <c r="F7">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="G7">
         <v>5.7</v>
@@ -2807,13 +2807,13 @@
         <v>1.78</v>
       </c>
       <c r="I7">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="J7">
         <v>3.85</v>
       </c>
       <c r="K7">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2846,7 +2846,7 @@
         <v>1.01</v>
       </c>
       <c r="V7">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="W7">
         <v>1.21</v>
@@ -3049,7 +3049,7 @@
         <v>1.59</v>
       </c>
       <c r="I8">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="J8">
         <v>4.2</v>
@@ -3079,7 +3079,7 @@
         <v>1.55</v>
       </c>
       <c r="S8">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T8">
         <v>1.67</v>
@@ -3088,7 +3088,7 @@
         <v>2.22</v>
       </c>
       <c r="V8">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="W8">
         <v>1.19</v>
@@ -3097,10 +3097,10 @@
         <v>29</v>
       </c>
       <c r="Y8">
+        <v>13.5</v>
+      </c>
+      <c r="Z8">
         <v>14</v>
-      </c>
-      <c r="Z8">
-        <v>14.5</v>
       </c>
       <c r="AA8">
         <v>21</v>
@@ -3115,7 +3115,7 @@
         <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AF8">
         <v>60</v>
@@ -3145,7 +3145,7 @@
         <v>70</v>
       </c>
       <c r="AO8">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AP8">
         <v>17</v>
@@ -3527,7 +3527,7 @@
         <v>15.5</v>
       </c>
       <c r="G10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10">
         <v>1.19</v>
@@ -3560,22 +3560,22 @@
         <v>1.43</v>
       </c>
       <c r="R10">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S10">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="T10">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U10">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="V10">
         <v>1.01</v>
       </c>
       <c r="W10">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
         <v>42</v>
@@ -3587,28 +3587,28 @@
         <v>10.5</v>
       </c>
       <c r="AA10">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AB10">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AC10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AD10">
         <v>15</v>
       </c>
       <c r="AE10">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF10">
         <v>220</v>
       </c>
       <c r="AG10">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH10">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AI10">
         <v>50</v>
@@ -3617,19 +3617,19 @@
         <v>1000</v>
       </c>
       <c r="AK10">
-        <v>340</v>
+        <v>360</v>
       </c>
       <c r="AL10">
+        <v>250</v>
+      </c>
+      <c r="AM10">
         <v>240</v>
       </c>
-      <c r="AM10">
-        <v>230</v>
-      </c>
       <c r="AN10">
-        <v>440</v>
+        <v>470</v>
       </c>
       <c r="AO10">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AP10">
         <v>1.01</v>
@@ -3647,13 +3647,13 @@
         <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AV10">
         <v>9.199999999999999</v>
       </c>
       <c r="AW10">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AX10">
         <v>1.01</v>
@@ -3683,7 +3683,7 @@
         <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BH10">
         <v>1000</v>
@@ -4011,13 +4011,13 @@
         <v>1.89</v>
       </c>
       <c r="G12">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="H12">
         <v>3.65</v>
       </c>
       <c r="I12">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="J12">
         <v>3.75</v>
@@ -4026,7 +4026,7 @@
         <v>5</v>
       </c>
       <c r="L12">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M12">
         <v>1.01</v>
@@ -4035,7 +4035,7 @@
         <v>2.82</v>
       </c>
       <c r="O12">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P12">
         <v>2.22</v>
@@ -4056,10 +4056,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="W12">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4253,7 +4253,7 @@
         <v>1.08</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H13">
         <v>1.08</v>
@@ -4298,10 +4298,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W13">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4498,13 +4498,13 @@
         <v>110</v>
       </c>
       <c r="H14">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J14">
-        <v>1.17</v>
+        <v>3.5</v>
       </c>
       <c r="K14">
         <v>350</v>
@@ -4516,16 +4516,16 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O14">
         <v>1.22</v>
       </c>
       <c r="P14">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q14">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="R14">
         <v>1.18</v>
@@ -4543,7 +4543,7 @@
         <v>1.02</v>
       </c>
       <c r="W14">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4773,13 +4773,13 @@
         <v>1.45</v>
       </c>
       <c r="S15">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T15">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="U15">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="V15">
         <v>1.7</v>
@@ -4788,7 +4788,7 @@
         <v>1.41</v>
       </c>
       <c r="X15">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Y15">
         <v>15</v>
@@ -4797,16 +4797,16 @@
         <v>20</v>
       </c>
       <c r="AA15">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB15">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AC15">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AE15">
         <v>28</v>
@@ -4815,31 +4815,31 @@
         <v>30</v>
       </c>
       <c r="AG15">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AH15">
         <v>19.5</v>
       </c>
       <c r="AI15">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ15">
         <v>65</v>
       </c>
       <c r="AK15">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL15">
         <v>48</v>
       </c>
       <c r="AM15">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AN15">
         <v>32</v>
       </c>
       <c r="AO15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AP15">
         <v>16</v>
@@ -4851,13 +4851,13 @@
         <v>12</v>
       </c>
       <c r="AS15">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT15">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AU15">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV15">
         <v>9.800000000000001</v>
@@ -4866,34 +4866,34 @@
         <v>19</v>
       </c>
       <c r="AX15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ15">
         <v>11.5</v>
       </c>
       <c r="BA15">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BB15">
-        <v>36</v>
+        <v>5.1</v>
       </c>
       <c r="BC15">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BD15">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="BE15">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF15">
         <v>18.5</v>
       </c>
       <c r="BG15">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH15">
         <v>1000</v>
@@ -4979,7 +4979,7 @@
         <v>1.54</v>
       </c>
       <c r="G16">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="H16">
         <v>5.2</v>
@@ -5000,10 +5000,10 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O16">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P16">
         <v>2.48</v>
@@ -5012,7 +5012,7 @@
         <v>1.51</v>
       </c>
       <c r="R16">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S16">
         <v>2.24</v>
@@ -5027,7 +5027,7 @@
         <v>1.17</v>
       </c>
       <c r="W16">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5233,7 +5233,7 @@
         <v>3.45</v>
       </c>
       <c r="K17">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L17">
         <v>1.01</v>
@@ -5245,7 +5245,7 @@
         <v>3.9</v>
       </c>
       <c r="O17">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P17">
         <v>2.02</v>
@@ -5469,7 +5469,7 @@
         <v>2.54</v>
       </c>
       <c r="I18">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="J18">
         <v>2.98</v>
@@ -5508,10 +5508,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W18">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X18">
         <v>18</v>
@@ -5986,10 +5986,10 @@
         <v>2.2</v>
       </c>
       <c r="T20">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="U20">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
         <v>1.01</v>
@@ -6228,10 +6228,10 @@
         <v>2.66</v>
       </c>
       <c r="T21">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="U21">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="V21">
         <v>1.25</v>
@@ -6670,7 +6670,7 @@
         <v>261</v>
       </c>
       <c r="F23">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="G23">
         <v>2.32</v>
@@ -6685,10 +6685,10 @@
         <v>3.35</v>
       </c>
       <c r="K23">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M23">
         <v>1.01</v>
@@ -6703,13 +6703,13 @@
         <v>1.83</v>
       </c>
       <c r="Q23">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="R23">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="S23">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6915,7 +6915,7 @@
         <v>2.66</v>
       </c>
       <c r="G24">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="H24">
         <v>3.05</v>
@@ -6930,25 +6930,25 @@
         <v>3.4</v>
       </c>
       <c r="L24">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="M24">
         <v>1.11</v>
       </c>
       <c r="N24">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O24">
         <v>1.46</v>
       </c>
       <c r="P24">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q24">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R24">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S24">
         <v>4.5</v>
@@ -6960,7 +6960,7 @@
         <v>1.86</v>
       </c>
       <c r="V24">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W24">
         <v>1.54</v>
@@ -6993,7 +6993,7 @@
         <v>21</v>
       </c>
       <c r="AG24">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AH24">
         <v>25</v>
@@ -7002,28 +7002,28 @@
         <v>75</v>
       </c>
       <c r="AJ24">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK24">
         <v>46</v>
       </c>
       <c r="AL24">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM24">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN24">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO24">
         <v>60</v>
       </c>
       <c r="AP24">
+        <v>7.4</v>
+      </c>
+      <c r="AQ24">
         <v>7.2</v>
-      </c>
-      <c r="AQ24">
-        <v>7</v>
       </c>
       <c r="AR24">
         <v>14</v>
@@ -7080,7 +7080,7 @@
         <v>2.34</v>
       </c>
       <c r="BJ24">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK24">
         <v>1.01</v>
@@ -7116,7 +7116,7 @@
         <v>4.5</v>
       </c>
       <c r="BV24">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BW24">
         <v>1.01</v>
@@ -7178,10 +7178,10 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>4.7</v>
+        <v>2.86</v>
       </c>
       <c r="O25">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P25">
         <v>2.86</v>
@@ -7414,7 +7414,7 @@
         <v>4.5</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M26">
         <v>1.01</v>
@@ -7883,7 +7883,7 @@
         <v>1.27</v>
       </c>
       <c r="G28">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="H28">
         <v>7.4</v>
@@ -7922,10 +7922,10 @@
         <v>2.02</v>
       </c>
       <c r="T28">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U28">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V28">
         <v>1.05</v>
@@ -7943,7 +7943,7 @@
         <v>110</v>
       </c>
       <c r="AA28">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB28">
         <v>15</v>
@@ -7952,7 +7952,7 @@
         <v>17</v>
       </c>
       <c r="AD28">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE28">
         <v>140</v>
@@ -7967,7 +7967,7 @@
         <v>28</v>
       </c>
       <c r="AI28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AJ28">
         <v>14</v>
@@ -7979,7 +7979,7 @@
         <v>34</v>
       </c>
       <c r="AM28">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN28">
         <v>4.6</v>
@@ -8012,7 +8012,7 @@
         <v>1.01</v>
       </c>
       <c r="AX28">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY28">
         <v>8.6</v>
@@ -8024,19 +8024,19 @@
         <v>1.01</v>
       </c>
       <c r="BB28">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC28">
         <v>10.5</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE28">
         <v>1.01</v>
       </c>
       <c r="BF28">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG28">
         <v>1.01</v>
@@ -8125,10 +8125,10 @@
         <v>2.3</v>
       </c>
       <c r="G29">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H29">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I29">
         <v>3.25</v>
@@ -8137,7 +8137,7 @@
         <v>3.85</v>
       </c>
       <c r="K29">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -8146,34 +8146,34 @@
         <v>1.05</v>
       </c>
       <c r="N29">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="O29">
         <v>1.22</v>
       </c>
       <c r="P29">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q29">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R29">
         <v>1.54</v>
       </c>
       <c r="S29">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="T29">
         <v>1.58</v>
       </c>
       <c r="U29">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="V29">
         <v>1.44</v>
       </c>
       <c r="W29">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X29">
         <v>24</v>
@@ -8224,7 +8224,7 @@
         <v>70</v>
       </c>
       <c r="AN29">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO29">
         <v>25</v>
@@ -8239,7 +8239,7 @@
         <v>18</v>
       </c>
       <c r="AS29">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT29">
         <v>12</v>
@@ -8263,7 +8263,7 @@
         <v>13</v>
       </c>
       <c r="BA29">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB29">
         <v>6</v>
@@ -8275,7 +8275,7 @@
         <v>22</v>
       </c>
       <c r="BE29">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF29">
         <v>11.5</v>
@@ -8364,7 +8364,7 @@
         <v>268</v>
       </c>
       <c r="F30">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G30">
         <v>2.58</v>
@@ -8376,7 +8376,7 @@
         <v>3.35</v>
       </c>
       <c r="J30">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="K30">
         <v>4.5</v>
@@ -8394,16 +8394,16 @@
         <v>1.22</v>
       </c>
       <c r="P30">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q30">
         <v>1.7</v>
       </c>
       <c r="R30">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S30">
-        <v>2.6</v>
+        <v>2.22</v>
       </c>
       <c r="T30">
         <v>1.01</v>
@@ -8654,7 +8654,7 @@
         <v>2.62</v>
       </c>
       <c r="V31">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W31">
         <v>2.4</v>
@@ -8672,7 +8672,7 @@
         <v>130</v>
       </c>
       <c r="AB31">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AC31">
         <v>13</v>
@@ -8723,7 +8723,7 @@
         <v>42</v>
       </c>
       <c r="AS31">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT31">
         <v>13</v>
@@ -8857,10 +8857,10 @@
         <v>1.66</v>
       </c>
       <c r="I32">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="J32">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K32">
         <v>5.3</v>
@@ -8878,7 +8878,7 @@
         <v>1.17</v>
       </c>
       <c r="P32">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="Q32">
         <v>1.52</v>
@@ -8896,7 +8896,7 @@
         <v>2.34</v>
       </c>
       <c r="V32">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="W32">
         <v>1.22</v>
@@ -8950,7 +8950,7 @@
         <v>80</v>
       </c>
       <c r="AN32">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO32">
         <v>7</v>
@@ -8965,7 +8965,7 @@
         <v>11</v>
       </c>
       <c r="AS32">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT32">
         <v>21</v>
@@ -8980,7 +8980,7 @@
         <v>13.5</v>
       </c>
       <c r="AX32">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY32">
         <v>17</v>
@@ -9111,7 +9111,7 @@
         <v>1.01</v>
       </c>
       <c r="M33">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N33">
         <v>3.15</v>
@@ -9332,7 +9332,7 @@
         <v>272</v>
       </c>
       <c r="F34">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="G34">
         <v>1.9</v>
@@ -9344,10 +9344,10 @@
         <v>4.4</v>
       </c>
       <c r="J34">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K34">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L34">
         <v>1.01</v>
@@ -9362,13 +9362,13 @@
         <v>1.2</v>
       </c>
       <c r="P34">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q34">
         <v>1.59</v>
       </c>
       <c r="R34">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S34">
         <v>2.46</v>
@@ -9610,13 +9610,13 @@
         <v>1.71</v>
       </c>
       <c r="R35">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S35">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="T35">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U35">
         <v>2.08</v>
@@ -9655,7 +9655,7 @@
         <v>10</v>
       </c>
       <c r="AG35">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AH35">
         <v>21</v>
@@ -9691,31 +9691,31 @@
         <v>48</v>
       </c>
       <c r="AS35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT35">
         <v>9</v>
       </c>
       <c r="AU35">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV35">
         <v>22</v>
       </c>
       <c r="AW35">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX35">
         <v>9.199999999999999</v>
       </c>
       <c r="AY35">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35">
         <v>18.5</v>
       </c>
       <c r="BA35">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BB35">
         <v>13</v>
@@ -9727,13 +9727,13 @@
         <v>27</v>
       </c>
       <c r="BE35">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF35">
         <v>6.6</v>
       </c>
       <c r="BG35">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="BH35">
         <v>4.5</v>
@@ -9831,7 +9831,7 @@
         <v>3.8</v>
       </c>
       <c r="K36">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L36">
         <v>1.01</v>
@@ -9852,7 +9852,7 @@
         <v>1.56</v>
       </c>
       <c r="R36">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="S36">
         <v>2.42</v>
@@ -10100,7 +10100,7 @@
         <v>2.08</v>
       </c>
       <c r="T37">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="U37">
         <v>2.14</v>
@@ -10351,7 +10351,7 @@
         <v>1.47</v>
       </c>
       <c r="W38">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X38">
         <v>38</v>
@@ -10408,7 +10408,7 @@
         <v>19.5</v>
       </c>
       <c r="AP38">
-        <v>25</v>
+        <v>6.6</v>
       </c>
       <c r="AQ38">
         <v>17.5</v>
@@ -10453,7 +10453,7 @@
         <v>18</v>
       </c>
       <c r="BE38">
-        <v>34</v>
+        <v>5.4</v>
       </c>
       <c r="BF38">
         <v>8.4</v>
@@ -10554,7 +10554,7 @@
         <v>2.4</v>
       </c>
       <c r="J39">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K39">
         <v>3.9</v>
@@ -10566,19 +10566,19 @@
         <v>1.06</v>
       </c>
       <c r="N39">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="O39">
         <v>1.29</v>
       </c>
       <c r="P39">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="Q39">
         <v>1.86</v>
       </c>
       <c r="R39">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S39">
         <v>3.05</v>
@@ -10784,22 +10784,22 @@
         <v>278</v>
       </c>
       <c r="F40">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G40">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I40">
-        <v>7.4</v>
+        <v>110</v>
       </c>
       <c r="J40">
-        <v>3.25</v>
+        <v>1.1</v>
       </c>
       <c r="K40">
-        <v>5.1</v>
+        <v>520</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10808,10 +10808,10 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="O40">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P40">
         <v>2.34</v>
@@ -10826,16 +10826,16 @@
         <v>2.24</v>
       </c>
       <c r="T40">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="U40">
-        <v>2.22</v>
+        <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="W40">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -11035,7 +11035,7 @@
         <v>5.7</v>
       </c>
       <c r="I41">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J41">
         <v>4.5</v>
@@ -11056,10 +11056,10 @@
         <v>1.2</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q41">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R41">
         <v>1.6</v>
@@ -11074,7 +11074,7 @@
         <v>2.26</v>
       </c>
       <c r="V41">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W41">
         <v>2.58</v>
@@ -11110,13 +11110,13 @@
         <v>10.5</v>
       </c>
       <c r="AH41">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AI41">
         <v>70</v>
       </c>
       <c r="AJ41">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AK41">
         <v>15.5</v>
@@ -11170,7 +11170,7 @@
         <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BC41">
         <v>11.5</v>
@@ -11755,7 +11755,7 @@
         <v>1.08</v>
       </c>
       <c r="G44">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H44">
         <v>1.08</v>
@@ -11994,7 +11994,7 @@
         <v>283</v>
       </c>
       <c r="F45">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G45">
         <v>2.04</v>
@@ -12478,7 +12478,7 @@
         <v>285</v>
       </c>
       <c r="F47">
-        <v>2.68</v>
+        <v>2.94</v>
       </c>
       <c r="G47">
         <v>4</v>
@@ -12493,7 +12493,7 @@
         <v>3.2</v>
       </c>
       <c r="K47">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12514,10 +12514,10 @@
         <v>1.57</v>
       </c>
       <c r="R47">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S47">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="T47">
         <v>1.01</v>
@@ -12723,7 +12723,7 @@
         <v>2.94</v>
       </c>
       <c r="G48">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="H48">
         <v>2.48</v>
@@ -12741,13 +12741,13 @@
         <v>1.36</v>
       </c>
       <c r="M48">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N48">
         <v>3.05</v>
       </c>
       <c r="O48">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="P48">
         <v>1.73</v>
@@ -12756,10 +12756,10 @@
         <v>2.12</v>
       </c>
       <c r="R48">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S48">
-        <v>2.18</v>
+        <v>2.46</v>
       </c>
       <c r="T48">
         <v>1.01</v>
@@ -12771,7 +12771,7 @@
         <v>1.57</v>
       </c>
       <c r="W48">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="X48">
         <v>1000</v>
@@ -12986,13 +12986,13 @@
         <v>1.07</v>
       </c>
       <c r="N49">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O49">
         <v>1.38</v>
       </c>
       <c r="P49">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="Q49">
         <v>2.16</v>
@@ -13237,16 +13237,16 @@
         <v>1.62</v>
       </c>
       <c r="Q50">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R50">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="S50">
         <v>4.5</v>
       </c>
       <c r="T50">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U50">
         <v>1.85</v>
@@ -13479,10 +13479,10 @@
         <v>1.73</v>
       </c>
       <c r="Q51">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R51">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S51">
         <v>3.95</v>
@@ -13712,19 +13712,19 @@
         <v>1.04</v>
       </c>
       <c r="N52">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="O52">
         <v>1.28</v>
       </c>
       <c r="P52">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="Q52">
         <v>1.86</v>
       </c>
       <c r="R52">
-        <v>1.26</v>
+        <v>1.41</v>
       </c>
       <c r="S52">
         <v>3.1</v>
@@ -14453,7 +14453,7 @@
         <v>1.6</v>
       </c>
       <c r="S55">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="T55">
         <v>1.01</v>
@@ -14692,10 +14692,10 @@
         <v>1.3</v>
       </c>
       <c r="R56">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="S56">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="T56">
         <v>1.36</v>
@@ -14991,7 +14991,7 @@
         <v>22</v>
       </c>
       <c r="AK57">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL57">
         <v>1000</v>
@@ -15021,7 +15021,7 @@
         <v>1.01</v>
       </c>
       <c r="AU57">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV57">
         <v>1.01</v>
@@ -15146,10 +15146,10 @@
         <v>3.1</v>
       </c>
       <c r="H58">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I58">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J58">
         <v>4.1</v>
@@ -15182,7 +15182,7 @@
         <v>2.18</v>
       </c>
       <c r="T58">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="U58">
         <v>2.48</v>
@@ -15221,7 +15221,7 @@
         <v>32</v>
       </c>
       <c r="AG58">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH58">
         <v>17.5</v>
@@ -15421,7 +15421,7 @@
         <v>2.04</v>
       </c>
       <c r="S59">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="T59">
         <v>1.49</v>
@@ -15639,7 +15639,7 @@
         <v>3.7</v>
       </c>
       <c r="K60">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -16604,7 +16604,7 @@
         <v>4.2</v>
       </c>
       <c r="J64">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K64">
         <v>3.7</v>
@@ -16616,7 +16616,7 @@
         <v>1.01</v>
       </c>
       <c r="N64">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="O64">
         <v>1.36</v>
@@ -16640,7 +16640,7 @@
         <v>1.01</v>
       </c>
       <c r="V64">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="W64">
         <v>1.79</v>
@@ -17121,7 +17121,7 @@
         <v>1.53</v>
       </c>
       <c r="U66">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="V66">
         <v>1.21</v>
@@ -17611,7 +17611,7 @@
         <v>1.12</v>
       </c>
       <c r="W68">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17832,10 +17832,10 @@
         <v>1.35</v>
       </c>
       <c r="P69">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="Q69">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="R69">
         <v>1.24</v>
@@ -18047,10 +18047,10 @@
         <v>4.2</v>
       </c>
       <c r="G70">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="H70">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="I70">
         <v>1.97</v>
@@ -18059,7 +18059,7 @@
         <v>3.7</v>
       </c>
       <c r="K70">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="L70">
         <v>1.27</v>
@@ -18095,7 +18095,7 @@
         <v>2.04</v>
       </c>
       <c r="W70">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -18289,7 +18289,7 @@
         <v>1.33</v>
       </c>
       <c r="G71">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="H71">
         <v>4.4</v>
@@ -18316,10 +18316,10 @@
         <v>1.19</v>
       </c>
       <c r="P71">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="Q71">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="R71">
         <v>1.4</v>
@@ -18337,7 +18337,7 @@
         <v>1.01</v>
       </c>
       <c r="W71">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="X71">
         <v>1000</v>
@@ -18534,7 +18534,7 @@
         <v>1.77</v>
       </c>
       <c r="H72">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I72">
         <v>17</v>
@@ -18543,7 +18543,7 @@
         <v>4.3</v>
       </c>
       <c r="K72">
-        <v>14</v>
+        <v>210</v>
       </c>
       <c r="L72">
         <v>1.01</v>
@@ -18824,7 +18824,7 @@
         <v>1.21</v>
       </c>
       <c r="X73">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="Y73">
         <v>7</v>
@@ -18869,16 +18869,16 @@
         <v>110</v>
       </c>
       <c r="AM73">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN73">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AO73">
         <v>17.5</v>
       </c>
       <c r="AP73">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ73">
         <v>6.6</v>
@@ -18923,7 +18923,7 @@
         <v>40</v>
       </c>
       <c r="BE73">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="BF73">
         <v>42</v>
@@ -18941,7 +18941,7 @@
         <v>11.5</v>
       </c>
       <c r="BK73">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BL73">
         <v>230</v>
@@ -18977,7 +18977,7 @@
         <v>14</v>
       </c>
       <c r="BW73">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BX73">
         <v>36</v>
@@ -19018,10 +19018,10 @@
         <v>4.2</v>
       </c>
       <c r="H74">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I74">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="J74">
         <v>3.95</v>
@@ -19045,10 +19045,10 @@
         <v>2.5</v>
       </c>
       <c r="Q74">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R74">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="S74">
         <v>2.3</v>
@@ -19057,10 +19057,10 @@
         <v>1.48</v>
       </c>
       <c r="U74">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="V74">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="W74">
         <v>1.31</v>
@@ -19093,7 +19093,7 @@
         <v>38</v>
       </c>
       <c r="AG74">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH74">
         <v>18</v>
@@ -19135,7 +19135,7 @@
         <v>15.5</v>
       </c>
       <c r="AU74">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV74">
         <v>8.6</v>
@@ -19147,13 +19147,13 @@
         <v>1.01</v>
       </c>
       <c r="AY74">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AZ74">
         <v>12</v>
       </c>
       <c r="BA74">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB74">
         <v>1.01</v>
@@ -19171,7 +19171,7 @@
         <v>19</v>
       </c>
       <c r="BG74">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="BH74">
         <v>1000</v>
@@ -19741,7 +19741,7 @@
         <v>2.08</v>
       </c>
       <c r="G77">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="H77">
         <v>3.4</v>
@@ -19780,7 +19780,7 @@
         <v>2.6</v>
       </c>
       <c r="T77">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="U77">
         <v>1.89</v>
@@ -19789,7 +19789,7 @@
         <v>1.35</v>
       </c>
       <c r="W77">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="X77">
         <v>1000</v>
@@ -19980,10 +19980,10 @@
         <v>316</v>
       </c>
       <c r="F78">
+        <v>5.9</v>
+      </c>
+      <c r="G78">
         <v>6</v>
-      </c>
-      <c r="G78">
-        <v>6.2</v>
       </c>
       <c r="H78">
         <v>1.57</v>
@@ -20022,16 +20022,16 @@
         <v>2.28</v>
       </c>
       <c r="T78">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="U78">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V78">
         <v>2.72</v>
       </c>
       <c r="W78">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X78">
         <v>30</v>
@@ -20061,7 +20061,7 @@
         <v>60</v>
       </c>
       <c r="AG78">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH78">
         <v>18</v>
@@ -20073,7 +20073,7 @@
         <v>140</v>
       </c>
       <c r="AK78">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AL78">
         <v>55</v>
@@ -20133,7 +20133,7 @@
         <v>50</v>
       </c>
       <c r="BE78">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BF78">
         <v>42</v>
@@ -20145,37 +20145,37 @@
         <v>4.8</v>
       </c>
       <c r="BI78">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="BJ78">
         <v>9.4</v>
       </c>
       <c r="BK78">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="BL78">
         <v>80</v>
       </c>
       <c r="BM78">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN78">
         <v>9.6</v>
       </c>
       <c r="BO78">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BP78">
         <v>40</v>
       </c>
       <c r="BQ78">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BR78">
         <v>38</v>
       </c>
       <c r="BS78">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BT78">
         <v>4.5</v>
@@ -20187,13 +20187,13 @@
         <v>9.6</v>
       </c>
       <c r="BW78">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX78">
         <v>19</v>
       </c>
       <c r="BY78">
-        <v>9.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BZ78">
         <v>11.5</v>
@@ -20464,22 +20464,22 @@
         <v>318</v>
       </c>
       <c r="F80">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G80">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H80">
         <v>1.67</v>
       </c>
       <c r="I80">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J80">
         <v>4.5</v>
       </c>
       <c r="K80">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="L80">
         <v>1.01</v>
@@ -20512,7 +20512,7 @@
         <v>2.42</v>
       </c>
       <c r="V80">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="W80">
         <v>1.25</v>
@@ -20709,7 +20709,7 @@
         <v>1.87</v>
       </c>
       <c r="G81">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H81">
         <v>3.9</v>
@@ -20763,7 +20763,7 @@
         <v>29</v>
       </c>
       <c r="Y81">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z81">
         <v>36</v>
@@ -20778,7 +20778,7 @@
         <v>12.5</v>
       </c>
       <c r="AD81">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE81">
         <v>55</v>
@@ -20835,7 +20835,7 @@
         <v>12.5</v>
       </c>
       <c r="AW81">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX81">
         <v>10</v>
@@ -20954,16 +20954,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H82">
+        <v>1.42</v>
+      </c>
+      <c r="I82">
         <v>1.43</v>
       </c>
-      <c r="I82">
-        <v>1.44</v>
-      </c>
       <c r="J82">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K82">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L82">
         <v>1.23</v>
@@ -20984,19 +20984,19 @@
         <v>1.42</v>
       </c>
       <c r="R82">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="S82">
         <v>2.06</v>
       </c>
       <c r="T82">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U82">
         <v>2.52</v>
       </c>
       <c r="V82">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="W82">
         <v>1.13</v>
@@ -21008,7 +21008,7 @@
         <v>15</v>
       </c>
       <c r="Z82">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AA82">
         <v>14</v>
@@ -21017,7 +21017,7 @@
         <v>44</v>
       </c>
       <c r="AC82">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD82">
         <v>10.5</v>
@@ -21038,7 +21038,7 @@
         <v>23</v>
       </c>
       <c r="AJ82">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AK82">
         <v>95</v>
@@ -21113,55 +21113,55 @@
         <v>6.4</v>
       </c>
       <c r="BI82">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BJ82">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BK82">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BL82">
         <v>80</v>
       </c>
       <c r="BM82">
-        <v>6.2</v>
+        <v>21</v>
       </c>
       <c r="BN82">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BO82">
-        <v>5.6</v>
+        <v>10</v>
       </c>
       <c r="BP82">
         <v>50</v>
       </c>
       <c r="BQ82">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BR82">
         <v>44</v>
       </c>
       <c r="BS82">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="BT82">
         <v>4.6</v>
       </c>
       <c r="BU82">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BV82">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="BW82">
         <v>7</v>
       </c>
       <c r="BX82">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="BY82">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BZ82">
         <v>9.6</v>
@@ -21190,16 +21190,16 @@
         <v>321</v>
       </c>
       <c r="F83">
+        <v>1.44</v>
+      </c>
+      <c r="G83">
         <v>1.45</v>
       </c>
-      <c r="G83">
-        <v>1.46</v>
-      </c>
       <c r="H83">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I83">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J83">
         <v>5.4</v>
@@ -21208,10 +21208,10 @@
         <v>5.6</v>
       </c>
       <c r="L83">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="M83">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N83">
         <v>6.6</v>
@@ -21229,13 +21229,13 @@
         <v>1.81</v>
       </c>
       <c r="S83">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="T83">
         <v>1.68</v>
       </c>
       <c r="U83">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="V83">
         <v>1.14</v>
@@ -21253,7 +21253,7 @@
         <v>75</v>
       </c>
       <c r="AA83">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="AB83">
         <v>13.5</v>
@@ -21349,10 +21349,10 @@
         <v>4.3</v>
       </c>
       <c r="BG83">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="BH83">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BI83">
         <v>3.9</v>
@@ -21361,7 +21361,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK83">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL83">
         <v>100</v>
@@ -21385,7 +21385,7 @@
         <v>18.5</v>
       </c>
       <c r="BS83">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT83">
         <v>11.5</v>
@@ -21394,7 +21394,7 @@
         <v>7.4</v>
       </c>
       <c r="BV83">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BW83">
         <v>1.01</v>
@@ -21438,13 +21438,13 @@
         <v>1.2</v>
       </c>
       <c r="H84">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="I84">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J84">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="K84">
         <v>8.199999999999999</v>
@@ -21453,31 +21453,31 @@
         <v>1.01</v>
       </c>
       <c r="M84">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N84">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O84">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P84">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q84">
         <v>1.7</v>
       </c>
       <c r="R84">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S84">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T84">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="U84">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V84">
         <v>1.03</v>
@@ -21486,34 +21486,34 @@
         <v>6</v>
       </c>
       <c r="X84">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="Y84">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="Z84">
-        <v>270</v>
+        <v>340</v>
       </c>
       <c r="AA84">
         <v>1000</v>
       </c>
       <c r="AB84">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AC84">
         <v>970</v>
       </c>
       <c r="AD84">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="AE84">
         <v>1000</v>
       </c>
       <c r="AF84">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG84">
-        <v>13</v>
+        <v>16.5</v>
       </c>
       <c r="AH84">
         <v>70</v>
@@ -21522,10 +21522,10 @@
         <v>530</v>
       </c>
       <c r="AJ84">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AK84">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="AL84">
         <v>75</v>
@@ -21534,64 +21534,64 @@
         <v>470</v>
       </c>
       <c r="AN84">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="AO84">
         <v>1000</v>
       </c>
       <c r="AP84">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ84">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AR84">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AS84">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT84">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AU84">
         <v>16.5</v>
       </c>
       <c r="AV84">
+        <v>6</v>
+      </c>
+      <c r="AW84">
+        <v>6</v>
+      </c>
+      <c r="AX84">
+        <v>5.6</v>
+      </c>
+      <c r="AY84">
+        <v>12</v>
+      </c>
+      <c r="AZ84">
         <v>5.9</v>
       </c>
-      <c r="AW84">
-        <v>6.2</v>
-      </c>
-      <c r="AX84">
-        <v>5.9</v>
-      </c>
-      <c r="AY84">
-        <v>11</v>
-      </c>
-      <c r="AZ84">
-        <v>5.8</v>
-      </c>
       <c r="BA84">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB84">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC84">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BD84">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE84">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BF84">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BG84">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH84">
         <v>1000</v>
@@ -21680,7 +21680,7 @@
         <v>3.25</v>
       </c>
       <c r="H85">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I85">
         <v>3</v>
@@ -21919,40 +21919,40 @@
         <v>1.52</v>
       </c>
       <c r="G86">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="H86">
         <v>6.4</v>
       </c>
       <c r="I86">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="J86">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K86">
         <v>5.4</v>
       </c>
       <c r="L86">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M86">
         <v>1.01</v>
       </c>
       <c r="N86">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="O86">
         <v>1.41</v>
       </c>
       <c r="P86">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q86">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="R86">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S86">
         <v>3.45</v>
@@ -21964,10 +21964,10 @@
         <v>1.01</v>
       </c>
       <c r="V86">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="W86">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="X86">
         <v>1000</v>
